--- a/pinokio_repos.xlsx
+++ b/pinokio_repos.xlsx
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-01-17T14:29:21Z</t>
+          <t>2026-01-31T15:36:48Z</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-01-17T14:29:18Z</t>
+          <t>2026-01-31T15:36:45Z</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -2461,7 +2461,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-01-17T22:52:18Z</t>
+          <t>2026-01-31T16:23:34Z</t>
         </is>
       </c>
       <c r="L53" t="n">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2025-12-19T04:34:35Z</t>
+          <t>2026-01-29T13:21:03Z</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2627,11 +2627,11 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2025-12-20T14:59:59Z</t>
+          <t>2026-02-01T04:51:15Z</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="57">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-01-21T16:57:23Z</t>
+          <t>2026-01-30T00:41:21Z</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-01-05T22:06:28Z</t>
+          <t>2026-01-30T00:41:17Z</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-01-25T02:33:03Z</t>
+          <t>2026-01-31T21:11:44Z</t>
         </is>
       </c>
       <c r="L61" t="n">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2025-11-19T15:34:36Z</t>
+          <t>2026-01-27T14:53:11Z</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3515,11 +3515,11 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2025-11-22T16:44:52Z</t>
+          <t>2026-02-01T03:05:32Z</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>299</v>
+        <v>309</v>
       </c>
     </row>
     <row r="73">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-01-18T21:13:14Z</t>
+          <t>2026-01-28T09:41:31Z</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3731,11 +3731,11 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-01-25T06:27:26Z</t>
+          <t>2026-02-01T06:34:39Z</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>612</v>
+        <v>639</v>
       </c>
     </row>
     <row r="77">
@@ -4027,12 +4027,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-01-03T13:47:18Z</t>
+          <t>2026-01-30T21:11:00Z</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-01-03T13:47:14Z</t>
+          <t>2026-01-30T21:10:56Z</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -4055,11 +4055,11 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-01-04T06:06:33Z</t>
+          <t>2026-02-01T01:25:30Z</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="83">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-01-24T21:46:05Z</t>
+          <t>2026-02-01T06:38:32Z</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4495,11 +4495,11 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-01-25T06:33:29Z</t>
+          <t>2026-02-01T06:53:32Z</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="91">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-01-13T11:25:28Z</t>
+          <t>2026-01-29T08:58:01Z</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -4943,11 +4943,11 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2026-01-18T01:58:21Z</t>
+          <t>2026-01-31T14:40:21Z</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="99">

--- a/pinokio_repos.xlsx
+++ b/pinokio_repos.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L99"/>
+  <dimension ref="A1:L100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-01-23T21:14:27Z</t>
+          <t>2026-02-03T09:04:11Z</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-01-16T04:36:18Z</t>
+          <t>2026-02-06T04:29:23Z</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1765,28 +1765,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>moshi</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
+          <t>mlx-video-ui</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Pinokio launcher scripts for MLX Video UI</t>
+        </is>
+      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/moshi</t>
+          <t>https://github.com/pinokiofactory/mlx-video-ui</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2024-09-18T19:39:38Z</t>
+          <t>2026-02-07T12:57:17Z</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2025-03-16T23:50:32Z</t>
+          <t>2026-02-08T00:09:41Z</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2025-03-16T23:50:29Z</t>
+          <t>2026-02-08T00:09:37Z</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -1801,28 +1805,28 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ominicontrol</t>
+          <t>moshi</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/ominicontrol</t>
+          <t>https://github.com/pinokiofactory/moshi</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2024-11-25T21:32:15Z</t>
+          <t>2024-09-18T19:39:38Z</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024-11-27T09:17:35Z</t>
+          <t>2025-03-16T23:50:32Z</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2024-11-27T09:17:32Z</t>
+          <t>2025-03-16T23:50:29Z</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -1837,32 +1841,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>omnigen</t>
+          <t>ominicontrol</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/omnigen</t>
+          <t>https://github.com/pinokiofactory/ominicontrol</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2024-10-23T18:24:35Z</t>
+          <t>2024-11-25T21:32:15Z</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2025-12-02T23:04:52Z</t>
+          <t>2024-11-27T09:17:35Z</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2025-12-02T23:04:48Z</t>
+          <t>2024-11-27T09:17:32Z</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
@@ -1873,32 +1877,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>open-webui</t>
+          <t>omnigen</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/open-webui</t>
+          <t>https://github.com/pinokiofactory/omnigen</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2024-07-23T16:53:00Z</t>
+          <t>2024-10-23T18:24:35Z</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2025-12-05T18:23:58Z</t>
+          <t>2026-02-04T06:30:37Z</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2025-11-25T11:47:58Z</t>
+          <t>2025-12-02T23:04:48Z</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
@@ -1909,32 +1913,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>openui</t>
+          <t>open-webui</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/openui</t>
+          <t>https://github.com/pinokiofactory/open-webui</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2024-05-08T08:33:21Z</t>
+          <t>2024-07-23T16:53:00Z</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2025-11-04T12:30:09Z</t>
+          <t>2025-12-05T18:23:58Z</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2024-11-28T23:09:18Z</t>
+          <t>2025-11-25T11:47:58Z</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
@@ -1945,32 +1949,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>pcm</t>
+          <t>openui</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/pcm</t>
+          <t>https://github.com/pinokiofactory/openui</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2024-06-05T15:35:00Z</t>
+          <t>2024-05-08T08:33:21Z</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2025-03-20T03:06:10Z</t>
+          <t>2025-11-04T12:30:09Z</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2025-03-20T03:06:07Z</t>
+          <t>2024-11-28T23:09:18Z</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
@@ -1981,28 +1985,28 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>photomaker2</t>
+          <t>pcm</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/photomaker2</t>
+          <t>https://github.com/pinokiofactory/pcm</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2024-07-22T16:01:32Z</t>
+          <t>2024-06-05T15:35:00Z</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-01-10T21:15:09Z</t>
+          <t>2025-03-20T03:06:10Z</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-01-10T21:15:05Z</t>
+          <t>2025-03-20T03:06:07Z</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -2017,28 +2021,28 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>rc-stableaudio</t>
+          <t>photomaker2</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/rc-stableaudio</t>
+          <t>https://github.com/pinokiofactory/photomaker2</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2024-07-29T14:44:01Z</t>
+          <t>2024-07-22T16:01:32Z</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2025-11-03T21:06:34Z</t>
+          <t>2026-01-10T21:15:09Z</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2025-03-17T00:05:11Z</t>
+          <t>2026-01-10T21:15:05Z</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -2053,28 +2057,28 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>sd35</t>
+          <t>rc-stableaudio</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/sd35</t>
+          <t>https://github.com/pinokiofactory/rc-stableaudio</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2024-10-22T19:23:06Z</t>
+          <t>2024-07-29T14:44:01Z</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2024-10-22T19:50:14Z</t>
+          <t>2025-11-03T21:06:34Z</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2024-10-22T19:50:11Z</t>
+          <t>2025-03-17T00:05:11Z</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -2089,32 +2093,32 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>sillytavern</t>
+          <t>sd35</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/sillytavern</t>
+          <t>https://github.com/pinokiofactory/sd35</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2024-05-21T11:58:31Z</t>
+          <t>2024-10-22T19:23:06Z</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2025-12-29T07:25:21Z</t>
+          <t>2024-10-22T19:50:14Z</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2025-11-26T23:36:47Z</t>
+          <t>2024-10-22T19:50:11Z</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
@@ -2125,32 +2129,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>stable-fast-3d</t>
+          <t>sillytavern</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/stable-fast-3d</t>
+          <t>https://github.com/pinokiofactory/sillytavern</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2024-08-01T18:33:57Z</t>
+          <t>2024-05-21T11:58:31Z</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2024-08-07T20:21:37Z</t>
+          <t>2025-12-29T07:25:21Z</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2024-08-01T18:34:06Z</t>
+          <t>2025-11-26T23:36:47Z</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
@@ -2161,28 +2165,28 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>stableaudio</t>
+          <t>stable-fast-3d</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/stableaudio</t>
+          <t>https://github.com/pinokiofactory/stable-fast-3d</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2024-06-05T20:15:59Z</t>
+          <t>2024-08-01T18:33:57Z</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2025-12-30T00:17:54Z</t>
+          <t>2024-08-07T20:21:37Z</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2025-03-17T00:31:10Z</t>
+          <t>2024-08-01T18:34:06Z</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -2197,28 +2201,28 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>video-background-removal</t>
+          <t>stableaudio</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/video-background-removal</t>
+          <t>https://github.com/pinokiofactory/stableaudio</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2024-10-11T16:00:13Z</t>
+          <t>2024-06-05T20:15:59Z</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2025-01-23T21:17:20Z</t>
+          <t>2025-12-30T00:17:54Z</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2024-10-11T17:35:54Z</t>
+          <t>2025-03-17T00:31:10Z</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -2233,32 +2237,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>video-background-removal</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/y</t>
+          <t>https://github.com/pinokiofactory/video-background-removal</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2024-05-20T15:06:00Z</t>
+          <t>2024-10-11T16:00:13Z</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2024-05-20T15:06:01Z</t>
+          <t>2025-01-23T21:17:20Z</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2024-05-20T15:06:01Z</t>
+          <t>2024-10-11T17:35:54Z</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
@@ -2269,32 +2273,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>z-image-turbo</t>
+          <t>y</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/z-image-turbo</t>
+          <t>https://github.com/pinokiofactory/y</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025-12-01T15:28:39Z</t>
+          <t>2024-05-20T15:06:00Z</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2025-12-01T19:45:36Z</t>
+          <t>2024-05-20T15:06:01Z</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2025-12-01T15:28:52Z</t>
+          <t>2024-05-20T15:06:01Z</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
@@ -2305,82 +2309,64 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ovis</t>
+          <t>z-image-turbo</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/ovis</t>
+          <t>https://github.com/pinokiofactory/z-image-turbo</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025-12-01T17:31:10Z</t>
+          <t>2025-12-01T15:28:39Z</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2025-12-01T19:45:35Z</t>
+          <t>2025-12-01T19:45:36Z</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2025-12-01T17:31:27Z</t>
+          <t>2025-12-01T15:28:52Z</t>
         </is>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>AIDC-AI/Ovis-Image</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/AIDC-AI/Ovis-Image</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>2025-11-18T03:46:26Z</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>2025-12-07T06:14:47Z</t>
-        </is>
-      </c>
-      <c r="L51" t="n">
-        <v>4</v>
-      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>text2midi</t>
+          <t>ovis</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/text2midi</t>
+          <t>https://github.com/pinokiofactory/ovis</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2024-12-27T18:31:20Z</t>
+          <t>2025-12-01T17:31:10Z</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2024-12-27T19:21:42Z</t>
+          <t>2025-12-01T19:45:35Z</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2024-12-27T19:21:39Z</t>
+          <t>2025-12-01T17:31:27Z</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -2388,57 +2374,53 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>AMAAI-Lab/Text2midi</t>
+          <t>AIDC-AI/Ovis-Image</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/AMAAI-Lab/Text2midi</t>
+          <t>https://github.com/AIDC-AI/Ovis-Image</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2024-12-19T07:51:33Z</t>
+          <t>2025-11-18T03:46:26Z</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2025-11-15T04:41:44Z</t>
+          <t>2025-12-07T06:14:47Z</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SongGeneration-Studio-MLX</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Tencent SongGeneration Studio MLX</t>
-        </is>
-      </c>
+          <t>text2midi</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/SongGeneration-Studio-MLX</t>
+          <t>https://github.com/pinokiofactory/text2midi</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-01-17T09:12:39Z</t>
+          <t>2024-12-27T18:31:20Z</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-01-31T15:36:48Z</t>
+          <t>2024-12-27T19:21:42Z</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-01-31T15:36:45Z</t>
+          <t>2024-12-27T19:21:39Z</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -2446,493 +2428,497 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>CharafChnioune/SongGeneration-Studio-MLX</t>
+          <t>AMAAI-Lab/Text2midi</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/CharafChnioune/SongGeneration-Studio-MLX</t>
+          <t>https://github.com/AMAAI-Lab/Text2midi</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-01-16T21:45:05Z</t>
+          <t>2024-12-19T07:51:33Z</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-01-31T16:23:34Z</t>
+          <t>2025-11-15T04:41:44Z</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>comfy</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr"/>
+          <t>SongGeneration-Studio-MLX</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Tencent SongGeneration Studio MLX</t>
+        </is>
+      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/comfy</t>
+          <t>https://github.com/pinokiofactory/SongGeneration-Studio-MLX</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2024-08-13T19:47:18Z</t>
+          <t>2026-01-17T09:12:39Z</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-01-14T11:37:40Z</t>
+          <t>2026-02-01T18:10:47Z</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2025-12-02T21:35:15Z</t>
+          <t>2026-01-31T15:36:45Z</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Comfy-Org/ComfyUI</t>
+          <t>CharafChnioune/SongGeneration-Studio-MLX</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/Comfy-Org/ComfyUI</t>
+          <t>https://github.com/CharafChnioune/SongGeneration-Studio-MLX</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2023-01-17T03:15:56Z</t>
+          <t>2026-01-16T21:45:05Z</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-01-18T06:40:45Z</t>
+          <t>2026-02-06T12:35:34Z</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>3530</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>audiocraft_plus</t>
+          <t>comfy</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/audiocraft_plus</t>
+          <t>https://github.com/pinokiofactory/comfy</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2024-07-30T17:39:46Z</t>
+          <t>2024-08-13T19:47:18Z</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2025-03-17T00:02:40Z</t>
+          <t>2026-01-14T11:37:40Z</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2025-03-17T00:02:36Z</t>
+          <t>2025-12-02T21:35:15Z</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>GrandaddyShmax/audiocraft_plus</t>
+          <t>Comfy-Org/ComfyUI</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/GrandaddyShmax/audiocraft_plus</t>
+          <t>https://github.com/Comfy-Org/ComfyUI</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2023-06-13T14:44:53Z</t>
+          <t>2023-01-17T03:15:56Z</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2025-11-05T05:42:24Z</t>
+          <t>2026-01-18T06:40:45Z</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>38</v>
+        <v>3530</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>applio</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Pinokio Installer for Applio</t>
-        </is>
-      </c>
+          <t>audiocraft_plus</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/applio</t>
+          <t>https://github.com/pinokiofactory/audiocraft_plus</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2024-09-13T18:29:14Z</t>
+          <t>2024-07-30T17:39:46Z</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-01-29T13:21:03Z</t>
+          <t>2025-03-17T00:02:40Z</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2025-12-19T04:34:32Z</t>
+          <t>2025-03-17T00:02:36Z</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>IAHispano/Applio</t>
+          <t>GrandaddyShmax/audiocraft_plus</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/IAHispano/Applio</t>
+          <t>https://github.com/GrandaddyShmax/audiocraft_plus</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2023-08-07T22:42:16Z</t>
+          <t>2023-06-13T14:44:53Z</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-02-01T04:51:15Z</t>
+          <t>2025-11-05T05:42:24Z</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>liveportrait</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr"/>
+          <t>applio</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Pinokio Installer for Applio</t>
+        </is>
+      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/liveportrait</t>
+          <t>https://github.com/pinokiofactory/applio</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2024-07-22T12:47:06Z</t>
+          <t>2024-09-13T18:29:14Z</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-01-25T06:00:38Z</t>
+          <t>2026-01-29T13:21:03Z</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-01-25T06:00:34Z</t>
+          <t>2025-12-19T04:34:32Z</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>KlingTeam/LivePortrait</t>
+          <t>IAHispano/Applio</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/KlingTeam/LivePortrait</t>
+          <t>https://github.com/IAHispano/Applio</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2024-07-03T16:15:03Z</t>
+          <t>2023-08-07T22:42:16Z</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-01-25T04:17:48Z</t>
+          <t>2026-02-01T04:51:15Z</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>284</v>
+        <v>31</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Orpheus-TTS-FastAPI</t>
+          <t>liveportrait</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/Orpheus-TTS-FastAPI</t>
+          <t>https://github.com/pinokiofactory/liveportrait</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025-03-23T05:39:00Z</t>
+          <t>2024-07-22T12:47:06Z</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-01-24T23:02:12Z</t>
+          <t>2026-01-25T06:00:38Z</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2025-12-02T20:56:20Z</t>
+          <t>2026-01-25T06:00:34Z</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Lex-au/Orpheus-FastAPI</t>
+          <t>KlingTeam/LivePortrait</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/Lex-au/Orpheus-FastAPI</t>
+          <t>https://github.com/KlingTeam/LivePortrait</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2025-03-21T15:24:16Z</t>
+          <t>2024-07-03T16:15:03Z</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-01-24T18:58:41Z</t>
+          <t>2026-01-25T04:17:48Z</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>14</v>
+        <v>284</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>mlx-video-transcription</t>
+          <t>Orpheus-TTS-FastAPI</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/mlx-video-transcription</t>
+          <t>https://github.com/pinokiofactory/Orpheus-TTS-FastAPI</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2024-08-19T17:41:12Z</t>
+          <t>2025-03-23T05:39:00Z</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-01-09T05:42:44Z</t>
+          <t>2026-01-24T23:02:12Z</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2024-10-03T19:11:23Z</t>
+          <t>2025-12-02T20:56:20Z</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>RayFernando1337/MLX-Auto-Subtitled-Video-Generator</t>
+          <t>Lex-au/Orpheus-FastAPI</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/RayFernando1337/MLX-Auto-Subtitled-Video-Generator</t>
+          <t>https://github.com/Lex-au/Orpheus-FastAPI</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2024-07-30T08:44:41Z</t>
+          <t>2025-03-21T15:24:16Z</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-01-10T13:59:01Z</t>
+          <t>2026-01-24T18:58:41Z</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>cube</t>
+          <t>mlx-video-transcription</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/cube</t>
+          <t>https://github.com/pinokiofactory/mlx-video-transcription</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025-03-20T21:16:36Z</t>
+          <t>2024-08-19T17:41:12Z</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-01-24T17:31:53Z</t>
+          <t>2026-01-09T05:42:44Z</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2025-12-02T21:01:20Z</t>
+          <t>2024-10-03T19:11:23Z</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Roblox/cube</t>
+          <t>RayFernando1337/MLX-Auto-Subtitled-Video-Generator</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/Roblox/cube</t>
+          <t>https://github.com/RayFernando1337/MLX-Auto-Subtitled-Video-Generator</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2025-03-11T22:09:47Z</t>
+          <t>2024-07-30T08:44:41Z</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-01-24T17:32:07Z</t>
+          <t>2026-01-10T13:59:01Z</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Ultimate-TTS-Studio</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>🟢 NVIDIA ONLY – All-in-One TTS App with Kokoro, KittenTTS, Higgs audio, Chatterbox, Fish-Speech, F5 &amp; index-tts &amp; indextts2, Supports Conversation Mode &amp; eBook-to-Audiobook. All features work across all engines in a unified interface except vibe voice which is it's own app panel.</t>
-        </is>
-      </c>
+          <t>cube</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/Ultimate-TTS-Studio</t>
+          <t>https://github.com/pinokiofactory/cube</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025-11-25T20:10:36Z</t>
+          <t>2025-03-20T21:16:36Z</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-01-30T00:41:21Z</t>
+          <t>2026-01-24T17:31:53Z</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-01-30T00:41:17Z</t>
+          <t>2025-12-02T21:01:20Z</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>SUP3RMASS1VE/Ultimate-TTS-Studio-SUP3R-Edition</t>
+          <t>Roblox/cube</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/SUP3RMASS1VE/Ultimate-TTS-Studio-SUP3R-Edition</t>
+          <t>https://github.com/Roblox/cube</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2025-06-06T14:54:06Z</t>
+          <t>2025-03-11T22:09:47Z</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-01-31T21:11:44Z</t>
+          <t>2026-01-24T17:32:07Z</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>hertz</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr"/>
+          <t>Ultimate-TTS-Studio</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>🟢 NVIDIA ONLY – All-in-One TTS App with Kokoro, KittenTTS, Higgs audio, Chatterbox, Fish-Speech, F5 &amp; index-tts &amp; indextts2, Supports Conversation Mode &amp; eBook-to-Audiobook. All features work across all engines in a unified interface except vibe voice which is it's own app panel.</t>
+        </is>
+      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/hertz</t>
+          <t>https://github.com/pinokiofactory/Ultimate-TTS-Studio</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2024-11-04T01:04:51Z</t>
+          <t>2025-11-25T20:10:36Z</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2024-11-05T08:54:25Z</t>
+          <t>2026-02-08T01:00:40Z</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2024-11-05T08:54:21Z</t>
+          <t>2026-01-30T00:41:17Z</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -2940,111 +2926,111 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Standard-Intelligence/hertz-dev</t>
+          <t>SUP3RMASS1VE/Ultimate-TTS-Studio-SUP3R-Edition</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/Standard-Intelligence/hertz-dev</t>
+          <t>https://github.com/SUP3RMASS1VE/Ultimate-TTS-Studio-SUP3R-Edition</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2024-11-03T14:41:39Z</t>
+          <t>2025-06-06T14:54:06Z</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2025-11-14T16:05:18Z</t>
+          <t>2026-02-08T01:00:48Z</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Hunyuan3D-2</t>
+          <t>hertz</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/Hunyuan3D-2</t>
+          <t>https://github.com/pinokiofactory/hertz</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025-01-25T04:41:01Z</t>
+          <t>2024-11-04T01:04:51Z</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2025-11-09T20:06:13Z</t>
+          <t>2024-11-05T08:54:25Z</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2025-11-09T20:06:10Z</t>
+          <t>2024-11-05T08:54:21Z</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Tencent-Hunyuan/Hunyuan3D-2</t>
+          <t>Standard-Intelligence/hertz-dev</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/Tencent-Hunyuan/Hunyuan3D-2</t>
+          <t>https://github.com/Standard-Intelligence/hertz-dev</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2025-01-21T05:21:35Z</t>
+          <t>2024-11-03T14:41:39Z</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2025-11-16T06:33:02Z</t>
+          <t>2025-11-14T16:05:18Z</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>219</v>
+        <v>16</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Hunyuan3D-2-mini</t>
+          <t>Hunyuan3D-2</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/Hunyuan3D-2-mini</t>
+          <t>https://github.com/pinokiofactory/Hunyuan3D-2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025-01-23T21:29:42Z</t>
+          <t>2025-01-25T04:41:01Z</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2025-01-25T03:18:46Z</t>
+          <t>2025-11-09T20:06:13Z</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2025-01-25T03:50:23Z</t>
+          <t>2025-11-09T20:06:10Z</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -3073,32 +3059,28 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AudioX</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>AudioX: Diffusion Transformer for Anything-to-Audio Generation</t>
-        </is>
-      </c>
+          <t>Hunyuan3D-2-mini</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/AudioX</t>
+          <t>https://github.com/pinokiofactory/Hunyuan3D-2-mini</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025-04-23T00:08:00Z</t>
+          <t>2025-01-23T21:29:42Z</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2025-07-12T12:25:25Z</t>
+          <t>2025-01-25T03:18:46Z</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2025-07-12T12:25:21Z</t>
+          <t>2025-01-25T03:50:23Z</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -3106,771 +3088,775 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>ZeyueT/AudioX</t>
+          <t>Tencent-Hunyuan/Hunyuan3D-2</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/ZeyueT/AudioX</t>
+          <t>https://github.com/Tencent-Hunyuan/Hunyuan3D-2</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2025-03-13T10:18:21Z</t>
+          <t>2025-01-21T05:21:35Z</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2025-11-14T16:45:52Z</t>
+          <t>2025-11-16T06:33:02Z</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>52</v>
+        <v>219</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>RMBG-2-Studio</t>
+          <t>AudioX</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Enhanced background remove and replace app built around BRIA-RMBG-2.0.  Low VRAM/RAM | 6GB Install</t>
+          <t>AudioX: Diffusion Transformer for Anything-to-Audio Generation</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/RMBG-2-Studio</t>
+          <t>https://github.com/pinokiofactory/AudioX</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2024-11-15T07:13:23Z</t>
+          <t>2025-04-23T00:08:00Z</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-01-06T18:02:20Z</t>
+          <t>2025-07-12T12:25:25Z</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2025-12-02T22:50:55Z</t>
+          <t>2025-07-12T12:25:21Z</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>ZhengPeng7/BiRefNet</t>
+          <t>ZeyueT/AudioX</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/ZhengPeng7/BiRefNet</t>
+          <t>https://github.com/ZeyueT/AudioX</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2022-08-17T09:13:39Z</t>
+          <t>2025-03-13T10:18:21Z</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-01-11T03:52:31Z</t>
+          <t>2025-11-14T16:45:52Z</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>21</v>
+        <v>52</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>zonos</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr"/>
+          <t>RMBG-2-Studio</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Enhanced background remove and replace app built around BRIA-RMBG-2.0.  Low VRAM/RAM | 6GB Install</t>
+        </is>
+      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/zonos</t>
+          <t>https://github.com/pinokiofactory/RMBG-2-Studio</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025-02-11T09:00:12Z</t>
+          <t>2024-11-15T07:13:23Z</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2025-12-06T22:44:56Z</t>
+          <t>2026-01-06T18:02:20Z</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2025-12-06T22:44:52Z</t>
+          <t>2025-12-02T22:50:55Z</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Zyphra/Zonos</t>
+          <t>ZhengPeng7/BiRefNet</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/Zyphra/Zonos</t>
+          <t>https://github.com/ZhengPeng7/BiRefNet</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2025-02-07T00:32:44Z</t>
+          <t>2022-08-17T09:13:39Z</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2025-12-06T07:10:48Z</t>
+          <t>2026-01-11T03:52:31Z</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>167</v>
+        <v>21</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ACE-Step</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>A Step Towards Music Generation Foundation Model</t>
-        </is>
-      </c>
+          <t>zonos</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/ACE-Step</t>
+          <t>https://github.com/pinokiofactory/zonos</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025-05-07T11:25:33Z</t>
+          <t>2025-02-11T09:00:12Z</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2025-12-06T11:35:01Z</t>
+          <t>2025-12-06T22:44:56Z</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2025-12-06T11:34:57Z</t>
+          <t>2025-12-06T22:44:52Z</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>ace-step/ACE-Step</t>
+          <t>Zyphra/Zonos</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/ace-step/ACE-Step</t>
+          <t>https://github.com/Zyphra/Zonos</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2025-04-28T07:03:09Z</t>
+          <t>2025-02-07T00:32:44Z</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2025-12-07T04:48:04Z</t>
+          <t>2025-12-06T07:10:48Z</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>118</v>
+        <v>167</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>MagicQuill</t>
+          <t>ACE-Step</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>An intelligent, interactive Image Editing System. Easily erase and add objects on a user-friendly interface.</t>
+          <t>A Step Towards Music Generation Foundation Model</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/MagicQuill</t>
+          <t>https://github.com/pinokiofactory/ACE-Step</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025-02-19T03:58:52Z</t>
+          <t>2025-05-07T11:25:33Z</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-01-11T20:08:02Z</t>
+          <t>2025-12-06T11:35:01Z</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-01-11T20:07:58Z</t>
+          <t>2025-12-06T11:34:57Z</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>ant-research/MagicQuill</t>
+          <t>ace-step/ACE-Step</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/ant-research/MagicQuill</t>
+          <t>https://github.com/ace-step/ACE-Step</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2024-11-12T12:52:36Z</t>
+          <t>2025-04-28T07:03:09Z</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-01-13T22:00:43Z</t>
+          <t>2025-12-07T04:48:04Z</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>46</v>
+        <v>118</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>echomimic2</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr"/>
+          <t>MagicQuill</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>An intelligent, interactive Image Editing System. Easily erase and add objects on a user-friendly interface.</t>
+        </is>
+      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/echomimic2</t>
+          <t>https://github.com/pinokiofactory/MagicQuill</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2024-11-24T07:52:04Z</t>
+          <t>2025-02-19T03:58:52Z</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2025-12-06T05:47:59Z</t>
+          <t>2026-01-11T20:08:02Z</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2025-12-06T05:47:56Z</t>
+          <t>2026-01-11T20:07:58Z</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>antgroup/echomimic_v2</t>
+          <t>ant-research/MagicQuill</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antgroup/echomimic_v2</t>
+          <t>https://github.com/ant-research/MagicQuill</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2024-11-20T08:35:35Z</t>
+          <t>2024-11-12T12:52:36Z</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2025-12-06T17:52:50Z</t>
+          <t>2026-01-13T22:00:43Z</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>79</v>
+        <v>46</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>macOS-use</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>We Make Mac apps accessible for AI agents</t>
-        </is>
-      </c>
+          <t>echomimic2</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/macOS-use</t>
+          <t>https://github.com/pinokiofactory/echomimic2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025-02-18T16:54:37Z</t>
+          <t>2024-11-24T07:52:04Z</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2025-11-04T13:06:11Z</t>
+          <t>2025-12-06T05:47:59Z</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2025-04-01T04:14:59Z</t>
+          <t>2025-12-06T05:47:56Z</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>browser-use/macOS-use</t>
+          <t>antgroup/echomimic_v2</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/browser-use/macOS-use</t>
+          <t>https://github.com/antgroup/echomimic_v2</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2025-01-23T00:35:15Z</t>
+          <t>2024-11-20T08:35:35Z</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2025-11-14T12:34:29Z</t>
+          <t>2025-12-06T17:52:50Z</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>16</v>
+        <v>79</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>browser-use</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr"/>
+          <t>macOS-use</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>We Make Mac apps accessible for AI agents</t>
+        </is>
+      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/browser-use</t>
+          <t>https://github.com/pinokiofactory/macOS-use</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025-01-19T21:55:50Z</t>
+          <t>2025-02-18T16:54:37Z</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-01-27T14:53:11Z</t>
+          <t>2025-11-04T13:06:11Z</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2025-04-01T04:25:12Z</t>
+          <t>2025-04-01T04:14:59Z</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>browser-use/web-ui</t>
+          <t>browser-use/macOS-use</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/browser-use/web-ui</t>
+          <t>https://github.com/browser-use/macOS-use</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2025-01-02T01:29:44Z</t>
+          <t>2025-01-23T00:35:15Z</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-02-01T03:05:32Z</t>
+          <t>2025-11-14T12:34:29Z</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>309</v>
+        <v>16</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>uno</t>
+          <t>browser-use</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/uno</t>
+          <t>https://github.com/pinokiofactory/browser-use</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025-04-10T18:31:57Z</t>
+          <t>2025-01-19T21:55:50Z</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2025-12-02T20:55:29Z</t>
+          <t>2026-01-27T14:53:11Z</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2025-12-02T20:55:25Z</t>
+          <t>2025-04-01T04:25:12Z</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>bytedance/UNO</t>
+          <t>browser-use/web-ui</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/bytedance/UNO</t>
+          <t>https://github.com/browser-use/web-ui</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2025-04-01T13:25:11Z</t>
+          <t>2025-01-02T01:29:44Z</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2025-12-04T05:12:09Z</t>
+          <t>2026-02-01T03:05:32Z</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>28</v>
+        <v>309</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Hunyuan3d-2-lowvram</t>
+          <t>uno</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/Hunyuan3d-2-lowvram</t>
+          <t>https://github.com/pinokiofactory/uno</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025-01-25T04:44:25Z</t>
+          <t>2025-04-10T18:31:57Z</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-01-18T02:36:25Z</t>
+          <t>2025-12-02T20:55:29Z</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2025-12-27T20:44:51Z</t>
+          <t>2025-12-02T20:55:25Z</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>deepbeepmeep/Hunyuan3D-2GP</t>
+          <t>bytedance/UNO</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/deepbeepmeep/Hunyuan3D-2GP</t>
+          <t>https://github.com/bytedance/UNO</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2025-01-22T01:50:03Z</t>
+          <t>2025-04-01T13:25:11Z</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-01-18T03:01:59Z</t>
+          <t>2025-12-04T05:12:09Z</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>hunyuanvideo</t>
+          <t>Hunyuan3d-2-lowvram</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/hunyuanvideo</t>
+          <t>https://github.com/pinokiofactory/Hunyuan3d-2-lowvram</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2024-12-11T01:55:53Z</t>
+          <t>2025-01-25T04:44:25Z</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-01-19T16:49:14Z</t>
+          <t>2026-01-18T02:36:25Z</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2025-12-02T20:58:56Z</t>
+          <t>2025-12-27T20:44:51Z</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>deepbeepmeep/HunyuanVideoGP</t>
+          <t>deepbeepmeep/Hunyuan3D-2GP</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/deepbeepmeep/HunyuanVideoGP</t>
+          <t>https://github.com/deepbeepmeep/Hunyuan3D-2GP</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2024-12-10T18:34:42Z</t>
+          <t>2025-01-22T01:50:03Z</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-01-21T10:14:46Z</t>
+          <t>2026-01-18T03:01:59Z</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>wan</t>
+          <t>hunyuanvideo</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/wan</t>
+          <t>https://github.com/pinokiofactory/hunyuanvideo</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025-03-03T17:32:45Z</t>
+          <t>2024-12-11T01:55:53Z</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-01-28T09:41:31Z</t>
+          <t>2026-01-19T16:49:14Z</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-01-14T23:51:12Z</t>
+          <t>2025-12-02T20:58:56Z</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>deepbeepmeep/Wan2GP</t>
+          <t>deepbeepmeep/HunyuanVideoGP</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/deepbeepmeep/Wan2GP</t>
+          <t>https://github.com/deepbeepmeep/HunyuanVideoGP</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2025-02-27T23:52:36Z</t>
+          <t>2024-12-10T18:34:42Z</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-02-01T06:34:39Z</t>
+          <t>2026-01-21T10:14:46Z</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>639</v>
+        <v>13</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>yue</t>
+          <t>wan</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/yue</t>
+          <t>https://github.com/pinokiofactory/wan</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025-01-29T11:22:39Z</t>
+          <t>2025-03-03T17:32:45Z</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2025-12-02T21:56:08Z</t>
+          <t>2026-02-06T10:13:26Z</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2025-12-02T21:56:04Z</t>
+          <t>2026-02-05T15:37:53Z</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>deepbeepmeep/YuEGP</t>
+          <t>deepbeepmeep/Wan2GP</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/deepbeepmeep/YuEGP</t>
+          <t>https://github.com/deepbeepmeep/Wan2GP</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2025-01-28T07:23:51Z</t>
+          <t>2025-02-27T23:52:36Z</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2025-12-06T23:11:18Z</t>
+          <t>2026-02-08T04:17:57Z</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>21</v>
+        <v>665</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>janus</t>
+          <t>yue</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/janus</t>
+          <t>https://github.com/pinokiofactory/yue</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025-01-27T18:23:47Z</t>
+          <t>2025-01-29T11:22:39Z</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2025-01-28T02:37:49Z</t>
+          <t>2025-12-02T21:56:08Z</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2025-01-28T02:37:46Z</t>
+          <t>2025-12-02T21:56:04Z</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>deepseek-ai/Janus</t>
+          <t>deepbeepmeep/YuEGP</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/deepseek-ai/Janus</t>
+          <t>https://github.com/deepbeepmeep/YuEGP</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2024-10-18T03:48:16Z</t>
+          <t>2025-01-28T07:23:51Z</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2025-11-15T15:45:09Z</t>
+          <t>2025-12-06T23:11:18Z</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>177</v>
+        <v>21</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>diamond</t>
+          <t>janus</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/diamond</t>
+          <t>https://github.com/pinokiofactory/janus</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2024-10-12T15:37:19Z</t>
+          <t>2025-01-27T18:23:47Z</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-01-24T06:17:09Z</t>
+          <t>2025-01-28T02:37:49Z</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2025-12-02T23:46:49Z</t>
+          <t>2025-01-28T02:37:46Z</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -3878,678 +3864,678 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>eloialonso/diamond</t>
+          <t>deepseek-ai/Janus</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/eloialonso/diamond</t>
+          <t>https://github.com/deepseek-ai/Janus</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2024-05-19T22:31:40Z</t>
+          <t>2024-10-18T03:48:16Z</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-01-23T09:30:32Z</t>
+          <t>2025-11-15T15:45:09Z</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>6</v>
+        <v>177</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>AllTalk-TTS</t>
+          <t>diamond</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/AllTalk-TTS</t>
+          <t>https://github.com/pinokiofactory/diamond</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025-02-05T16:24:30Z</t>
+          <t>2024-10-12T15:37:19Z</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2025-04-05T16:19:34Z</t>
+          <t>2026-01-24T06:17:09Z</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2025-03-29T16:44:51Z</t>
+          <t>2025-12-02T23:46:49Z</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>erew123/alltalk_tts</t>
+          <t>eloialonso/diamond</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/erew123/alltalk_tts</t>
+          <t>https://github.com/eloialonso/diamond</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2023-12-08T09:35:19Z</t>
+          <t>2024-05-19T22:31:40Z</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2025-11-15T23:50:46Z</t>
+          <t>2026-01-23T09:30:32Z</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>71</v>
+        <v>6</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>oasis</t>
+          <t>AllTalk-TTS</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/oasis</t>
+          <t>https://github.com/pinokiofactory/AllTalk-TTS</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2024-10-31T23:24:32Z</t>
+          <t>2025-02-05T16:24:30Z</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2024-10-31T23:47:38Z</t>
+          <t>2025-04-05T16:19:34Z</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2024-10-31T23:47:35Z</t>
+          <t>2025-03-29T16:44:51Z</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>etched-ai/open-oasis</t>
+          <t>erew123/alltalk_tts</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/etched-ai/open-oasis</t>
+          <t>https://github.com/erew123/alltalk_tts</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2024-10-31T09:10:45Z</t>
+          <t>2023-12-08T09:35:19Z</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2025-11-14T05:41:47Z</t>
+          <t>2025-11-15T23:50:46Z</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>30</v>
+        <v>71</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>openaudio</t>
+          <t>oasis</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/openaudio</t>
+          <t>https://github.com/pinokiofactory/oasis</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2024-11-02T08:47:31Z</t>
+          <t>2024-10-31T23:24:32Z</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-01-30T21:11:00Z</t>
+          <t>2024-10-31T23:47:38Z</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-01-30T21:10:56Z</t>
+          <t>2024-10-31T23:47:35Z</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>fishaudio/fish-speech</t>
+          <t>etched-ai/open-oasis</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/fishaudio/fish-speech</t>
+          <t>https://github.com/etched-ai/open-oasis</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2023-10-10T03:16:51Z</t>
+          <t>2024-10-31T09:10:45Z</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-02-01T01:25:30Z</t>
+          <t>2025-11-14T05:41:47Z</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>mochi</t>
+          <t>openaudio</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/mochi</t>
+          <t>https://github.com/pinokiofactory/openaudio</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2024-10-23T18:51:07Z</t>
+          <t>2024-11-02T08:47:31Z</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2024-10-29T03:03:08Z</t>
+          <t>2026-01-30T21:11:00Z</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2024-10-29T03:03:04Z</t>
+          <t>2026-01-30T21:10:56Z</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>genmoai/mochi</t>
+          <t>fishaudio/fish-speech</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/genmoai/mochi</t>
+          <t>https://github.com/fishaudio/fish-speech</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2024-09-11T02:55:33Z</t>
+          <t>2023-10-10T03:16:51Z</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2025-11-15T23:14:45Z</t>
+          <t>2026-02-01T01:25:30Z</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>58</v>
+        <v>19</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>instantir</t>
+          <t>mochi</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/instantir</t>
+          <t>https://github.com/pinokiofactory/mochi</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2024-11-08T08:05:55Z</t>
+          <t>2024-10-23T18:51:07Z</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2025-12-02T22:52:18Z</t>
+          <t>2024-10-29T03:03:08Z</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2025-12-02T22:52:15Z</t>
+          <t>2024-10-29T03:03:04Z</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>instantX-research/InstantIR</t>
+          <t>genmoai/mochi</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/instantX-research/InstantIR</t>
+          <t>https://github.com/genmoai/mochi</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2024-10-20T03:17:01Z</t>
+          <t>2024-09-11T02:55:33Z</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2025-11-26T08:31:35Z</t>
+          <t>2025-11-15T23:14:45Z</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>8</v>
+        <v>58</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>whisper-webui</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Pinokio Installer for Whisper-Webui</t>
-        </is>
-      </c>
+          <t>instantir</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/whisper-webui</t>
+          <t>https://github.com/pinokiofactory/instantir</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2024-09-21T20:42:20Z</t>
+          <t>2024-11-08T08:05:55Z</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-01-20T23:36:49Z</t>
+          <t>2025-12-02T22:52:18Z</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-01-09T00:52:01Z</t>
+          <t>2025-12-02T22:52:15Z</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>jhj0517/Whisper-WebUI</t>
+          <t>instantX-research/InstantIR</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/jhj0517/Whisper-WebUI</t>
+          <t>https://github.com/instantX-research/InstantIR</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>2023-03-02T13:42:01Z</t>
+          <t>2024-10-20T03:17:01Z</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-01-24T00:59:46Z</t>
+          <t>2025-11-26T08:31:35Z</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>136</v>
+        <v>8</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>pyramidflow</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr"/>
+          <t>whisper-webui</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Pinokio Installer for Whisper-Webui</t>
+        </is>
+      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/pyramidflow</t>
+          <t>https://github.com/pinokiofactory/whisper-webui</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2024-11-16T08:35:22Z</t>
+          <t>2024-09-21T20:42:20Z</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2025-12-04T18:28:05Z</t>
+          <t>2026-01-20T23:36:49Z</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2025-12-04T18:28:01Z</t>
+          <t>2026-01-09T00:52:01Z</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>jy0205/Pyramid-Flow</t>
+          <t>jhj0517/Whisper-WebUI</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/jy0205/Pyramid-Flow</t>
+          <t>https://github.com/jhj0517/Whisper-WebUI</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>2024-10-06T13:06:31Z</t>
+          <t>2023-03-02T13:42:01Z</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2025-12-06T20:01:25Z</t>
+          <t>2026-01-24T00:59:46Z</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>71</v>
+        <v>136</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Frame-Pack</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>(NVIDIA) FramePack is a next-frame (next-frame-section) prediction neural network structure that generates videos progressively.</t>
-        </is>
-      </c>
+          <t>pyramidflow</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/Frame-Pack</t>
+          <t>https://github.com/pinokiofactory/pyramidflow</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025-04-17T11:43:03Z</t>
+          <t>2024-11-16T08:35:22Z</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2025-12-18T10:04:25Z</t>
+          <t>2025-12-04T18:28:05Z</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2025-12-18T10:04:19Z</t>
+          <t>2025-12-04T18:28:01Z</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>lllyasviel/FramePack</t>
+          <t>jy0205/Pyramid-Flow</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/lllyasviel/FramePack</t>
+          <t>https://github.com/jy0205/Pyramid-Flow</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>2025-04-12T14:45:22Z</t>
+          <t>2024-10-06T13:06:31Z</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2025-12-20T22:41:55Z</t>
+          <t>2025-12-06T20:01:25Z</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>472</v>
+        <v>71</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>stable-diffusion-webui-forge</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr"/>
+          <t>Frame-Pack</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>(NVIDIA) FramePack is a next-frame (next-frame-section) prediction neural network structure that generates videos progressively.</t>
+        </is>
+      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/stable-diffusion-webui-forge</t>
+          <t>https://github.com/pinokiofactory/Frame-Pack</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2024-08-12T12:38:49Z</t>
+          <t>2025-04-17T11:43:03Z</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-01-07T01:28:48Z</t>
+          <t>2026-02-07T10:08:40Z</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-01-07T01:28:45Z</t>
+          <t>2025-12-18T10:04:19Z</t>
         </is>
       </c>
       <c r="G88" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>lllyasviel/stable-diffusion-webui-forge</t>
+          <t>lllyasviel/FramePack</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/lllyasviel/stable-diffusion-webui-forge</t>
+          <t>https://github.com/lllyasviel/FramePack</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>2024-01-14T11:39:30Z</t>
+          <t>2025-04-12T14:45:22Z</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-01-11T03:02:46Z</t>
+          <t>2026-02-08T06:42:47Z</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1126</v>
+        <v>474</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>omniparser</t>
+          <t>stable-diffusion-webui-forge</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/omniparser</t>
+          <t>https://github.com/pinokiofactory/stable-diffusion-webui-forge</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2024-10-26T06:04:17Z</t>
+          <t>2024-08-12T12:38:49Z</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2024-10-28T04:49:07Z</t>
+          <t>2026-01-07T01:28:48Z</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2024-10-26T08:03:10Z</t>
+          <t>2026-01-07T01:28:45Z</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>microsoft/OmniParser</t>
+          <t>lllyasviel/stable-diffusion-webui-forge</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/microsoft/OmniParser</t>
+          <t>https://github.com/lllyasviel/stable-diffusion-webui-forge</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>2024-09-20T05:18:18Z</t>
+          <t>2024-01-14T11:39:30Z</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2025-11-16T06:25:49Z</t>
+          <t>2026-01-11T03:02:46Z</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>225</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>vibevoice-realtime</t>
+          <t>omniparser</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/vibevoice-realtime</t>
+          <t>https://github.com/pinokiofactory/omniparser</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025-12-04T21:57:09Z</t>
+          <t>2024-10-26T06:04:17Z</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-02-01T06:38:32Z</t>
+          <t>2024-10-28T04:49:07Z</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2025-12-22T22:00:09Z</t>
+          <t>2024-10-26T08:03:10Z</t>
         </is>
       </c>
       <c r="G90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>microsoft/VibeVoice</t>
+          <t>microsoft/OmniParser</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/microsoft/VibeVoice</t>
+          <t>https://github.com/microsoft/OmniParser</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>2025-08-25T13:24:01Z</t>
+          <t>2024-09-20T05:18:18Z</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-02-01T06:53:32Z</t>
+          <t>2025-11-16T06:25:49Z</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>87</v>
+        <v>225</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>dia</t>
+          <t>vibevoice-realtime</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/dia</t>
+          <t>https://github.com/pinokiofactory/vibevoice-realtime</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025-04-22T14:57:53Z</t>
+          <t>2025-12-04T21:57:09Z</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2025-12-07T19:55:02Z</t>
+          <t>2026-02-01T06:38:32Z</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2025-12-07T19:54:59Z</t>
+          <t>2025-12-22T22:00:09Z</t>
         </is>
       </c>
       <c r="G91" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>nari-labs/dia</t>
+          <t>microsoft/VibeVoice</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/nari-labs/dia</t>
+          <t>https://github.com/microsoft/VibeVoice</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>2025-04-19T07:15:57Z</t>
+          <t>2025-08-25T13:24:01Z</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2025-12-14T04:00:35Z</t>
+          <t>2026-02-01T06:53:32Z</t>
         </is>
       </c>
       <c r="L91" t="n">
@@ -4559,152 +4545,148 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>clarity-refiners-ui</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Creative Image Enhancer/Upscaler. Powered By Refiners.  8GB VRAM | 10GB Install</t>
-        </is>
-      </c>
+          <t>dia</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/clarity-refiners-ui</t>
+          <t>https://github.com/pinokiofactory/dia</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2024-11-12T07:03:48Z</t>
+          <t>2025-04-22T14:57:53Z</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-01-02T20:07:27Z</t>
+          <t>2025-12-07T19:55:02Z</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2025-12-02T22:18:28Z</t>
+          <t>2025-12-07T19:54:59Z</t>
         </is>
       </c>
       <c r="G92" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>philz1337x/clarity-upscaler</t>
+          <t>nari-labs/dia</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/philz1337x/clarity-upscaler</t>
+          <t>https://github.com/nari-labs/dia</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>2024-03-15T15:21:40Z</t>
+          <t>2025-04-19T07:15:57Z</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-01-03T09:04:39Z</t>
+          <t>2025-12-14T04:00:35Z</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>18</v>
+        <v>87</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Allegro-txt2vid</t>
+          <t>clarity-refiners-ui</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Allegro is a powerful text-to-video model that generates high-quality videos up to 6 seconds at 15 FPS and 720p resolution from simple text input.</t>
+          <t>Creative Image Enhancer/Upscaler. Powered By Refiners.  8GB VRAM | 10GB Install</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/Allegro-txt2vid</t>
+          <t>https://github.com/pinokiofactory/clarity-refiners-ui</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2024-10-25T06:33:03Z</t>
+          <t>2024-11-12T07:03:48Z</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2024-11-05T23:56:50Z</t>
+          <t>2026-01-02T20:07:27Z</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2024-11-05T23:56:47Z</t>
+          <t>2025-12-02T22:18:28Z</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>rhymes-ai/Allegro</t>
+          <t>philz1337x/clarity-upscaler</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/rhymes-ai/Allegro</t>
+          <t>https://github.com/philz1337x/clarity-upscaler</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>2024-10-16T04:04:15Z</t>
+          <t>2024-03-15T15:21:40Z</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2025-11-07T08:32:13Z</t>
+          <t>2026-01-03T09:04:39Z</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Allegro-txt2vid-install</t>
+          <t>Allegro-txt2vid</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Allegro-txt2vid. WARNING: takes a long time to generate a result, 1hr on a 3090. 12GB+ VRAM | 32GB+ RAM | 30GB Download. Check the README for details</t>
+          <t>Allegro is a powerful text-to-video model that generates high-quality videos up to 6 seconds at 15 FPS and 720p resolution from simple text input.</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/Allegro-txt2vid-install</t>
+          <t>https://github.com/pinokiofactory/Allegro-txt2vid</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2024-10-27T14:58:05Z</t>
+          <t>2024-10-25T06:33:03Z</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2025-12-04T05:36:24Z</t>
+          <t>2024-11-05T23:56:50Z</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2025-12-04T05:36:20Z</t>
+          <t>2024-11-05T23:56:47Z</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -4723,7 +4705,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2025-12-06T00:53:45Z</t>
+          <t>2025-11-07T08:32:13Z</t>
         </is>
       </c>
       <c r="L94" t="n">
@@ -4733,32 +4715,32 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>RuinedFooocus</t>
+          <t>Allegro-txt2vid-install</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t xml:space="preserve">(NVIDIA ONLY) Forget everything you thought you knew about AI art generation - RuinedFooocus is here to completely reinvent the game! This groundbreaking image creator combines the best aspects of Stable Diffusion and Midjourney into one seamless, cutting-edge experience. </t>
+          <t>Allegro-txt2vid. WARNING: takes a long time to generate a result, 1hr on a 3090. 12GB+ VRAM | 32GB+ RAM | 30GB Download. Check the README for details</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/RuinedFooocus</t>
+          <t>https://github.com/pinokiofactory/Allegro-txt2vid-install</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025-04-22T14:09:26Z</t>
+          <t>2024-10-27T14:58:05Z</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2025-10-30T19:53:32Z</t>
+          <t>2025-12-04T05:36:24Z</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2025-10-30T19:53:29Z</t>
+          <t>2025-12-04T05:36:20Z</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -4766,241 +4748,299 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>runew0lf/RuinedFooocus</t>
+          <t>rhymes-ai/Allegro</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/runew0lf/RuinedFooocus</t>
+          <t>https://github.com/rhymes-ai/Allegro</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>2023-08-16T09:20:46Z</t>
+          <t>2024-10-16T04:04:15Z</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>2025-11-15T08:55:10Z</t>
+          <t>2025-12-06T00:53:45Z</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>bolt</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr"/>
+          <t>RuinedFooocus</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(NVIDIA ONLY) Forget everything you thought you knew about AI art generation - RuinedFooocus is here to completely reinvent the game! This groundbreaking image creator combines the best aspects of Stable Diffusion and Midjourney into one seamless, cutting-edge experience. </t>
+        </is>
+      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/bolt</t>
+          <t>https://github.com/pinokiofactory/RuinedFooocus</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2024-10-30T04:46:10Z</t>
+          <t>2025-04-22T14:09:26Z</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-01-11T08:23:24Z</t>
+          <t>2025-10-30T19:53:32Z</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2025-12-06T21:59:33Z</t>
+          <t>2025-10-30T19:53:29Z</t>
         </is>
       </c>
       <c r="G96" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>stackblitz-labs/bolt.diy</t>
+          <t>runew0lf/RuinedFooocus</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/stackblitz-labs/bolt.diy</t>
+          <t>https://github.com/runew0lf/RuinedFooocus</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>2024-10-13T18:40:54Z</t>
+          <t>2023-08-16T09:20:46Z</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2026-01-18T05:04:40Z</t>
+          <t>2025-11-15T08:55:10Z</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>81</v>
+        <v>23</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ditto</t>
+          <t>bolt</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/ditto</t>
+          <t>https://github.com/pinokiofactory/bolt</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2024-10-15T21:29:32Z</t>
+          <t>2024-10-30T04:46:10Z</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2025-11-06T00:05:04Z</t>
+          <t>2026-01-11T08:23:24Z</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2024-10-15T22:47:07Z</t>
+          <t>2025-12-06T21:59:33Z</t>
         </is>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>yoheinakajima/ditto</t>
+          <t>stackblitz-labs/bolt.diy</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/yoheinakajima/ditto</t>
+          <t>https://github.com/stackblitz-labs/bolt.diy</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>2024-10-15T19:45:13Z</t>
+          <t>2024-10-13T18:40:54Z</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2025-11-11T07:07:11Z</t>
+          <t>2026-01-18T05:04:40Z</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>8</v>
+        <v>81</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>cogstudio</t>
+          <t>ditto</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/cogstudio</t>
+          <t>https://github.com/pinokiofactory/ditto</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2024-09-20T10:46:17Z</t>
+          <t>2024-10-15T21:29:32Z</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-01-29T08:58:01Z</t>
+          <t>2025-11-06T00:05:04Z</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-01-04T00:47:22Z</t>
+          <t>2024-10-15T22:47:07Z</t>
         </is>
       </c>
       <c r="G98" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>zai-org/CogVideo</t>
+          <t>yoheinakajima/ditto</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/zai-org/CogVideo</t>
+          <t>https://github.com/yoheinakajima/ditto</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>2022-05-29T06:46:18Z</t>
+          <t>2024-10-15T19:45:13Z</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2026-01-31T14:40:21Z</t>
+          <t>2025-11-11T07:07:11Z</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>106</v>
+        <v>8</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>cogvideo</t>
+          <t>cogstudio</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" s="2" t="inlineStr">
         <is>
+          <t>https://github.com/pinokiofactory/cogstudio</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2024-09-20T10:46:17Z</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>2026-01-29T08:58:01Z</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-01-04T00:47:22Z</t>
+        </is>
+      </c>
+      <c r="G99" t="n">
+        <v>37</v>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>zai-org/CogVideo</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/zai-org/CogVideo</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>2022-05-29T06:46:18Z</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>2026-01-31T14:40:21Z</t>
+        </is>
+      </c>
+      <c r="L99" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>cogvideo</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
           <t>https://github.com/pinokiofactory/cogvideo</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
+      <c r="D100" t="inlineStr">
         <is>
           <t>2024-08-30T10:13:02Z</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
+      <c r="E100" t="inlineStr">
         <is>
           <t>2026-01-04T01:51:05Z</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
+      <c r="F100" t="inlineStr">
         <is>
           <t>2026-01-04T01:51:01Z</t>
         </is>
       </c>
-      <c r="G99" t="n">
+      <c r="G100" t="n">
         <v>1</v>
       </c>
-      <c r="H99" t="inlineStr">
+      <c r="H100" t="inlineStr">
         <is>
           <t>zai-org/CogVideo</t>
         </is>
       </c>
-      <c r="I99" s="2" t="inlineStr">
+      <c r="I100" s="2" t="inlineStr">
         <is>
           <t>https://github.com/zai-org/CogVideo</t>
         </is>
       </c>
-      <c r="J99" t="inlineStr">
+      <c r="J100" t="inlineStr">
         <is>
           <t>2022-05-29T06:46:18Z</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
+      <c r="K100" t="inlineStr">
         <is>
           <t>2026-01-04T04:24:11Z</t>
         </is>
       </c>
-      <c r="L99" t="n">
+      <c r="L100" t="n">
         <v>105</v>
       </c>
     </row>
@@ -5056,103 +5096,104 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C49" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C52" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C53" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C54" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C56" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C58" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C59" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C60" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C61" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C62" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C63" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C64" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C65" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C66" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C67" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C68" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C69" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C70" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C71" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C72" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C73" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C74" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C75" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C76" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C77" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C78" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C79" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C80" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I80" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C81" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C82" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C83" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I83" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C84" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C85" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C86" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I86" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C87" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I87" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C88" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C89" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I89" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C90" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I90" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C91" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C92" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I92" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C93" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I93" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C94" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I94" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C95" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I95" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C96" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I96" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C97" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I97" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C98" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I98" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C99" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I99" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C53" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C54" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C56" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C58" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C59" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C60" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C61" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C62" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C63" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C64" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C65" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C66" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C67" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C68" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C69" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C70" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C71" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C72" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C73" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C74" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C75" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C76" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C77" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C78" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C79" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C80" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I80" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C81" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C82" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C83" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I83" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C84" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C85" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C86" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I86" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C87" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I87" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C88" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C89" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I89" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C90" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I90" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C91" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C92" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I92" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C93" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I93" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C94" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I94" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C95" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I95" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C96" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I96" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C97" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I97" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C98" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I98" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C99" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I99" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C100" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I100" r:id="rId148"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pinokio_repos.xlsx
+++ b/pinokio_repos.xlsx
@@ -1277,7 +1277,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-02-03T09:04:11Z</t>
+          <t>2026-02-11T13:58:38Z</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1785,12 +1785,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-02-08T00:09:41Z</t>
+          <t>2026-02-14T00:58:46Z</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-02-08T00:09:37Z</t>
+          <t>2026-02-14T00:58:43Z</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2025-12-30T00:17:54Z</t>
+          <t>2026-02-10T21:43:55Z</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2527,16 +2527,16 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-01-14T11:37:40Z</t>
+          <t>2026-02-14T19:28:17Z</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2025-12-02T21:35:15Z</t>
+          <t>2026-02-14T19:28:13Z</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -2555,11 +2555,11 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-01-18T06:40:45Z</t>
+          <t>2026-02-15T06:44:49Z</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>3530</v>
+        <v>3704</v>
       </c>
     </row>
     <row r="56">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-01-06T18:02:20Z</t>
+          <t>2026-02-15T02:31:25Z</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3219,11 +3219,11 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-01-11T03:52:31Z</t>
+          <t>2026-02-14T03:12:03Z</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
     </row>
     <row r="68">
@@ -3743,16 +3743,16 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-02-06T10:13:26Z</t>
+          <t>2026-02-13T18:32:49Z</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-02-05T15:37:53Z</t>
+          <t>2026-02-13T18:32:45Z</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -3771,11 +3771,11 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-02-08T04:17:57Z</t>
+          <t>2026-02-15T00:03:27Z</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>665</v>
+        <v>670</v>
       </c>
     </row>
     <row r="78">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2025-12-02T21:56:08Z</t>
+          <t>2026-02-11T18:06:59Z</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2025-12-06T23:11:18Z</t>
+          <t>2026-02-07T07:04:54Z</t>
         </is>
       </c>
       <c r="L78" t="n">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-02-07T10:08:40Z</t>
+          <t>2026-02-12T07:58:31Z</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -4354,7 +4354,7 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -4373,7 +4373,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-02-08T06:42:47Z</t>
+          <t>2026-02-15T02:39:47Z</t>
         </is>
       </c>
       <c r="L88" t="n">
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-01-07T01:28:48Z</t>
+          <t>2026-02-10T03:05:59Z</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-01-07T01:28:45Z</t>
+          <t>2026-02-10T03:05:55Z</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -4427,11 +4427,11 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-01-11T03:02:46Z</t>
+          <t>2026-02-15T02:28:41Z</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1126</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="90">
@@ -4955,7 +4955,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-01-29T08:58:01Z</t>
+          <t>2026-02-13T05:24:32Z</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -4983,11 +4983,11 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2026-01-31T14:40:21Z</t>
+          <t>2026-02-15T04:56:01Z</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="100">

--- a/pinokio_repos.xlsx
+++ b/pinokio_repos.xlsx
@@ -1277,7 +1277,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-02-11T13:58:38Z</t>
+          <t>2026-02-19T02:16:33Z</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2527,12 +2527,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-02-14T19:28:17Z</t>
+          <t>2026-02-20T19:45:36Z</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-02-14T19:28:13Z</t>
+          <t>2026-02-20T19:45:32Z</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -2555,11 +2555,11 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-02-15T06:44:49Z</t>
+          <t>2026-02-22T06:49:05Z</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>3704</v>
+        <v>3722</v>
       </c>
     </row>
     <row r="56">
@@ -2747,7 +2747,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-01-24T23:02:12Z</t>
+          <t>2026-02-20T16:26:14Z</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2775,11 +2775,11 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-01-24T18:58:41Z</t>
+          <t>2026-02-21T14:02:05Z</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="60">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-01-09T05:42:44Z</t>
+          <t>2026-02-15T23:03:28Z</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-01-10T13:59:01Z</t>
+          <t>2026-02-19T16:27:53Z</t>
         </is>
       </c>
       <c r="L60" t="n">
@@ -2913,16 +2913,16 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-02-08T01:00:40Z</t>
+          <t>2026-02-18T00:45:14Z</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-01-30T00:41:17Z</t>
+          <t>2026-02-18T00:45:10Z</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -2941,11 +2941,11 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-02-08T01:00:48Z</t>
+          <t>2026-02-16T16:32:31Z</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="63">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-02-13T18:32:49Z</t>
+          <t>2026-02-20T18:00:27Z</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-02-13T18:32:45Z</t>
+          <t>2026-02-20T18:00:24Z</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -3771,11 +3771,11 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-02-15T00:03:27Z</t>
+          <t>2026-02-22T05:00:48Z</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>670</v>
+        <v>677</v>
       </c>
     </row>
     <row r="78">
@@ -4399,7 +4399,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-02-10T03:05:59Z</t>
+          <t>2026-02-20T18:30:12Z</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -4427,11 +4427,11 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-02-15T02:28:41Z</t>
+          <t>2026-02-22T02:25:46Z</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1125</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="90">
@@ -4955,7 +4955,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-02-13T05:24:32Z</t>
+          <t>2026-02-18T16:48:06Z</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -4983,11 +4983,11 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2026-02-15T04:56:01Z</t>
+          <t>2026-02-21T19:46:09Z</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="100">

--- a/pinokio_repos.xlsx
+++ b/pinokio_repos.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-01-24T16:44:46Z</t>
+          <t>2026-02-26T21:19:42Z</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-02-19T02:16:33Z</t>
+          <t>2026-02-28T17:33:00Z</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-02-10T21:43:55Z</t>
+          <t>2026-02-26T20:36:40Z</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2025-03-17T00:31:10Z</t>
+          <t>2026-02-26T20:36:35Z</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-02-20T19:45:36Z</t>
+          <t>2026-02-26T12:44:50Z</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2555,11 +2555,11 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-02-22T06:49:05Z</t>
+          <t>2026-03-01T06:49:49Z</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>3722</v>
+        <v>3775</v>
       </c>
     </row>
     <row r="56">
@@ -2913,7 +2913,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-02-18T00:45:14Z</t>
+          <t>2026-02-23T15:45:46Z</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2941,11 +2941,11 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-02-16T16:32:31Z</t>
+          <t>2026-02-28T14:20:01Z</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="63">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-02-15T02:31:25Z</t>
+          <t>2026-02-26T00:56:36Z</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3219,11 +3219,11 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-02-14T03:12:03Z</t>
+          <t>2026-03-01T06:41:47Z</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="68">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-02-20T18:00:27Z</t>
+          <t>2026-03-01T00:31:25Z</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3771,11 +3771,11 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-02-22T05:00:48Z</t>
+          <t>2026-03-01T03:56:08Z</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>677</v>
+        <v>673</v>
       </c>
     </row>
     <row r="78">

--- a/pinokio_repos.xlsx
+++ b/pinokio_repos.xlsx
@@ -1205,7 +1205,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2025-12-03T13:16:26Z</t>
+          <t>2026-03-01T17:52:15Z</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-02-04T06:30:37Z</t>
+          <t>2026-03-07T20:08:42Z</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-02-26T12:44:50Z</t>
+          <t>2026-03-06T10:06:31Z</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2555,11 +2555,11 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-03-01T06:49:49Z</t>
+          <t>2026-03-08T06:53:48Z</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>3775</v>
+        <v>3796</v>
       </c>
     </row>
     <row r="56">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-02-26T00:56:36Z</t>
+          <t>2026-03-07T21:28:47Z</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3219,11 +3219,11 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-03-01T06:41:47Z</t>
+          <t>2026-03-07T14:17:38Z</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="68">
@@ -3635,7 +3635,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-01-18T02:36:25Z</t>
+          <t>2026-03-04T05:39:26Z</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-01-18T03:01:59Z</t>
+          <t>2026-03-04T19:04:33Z</t>
         </is>
       </c>
       <c r="L75" t="n">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-03-01T00:31:25Z</t>
+          <t>2026-03-07T20:45:48Z</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3771,11 +3771,11 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-03-01T03:56:08Z</t>
+          <t>2026-03-08T03:57:04Z</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>673</v>
+        <v>686</v>
       </c>
     </row>
     <row r="78">
@@ -4847,7 +4847,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-01-11T08:23:24Z</t>
+          <t>2026-03-06T16:37:35Z</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -4875,11 +4875,11 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2026-01-18T05:04:40Z</t>
+          <t>2026-03-08T05:14:22Z</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>81</v>
+        <v>92</v>
       </c>
     </row>
     <row r="98">
@@ -4955,7 +4955,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-02-18T16:48:06Z</t>
+          <t>2026-03-01T16:13:28Z</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2026-02-21T19:46:09Z</t>
+          <t>2026-03-08T06:29:40Z</t>
         </is>
       </c>
       <c r="L99" t="n">

--- a/pinokio_repos.xlsx
+++ b/pinokio_repos.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L100"/>
+  <dimension ref="A1:L101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-01-08T19:42:15Z</t>
+          <t>2026-03-12T03:17:46Z</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -589,36 +589,36 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MFLUX-WEBUI</t>
+          <t>LTX-Desktop-WanGP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>A powerful and user-friendly web interface for MFLUX, powered by Gradio and MLX. https://github.com/CharafChnioune/MFLUX-WEBUI</t>
+          <t>[NVIDIA only] [Currently Windows only]  LTX-Desktop powered By WanGP itself powered among other things by LTX-2 Engine</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/MFLUX-WEBUI</t>
+          <t>https://github.com/pinokiofactory/LTX-Desktop-WanGP</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2024-09-29T11:23:11Z</t>
+          <t>2026-03-11T06:56:54Z</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-01-18T13:15:57Z</t>
+          <t>2026-03-12T02:15:07Z</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-01-18T13:15:52Z</t>
+          <t>2026-03-12T02:15:04Z</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
@@ -629,32 +629,36 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MMAudio</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
+          <t>MFLUX-WEBUI</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>A powerful and user-friendly web interface for MFLUX, powered by Gradio and MLX. https://github.com/CharafChnioune/MFLUX-WEBUI</t>
+        </is>
+      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/MMAudio</t>
+          <t>https://github.com/pinokiofactory/MFLUX-WEBUI</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2024-12-15T04:45:43Z</t>
+          <t>2024-09-29T11:23:11Z</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2025-12-02T22:00:13Z</t>
+          <t>2026-01-18T13:15:57Z</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2025-12-02T22:00:10Z</t>
+          <t>2026-01-18T13:15:52Z</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
@@ -665,32 +669,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MatAnyone</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>[NVIDIA ONLY] "Stable Video Matting with Consistent Memory Propagation"   9GB install, 9GB+ VRAM</t>
-        </is>
-      </c>
+          <t>MMAudio</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/MatAnyone</t>
+          <t>https://github.com/pinokiofactory/MMAudio</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-02-21T04:25:40Z</t>
+          <t>2024-12-15T04:45:43Z</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2025-12-02T21:43:31Z</t>
+          <t>2025-12-02T22:00:13Z</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2025-12-02T21:43:28Z</t>
+          <t>2025-12-02T22:00:10Z</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -705,32 +705,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Nari-Dia-TTS</t>
+          <t>MatAnyone</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Nari Dia is a powerful text-to-speech (TTS) application based on the Dia-1.6B model from Nari Labs. This application allows you to convert text into natural-sounding speech with various customization options.</t>
+          <t>[NVIDIA ONLY] "Stable Video Matting with Consistent Memory Propagation"   9GB install, 9GB+ VRAM</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/Nari-Dia-TTS</t>
+          <t>https://github.com/pinokiofactory/MatAnyone</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-04-22T11:51:10Z</t>
+          <t>2025-02-21T04:25:40Z</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-02-26T21:19:42Z</t>
+          <t>2025-12-02T21:43:31Z</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2025-04-22T12:03:27Z</t>
+          <t>2025-12-02T21:43:28Z</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -745,32 +745,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>StreamDiffusion</t>
+          <t>Nari-Dia-TTS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>StreamDiffusion: A Pipeline-Level Solution for Real-Time Interactive Generation</t>
+          <t>Nari Dia is a powerful text-to-speech (TTS) application based on the Dia-1.6B model from Nari Labs. This application allows you to convert text into natural-sounding speech with various customization options.</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/StreamDiffusion</t>
+          <t>https://github.com/pinokiofactory/Nari-Dia-TTS</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2024-11-06T22:32:16Z</t>
+          <t>2025-04-22T11:51:10Z</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2025-03-23T00:07:51Z</t>
+          <t>2026-03-09T19:03:04Z</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2025-03-23T00:07:47Z</t>
+          <t>2025-04-22T12:03:27Z</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -785,32 +785,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>StyleTTS2_Studio</t>
+          <t>StreamDiffusion</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Build your own StyleTTS 2 Voice!</t>
+          <t>StreamDiffusion: A Pipeline-Level Solution for Real-Time Interactive Generation</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/StyleTTS2_Studio</t>
+          <t>https://github.com/pinokiofactory/StreamDiffusion</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2024-12-25T23:02:32Z</t>
+          <t>2024-11-06T22:32:16Z</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-01-04T05:07:11Z</t>
+          <t>2026-03-12T03:42:33Z</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2025-12-02T21:58:14Z</t>
+          <t>2025-03-23T00:07:47Z</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -825,36 +825,36 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TRELLIS</t>
+          <t>StyleTTS2_Studio</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A pinokio script for https://github.com/microsoft/TRELLIS</t>
+          <t>Build your own StyleTTS 2 Voice!</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/TRELLIS</t>
+          <t>https://github.com/pinokiofactory/StyleTTS2_Studio</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2024-12-08T13:33:11Z</t>
+          <t>2024-12-25T23:02:32Z</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2025-10-06T09:31:47Z</t>
+          <t>2026-01-04T05:07:11Z</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2025-06-08T06:02:31Z</t>
+          <t>2025-12-02T21:58:14Z</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
@@ -865,32 +865,36 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>accdiffusion</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
+          <t>TRELLIS</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A pinokio script for https://github.com/microsoft/TRELLIS</t>
+        </is>
+      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/accdiffusion</t>
+          <t>https://github.com/pinokiofactory/TRELLIS</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2024-07-31T15:54:10Z</t>
+          <t>2024-12-08T13:33:11Z</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024-07-31T15:55:00Z</t>
+          <t>2025-10-06T09:31:47Z</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2024-07-31T15:54:56Z</t>
+          <t>2025-06-08T06:02:31Z</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
@@ -901,32 +905,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ai-video-composer</t>
+          <t>accdiffusion</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/ai-video-composer</t>
+          <t>https://github.com/pinokiofactory/accdiffusion</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2024-11-26T00:57:07Z</t>
+          <t>2024-07-31T15:54:10Z</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-01-09T05:42:47Z</t>
+          <t>2024-07-31T15:55:00Z</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2025-12-02T22:14:35Z</t>
+          <t>2024-07-31T15:54:56Z</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
@@ -937,32 +941,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>applio-old</t>
+          <t>ai-video-composer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/applio-old</t>
+          <t>https://github.com/pinokiofactory/ai-video-composer</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2024-06-17T22:35:00Z</t>
+          <t>2024-11-26T00:57:07Z</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024-09-12T13:25:42Z</t>
+          <t>2026-01-09T05:42:47Z</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2024-06-24T21:39:45Z</t>
+          <t>2025-12-02T22:14:35Z</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
@@ -973,32 +977,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>artist</t>
+          <t>applio-old</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/artist</t>
+          <t>https://github.com/pinokiofactory/applio-old</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2024-07-30T14:02:34Z</t>
+          <t>2024-06-17T22:35:00Z</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2025-04-23T21:33:35Z</t>
+          <t>2024-09-12T13:25:42Z</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2025-04-23T21:33:31Z</t>
+          <t>2024-06-24T21:39:45Z</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
@@ -1009,28 +1013,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>augmentoolkit</t>
+          <t>artist</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/augmentoolkit</t>
+          <t>https://github.com/pinokiofactory/artist</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2024-05-16T12:39:35Z</t>
+          <t>2024-07-30T14:02:34Z</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024-10-19T17:14:02Z</t>
+          <t>2025-04-23T21:33:35Z</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2024-08-15T01:13:13Z</t>
+          <t>2025-04-23T21:33:31Z</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -1045,28 +1049,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>aura-sr-upscaler</t>
+          <t>augmentoolkit</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/aura-sr-upscaler</t>
+          <t>https://github.com/pinokiofactory/augmentoolkit</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2024-07-31T12:18:57Z</t>
+          <t>2024-05-16T12:39:35Z</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-01-13T16:59:17Z</t>
+          <t>2024-10-19T17:14:02Z</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-01-13T16:59:11Z</t>
+          <t>2024-08-15T01:13:13Z</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -1081,32 +1085,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>autogpt</t>
+          <t>aura-sr-upscaler</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/autogpt</t>
+          <t>https://github.com/pinokiofactory/aura-sr-upscaler</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2024-07-19T14:00:12Z</t>
+          <t>2024-07-31T12:18:57Z</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2025-12-15T20:38:43Z</t>
+          <t>2026-01-13T16:59:17Z</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2024-09-11T05:57:21Z</t>
+          <t>2026-01-13T16:59:11Z</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
@@ -1117,32 +1121,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>controlyourself</t>
+          <t>autogpt</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/controlyourself</t>
+          <t>https://github.com/pinokiofactory/autogpt</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2024-11-26T09:11:44Z</t>
+          <t>2024-07-19T14:00:12Z</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024-11-26T11:00:33Z</t>
+          <t>2026-03-10T07:04:46Z</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2024-11-26T11:00:30Z</t>
+          <t>2024-09-11T05:57:21Z</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
@@ -1153,32 +1157,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>diffrhythm</t>
+          <t>controlyourself</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/diffrhythm</t>
+          <t>https://github.com/pinokiofactory/controlyourself</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-03-04T22:13:30Z</t>
+          <t>2024-11-26T09:11:44Z</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-01-15T18:34:00Z</t>
+          <t>2024-11-26T11:00:33Z</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2025-12-05T01:50:29Z</t>
+          <t>2024-11-26T11:00:30Z</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
@@ -1189,32 +1193,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>diffusers-image-fill</t>
+          <t>diffrhythm</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/diffusers-image-fill</t>
+          <t>https://github.com/pinokiofactory/diffrhythm</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2024-09-27T17:14:28Z</t>
+          <t>2025-03-04T22:13:30Z</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-03-01T17:52:15Z</t>
+          <t>2026-01-15T18:34:00Z</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2025-04-15T20:43:01Z</t>
+          <t>2025-12-05T01:50:29Z</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
@@ -1225,32 +1229,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>dough</t>
+          <t>diffusers-image-fill</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/dough</t>
+          <t>https://github.com/pinokiofactory/diffusers-image-fill</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2024-07-18T11:39:16Z</t>
+          <t>2024-09-27T17:14:28Z</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024-07-19T12:30:00Z</t>
+          <t>2026-03-01T17:52:15Z</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2024-08-14T20:21:12Z</t>
+          <t>2025-04-15T20:43:01Z</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
@@ -1261,32 +1265,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>e2-f5-tts</t>
+          <t>dough</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/e2-f5-tts</t>
+          <t>https://github.com/pinokiofactory/dough</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2024-10-13T17:23:57Z</t>
+          <t>2024-07-18T11:39:16Z</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-02-28T17:33:00Z</t>
+          <t>2024-07-19T12:30:00Z</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2025-12-20T20:47:38Z</t>
+          <t>2024-08-14T20:21:12Z</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
@@ -1297,32 +1301,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>errortest</t>
+          <t>e2-f5-tts</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/errortest</t>
+          <t>https://github.com/pinokiofactory/e2-f5-tts</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2024-11-12T02:01:21Z</t>
+          <t>2024-10-13T17:23:57Z</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024-11-16T03:20:20Z</t>
+          <t>2026-02-28T17:33:00Z</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2024-11-16T03:20:16Z</t>
+          <t>2025-12-20T20:47:38Z</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
@@ -1333,32 +1337,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>facepoke</t>
+          <t>errortest</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/facepoke</t>
+          <t>https://github.com/pinokiofactory/errortest</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2024-10-07T13:28:53Z</t>
+          <t>2024-11-12T02:01:21Z</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2025-12-04T03:24:42Z</t>
+          <t>2024-11-16T03:20:20Z</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2025-12-04T03:24:37Z</t>
+          <t>2024-11-16T03:20:16Z</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
@@ -1369,32 +1373,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>factory</t>
+          <t>facepoke</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/factory</t>
+          <t>https://github.com/pinokiofactory/facepoke</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2024-08-27T21:49:02Z</t>
+          <t>2024-10-07T13:28:53Z</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024-08-27T21:49:02Z</t>
+          <t>2025-12-04T03:24:42Z</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2024-08-27T21:49:02Z</t>
+          <t>2025-12-04T03:24:37Z</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
@@ -1405,32 +1409,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>flashdiffusion</t>
+          <t>factory</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/flashdiffusion</t>
+          <t>https://github.com/pinokiofactory/factory</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2024-06-07T19:33:04Z</t>
+          <t>2024-08-27T21:49:02Z</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2025-03-17T00:27:35Z</t>
+          <t>2024-08-27T21:49:02Z</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2025-03-17T00:27:32Z</t>
+          <t>2024-08-27T21:49:02Z</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -1441,28 +1445,28 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>florence-sam</t>
+          <t>flashdiffusion</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/florence-sam</t>
+          <t>https://github.com/pinokiofactory/flashdiffusion</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2024-08-01T14:15:49Z</t>
+          <t>2024-06-07T19:33:04Z</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024-08-01T18:30:44Z</t>
+          <t>2026-03-10T07:04:34Z</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2024-08-01T18:30:41Z</t>
+          <t>2025-03-17T00:27:32Z</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -1477,28 +1481,28 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>florence2</t>
+          <t>florence-sam</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/florence2</t>
+          <t>https://github.com/pinokiofactory/florence-sam</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2024-06-20T21:16:01Z</t>
+          <t>2024-08-01T14:15:49Z</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2025-11-06T04:53:27Z</t>
+          <t>2024-08-01T18:30:44Z</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2025-11-06T04:53:23Z</t>
+          <t>2024-08-01T18:30:41Z</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -1513,32 +1517,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>flux-webui</t>
+          <t>florence2</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/flux-webui</t>
+          <t>https://github.com/pinokiofactory/florence2</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2024-08-07T15:22:56Z</t>
+          <t>2024-06-20T21:16:01Z</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-01-24T02:56:20Z</t>
+          <t>2025-11-06T04:53:27Z</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-01-06T14:59:02Z</t>
+          <t>2025-11-06T04:53:23Z</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
@@ -1549,32 +1553,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>forge</t>
+          <t>flux-webui</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/forge</t>
+          <t>https://github.com/pinokiofactory/flux-webui</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2024-05-11T09:24:03Z</t>
+          <t>2024-08-07T15:22:56Z</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024-08-16T22:18:57Z</t>
+          <t>2026-01-24T02:56:20Z</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2024-08-16T22:18:54Z</t>
+          <t>2026-01-06T14:59:02Z</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
@@ -1585,32 +1589,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>hallo</t>
+          <t>forge</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/hallo</t>
+          <t>https://github.com/pinokiofactory/forge</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2024-06-15T21:19:25Z</t>
+          <t>2024-05-11T09:24:03Z</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-02-06T04:29:23Z</t>
+          <t>2024-08-16T22:18:57Z</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2025-11-27T21:34:29Z</t>
+          <t>2024-08-16T22:18:54Z</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
@@ -1621,32 +1625,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>invoke</t>
+          <t>hallo</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/invoke</t>
+          <t>https://github.com/pinokiofactory/hallo</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2024-05-10T07:32:14Z</t>
+          <t>2024-06-15T21:19:25Z</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-01-12T03:44:31Z</t>
+          <t>2026-02-06T04:29:23Z</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2025-12-04T05:43:02Z</t>
+          <t>2025-11-27T21:34:29Z</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
@@ -1657,32 +1661,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>llamafactory</t>
+          <t>invoke</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/llamafactory</t>
+          <t>https://github.com/pinokiofactory/invoke</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2024-05-09T06:38:54Z</t>
+          <t>2024-05-10T07:32:14Z</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-01-24T23:57:24Z</t>
+          <t>2026-01-12T03:44:31Z</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2025-03-17T00:35:50Z</t>
+          <t>2025-12-04T05:43:02Z</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
@@ -1693,32 +1697,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>mcp</t>
+          <t>llamafactory</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/mcp</t>
+          <t>https://github.com/pinokiofactory/llamafactory</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2024-12-21T14:25:08Z</t>
+          <t>2024-05-09T06:38:54Z</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2025-04-28T07:12:22Z</t>
+          <t>2026-03-10T07:05:42Z</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2025-01-03T15:23:57Z</t>
+          <t>2025-03-17T00:35:50Z</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
@@ -1729,32 +1733,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>mlx</t>
+          <t>mcp</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/mlx</t>
+          <t>https://github.com/pinokiofactory/mcp</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2024-06-11T18:20:24Z</t>
+          <t>2024-12-21T14:25:08Z</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2025-11-04T13:12:35Z</t>
+          <t>2025-04-28T07:12:22Z</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2024-11-20T20:34:34Z</t>
+          <t>2025-01-03T15:23:57Z</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
@@ -1765,36 +1769,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>mlx-video-ui</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Pinokio launcher scripts for MLX Video UI</t>
-        </is>
-      </c>
+          <t>mlx</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/mlx-video-ui</t>
+          <t>https://github.com/pinokiofactory/mlx</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-02-07T12:57:17Z</t>
+          <t>2024-06-11T18:20:24Z</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-02-14T00:58:46Z</t>
+          <t>2025-11-04T13:12:35Z</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-02-14T00:58:43Z</t>
+          <t>2024-11-20T20:34:34Z</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
@@ -1805,28 +1805,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>moshi</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
+          <t>mlx-video-ui</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Pinokio launcher scripts for MLX Video UI</t>
+        </is>
+      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/moshi</t>
+          <t>https://github.com/pinokiofactory/mlx-video-ui</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2024-09-18T19:39:38Z</t>
+          <t>2026-02-07T12:57:17Z</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2025-03-16T23:50:32Z</t>
+          <t>2026-02-14T00:58:46Z</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2025-03-16T23:50:29Z</t>
+          <t>2026-02-14T00:58:43Z</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -1841,28 +1845,28 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ominicontrol</t>
+          <t>moshi</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/ominicontrol</t>
+          <t>https://github.com/pinokiofactory/moshi</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2024-11-25T21:32:15Z</t>
+          <t>2024-09-18T19:39:38Z</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024-11-27T09:17:35Z</t>
+          <t>2025-03-16T23:50:32Z</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2024-11-27T09:17:32Z</t>
+          <t>2025-03-16T23:50:29Z</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -1877,32 +1881,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>omnigen</t>
+          <t>ominicontrol</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/omnigen</t>
+          <t>https://github.com/pinokiofactory/ominicontrol</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2024-10-23T18:24:35Z</t>
+          <t>2024-11-25T21:32:15Z</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-03-07T20:08:42Z</t>
+          <t>2024-11-27T09:17:35Z</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2025-12-02T23:04:48Z</t>
+          <t>2024-11-27T09:17:32Z</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
@@ -1913,32 +1917,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>open-webui</t>
+          <t>omnigen</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/open-webui</t>
+          <t>https://github.com/pinokiofactory/omnigen</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2024-07-23T16:53:00Z</t>
+          <t>2024-10-23T18:24:35Z</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2025-12-05T18:23:58Z</t>
+          <t>2026-03-07T20:08:42Z</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2025-11-25T11:47:58Z</t>
+          <t>2025-12-02T23:04:48Z</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
@@ -1949,32 +1953,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>openui</t>
+          <t>open-webui</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/openui</t>
+          <t>https://github.com/pinokiofactory/open-webui</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2024-05-08T08:33:21Z</t>
+          <t>2024-07-23T16:53:00Z</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2025-11-04T12:30:09Z</t>
+          <t>2026-03-08T17:52:21Z</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2024-11-28T23:09:18Z</t>
+          <t>2025-11-25T11:47:58Z</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
@@ -1985,32 +1989,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>pcm</t>
+          <t>openui</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/pcm</t>
+          <t>https://github.com/pinokiofactory/openui</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2024-06-05T15:35:00Z</t>
+          <t>2024-05-08T08:33:21Z</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2025-03-20T03:06:10Z</t>
+          <t>2025-11-04T12:30:09Z</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2025-03-20T03:06:07Z</t>
+          <t>2024-11-28T23:09:18Z</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
@@ -2021,28 +2025,28 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>photomaker2</t>
+          <t>pcm</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/photomaker2</t>
+          <t>https://github.com/pinokiofactory/pcm</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2024-07-22T16:01:32Z</t>
+          <t>2024-06-05T15:35:00Z</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-01-10T21:15:09Z</t>
+          <t>2026-03-10T07:04:59Z</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-01-10T21:15:05Z</t>
+          <t>2025-03-20T03:06:07Z</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -2057,32 +2061,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>rc-stableaudio</t>
+          <t>photomaker2</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/rc-stableaudio</t>
+          <t>https://github.com/pinokiofactory/photomaker2</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2024-07-29T14:44:01Z</t>
+          <t>2024-07-22T16:01:32Z</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2025-11-03T21:06:34Z</t>
+          <t>2026-01-10T21:15:09Z</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2025-03-17T00:05:11Z</t>
+          <t>2026-01-10T21:15:05Z</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
@@ -2093,28 +2097,28 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>sd35</t>
+          <t>rc-stableaudio</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/sd35</t>
+          <t>https://github.com/pinokiofactory/rc-stableaudio</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2024-10-22T19:23:06Z</t>
+          <t>2024-07-29T14:44:01Z</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2024-10-22T19:50:14Z</t>
+          <t>2025-11-03T21:06:34Z</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2024-10-22T19:50:11Z</t>
+          <t>2025-03-17T00:05:11Z</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -2129,32 +2133,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>sillytavern</t>
+          <t>sd35</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/sillytavern</t>
+          <t>https://github.com/pinokiofactory/sd35</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2024-05-21T11:58:31Z</t>
+          <t>2024-10-22T19:23:06Z</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2025-12-29T07:25:21Z</t>
+          <t>2024-10-22T19:50:14Z</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2025-11-26T23:36:47Z</t>
+          <t>2024-10-22T19:50:11Z</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
@@ -2165,32 +2169,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>stable-fast-3d</t>
+          <t>sillytavern</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/stable-fast-3d</t>
+          <t>https://github.com/pinokiofactory/sillytavern</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2024-08-01T18:33:57Z</t>
+          <t>2024-05-21T11:58:31Z</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2024-08-07T20:21:37Z</t>
+          <t>2026-03-14T07:34:23Z</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2024-08-01T18:34:06Z</t>
+          <t>2025-11-26T23:36:47Z</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
@@ -2201,28 +2205,28 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>stableaudio</t>
+          <t>stable-fast-3d</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/stableaudio</t>
+          <t>https://github.com/pinokiofactory/stable-fast-3d</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2024-06-05T20:15:59Z</t>
+          <t>2024-08-01T18:33:57Z</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-02-26T20:36:40Z</t>
+          <t>2024-08-07T20:21:37Z</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-02-26T20:36:35Z</t>
+          <t>2024-08-01T18:34:06Z</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -2237,28 +2241,28 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>video-background-removal</t>
+          <t>stableaudio</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/video-background-removal</t>
+          <t>https://github.com/pinokiofactory/stableaudio</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2024-10-11T16:00:13Z</t>
+          <t>2024-06-05T20:15:59Z</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2025-01-23T21:17:20Z</t>
+          <t>2026-02-26T20:36:40Z</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2024-10-11T17:35:54Z</t>
+          <t>2026-02-26T20:36:35Z</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -2273,32 +2277,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>video-background-removal</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/y</t>
+          <t>https://github.com/pinokiofactory/video-background-removal</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2024-05-20T15:06:00Z</t>
+          <t>2024-10-11T16:00:13Z</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2024-05-20T15:06:01Z</t>
+          <t>2026-03-12T03:43:34Z</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2024-05-20T15:06:01Z</t>
+          <t>2024-10-11T17:35:54Z</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
@@ -2309,32 +2313,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>z-image-turbo</t>
+          <t>y</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/z-image-turbo</t>
+          <t>https://github.com/pinokiofactory/y</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025-12-01T15:28:39Z</t>
+          <t>2024-05-20T15:06:00Z</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2025-12-01T19:45:36Z</t>
+          <t>2024-05-20T15:06:01Z</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2025-12-01T15:28:52Z</t>
+          <t>2024-05-20T15:06:01Z</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
@@ -2345,82 +2349,64 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ovis</t>
+          <t>z-image-turbo</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/ovis</t>
+          <t>https://github.com/pinokiofactory/z-image-turbo</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025-12-01T17:31:10Z</t>
+          <t>2025-12-01T15:28:39Z</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2025-12-01T19:45:35Z</t>
+          <t>2025-12-01T19:45:36Z</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2025-12-01T17:31:27Z</t>
+          <t>2025-12-01T15:28:52Z</t>
         </is>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>AIDC-AI/Ovis-Image</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/AIDC-AI/Ovis-Image</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>2025-11-18T03:46:26Z</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>2025-12-07T06:14:47Z</t>
-        </is>
-      </c>
-      <c r="L52" t="n">
-        <v>4</v>
-      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>text2midi</t>
+          <t>ovis</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/text2midi</t>
+          <t>https://github.com/pinokiofactory/ovis</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2024-12-27T18:31:20Z</t>
+          <t>2025-12-01T17:31:10Z</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2024-12-27T19:21:42Z</t>
+          <t>2025-12-01T19:45:35Z</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2024-12-27T19:21:39Z</t>
+          <t>2025-12-01T17:31:27Z</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -2428,57 +2414,53 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>AMAAI-Lab/Text2midi</t>
+          <t>AIDC-AI/Ovis-Image</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/AMAAI-Lab/Text2midi</t>
+          <t>https://github.com/AIDC-AI/Ovis-Image</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2024-12-19T07:51:33Z</t>
+          <t>2025-11-18T03:46:26Z</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2025-11-15T04:41:44Z</t>
+          <t>2026-03-06T09:24:54Z</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SongGeneration-Studio-MLX</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Tencent SongGeneration Studio MLX</t>
-        </is>
-      </c>
+          <t>text2midi</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/SongGeneration-Studio-MLX</t>
+          <t>https://github.com/pinokiofactory/text2midi</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-01-17T09:12:39Z</t>
+          <t>2024-12-27T18:31:20Z</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-02-01T18:10:47Z</t>
+          <t>2024-12-27T19:21:42Z</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-01-31T15:36:45Z</t>
+          <t>2024-12-27T19:21:39Z</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -2486,439 +2468,439 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>CharafChnioune/SongGeneration-Studio-MLX</t>
+          <t>AMAAI-Lab/Text2midi</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/CharafChnioune/SongGeneration-Studio-MLX</t>
+          <t>https://github.com/AMAAI-Lab/Text2midi</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-01-16T21:45:05Z</t>
+          <t>2024-12-19T07:51:33Z</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-02-06T12:35:34Z</t>
+          <t>2026-03-13T01:11:18Z</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>comfy</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr"/>
+          <t>SongGeneration-Studio-MLX</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Tencent SongGeneration Studio MLX</t>
+        </is>
+      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/comfy</t>
+          <t>https://github.com/pinokiofactory/SongGeneration-Studio-MLX</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2024-08-13T19:47:18Z</t>
+          <t>2026-01-17T09:12:39Z</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-03-06T10:06:31Z</t>
+          <t>2026-03-12T03:44:58Z</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-02-20T19:45:32Z</t>
+          <t>2026-01-31T15:36:45Z</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Comfy-Org/ComfyUI</t>
+          <t>CharafChnioune/SongGeneration-Studio-MLX</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/Comfy-Org/ComfyUI</t>
+          <t>https://github.com/CharafChnioune/SongGeneration-Studio-MLX</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2023-01-17T03:15:56Z</t>
+          <t>2026-01-16T21:45:05Z</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-03-08T06:53:48Z</t>
+          <t>2026-02-10T22:42:47Z</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>3796</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>audiocraft_plus</t>
+          <t>comfy</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/audiocraft_plus</t>
+          <t>https://github.com/pinokiofactory/comfy</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2024-07-30T17:39:46Z</t>
+          <t>2024-08-13T19:47:18Z</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2025-03-17T00:02:40Z</t>
+          <t>2026-03-06T10:06:31Z</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2025-03-17T00:02:36Z</t>
+          <t>2026-02-20T19:45:32Z</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>GrandaddyShmax/audiocraft_plus</t>
+          <t>Comfy-Org/ComfyUI</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/GrandaddyShmax/audiocraft_plus</t>
+          <t>https://github.com/Comfy-Org/ComfyUI</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2023-06-13T14:44:53Z</t>
+          <t>2023-01-17T03:15:56Z</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2025-11-05T05:42:24Z</t>
+          <t>2026-03-15T07:05:58Z</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>38</v>
+        <v>3823</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>applio</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Pinokio Installer for Applio</t>
-        </is>
-      </c>
+          <t>audiocraft_plus</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/applio</t>
+          <t>https://github.com/pinokiofactory/audiocraft_plus</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2024-09-13T18:29:14Z</t>
+          <t>2024-07-30T17:39:46Z</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-01-29T13:21:03Z</t>
+          <t>2025-03-17T00:02:40Z</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2025-12-19T04:34:32Z</t>
+          <t>2025-03-17T00:02:36Z</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>IAHispano/Applio</t>
+          <t>GrandaddyShmax/audiocraft_plus</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/IAHispano/Applio</t>
+          <t>https://github.com/GrandaddyShmax/audiocraft_plus</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2023-08-07T22:42:16Z</t>
+          <t>2023-06-13T14:44:53Z</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-02-01T04:51:15Z</t>
+          <t>2026-03-13T14:44:27Z</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>liveportrait</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr"/>
+          <t>applio</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Pinokio Installer for Applio</t>
+        </is>
+      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/liveportrait</t>
+          <t>https://github.com/pinokiofactory/applio</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2024-07-22T12:47:06Z</t>
+          <t>2024-09-13T18:29:14Z</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-01-25T06:00:38Z</t>
+          <t>2026-01-29T13:21:03Z</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-01-25T06:00:34Z</t>
+          <t>2025-12-19T04:34:32Z</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>KlingTeam/LivePortrait</t>
+          <t>IAHispano/Applio</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/KlingTeam/LivePortrait</t>
+          <t>https://github.com/IAHispano/Applio</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2024-07-03T16:15:03Z</t>
+          <t>2023-08-07T22:42:16Z</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-01-25T04:17:48Z</t>
+          <t>2026-03-14T21:25:05Z</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>284</v>
+        <v>30</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Orpheus-TTS-FastAPI</t>
+          <t>liveportrait</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/Orpheus-TTS-FastAPI</t>
+          <t>https://github.com/pinokiofactory/liveportrait</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025-03-23T05:39:00Z</t>
+          <t>2024-07-22T12:47:06Z</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-02-20T16:26:14Z</t>
+          <t>2026-01-25T06:00:38Z</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2025-12-02T20:56:20Z</t>
+          <t>2026-01-25T06:00:34Z</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Lex-au/Orpheus-FastAPI</t>
+          <t>KlingAIResearch/LivePortrait</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/Lex-au/Orpheus-FastAPI</t>
+          <t>https://github.com/KlingAIResearch/LivePortrait</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2025-03-21T15:24:16Z</t>
+          <t>2024-07-03T16:15:03Z</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-02-21T14:02:05Z</t>
+          <t>2026-03-15T05:19:39Z</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>16</v>
+        <v>285</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>mlx-video-transcription</t>
+          <t>Orpheus-TTS-FastAPI</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/mlx-video-transcription</t>
+          <t>https://github.com/pinokiofactory/Orpheus-TTS-FastAPI</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2024-08-19T17:41:12Z</t>
+          <t>2025-03-23T05:39:00Z</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-02-15T23:03:28Z</t>
+          <t>2026-03-12T03:33:51Z</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2024-10-03T19:11:23Z</t>
+          <t>2025-12-02T20:56:20Z</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>RayFernando1337/MLX-Auto-Subtitled-Video-Generator</t>
+          <t>Lex-au/Orpheus-FastAPI</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/RayFernando1337/MLX-Auto-Subtitled-Video-Generator</t>
+          <t>https://github.com/Lex-au/Orpheus-FastAPI</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2024-07-30T08:44:41Z</t>
+          <t>2025-03-21T15:24:16Z</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-02-19T16:27:53Z</t>
+          <t>2026-03-10T16:47:25Z</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>cube</t>
+          <t>mlx-video-transcription</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/cube</t>
+          <t>https://github.com/pinokiofactory/mlx-video-transcription</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025-03-20T21:16:36Z</t>
+          <t>2024-08-19T17:41:12Z</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-01-24T17:31:53Z</t>
+          <t>2026-03-12T03:41:40Z</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2025-12-02T21:01:20Z</t>
+          <t>2024-10-03T19:11:23Z</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Roblox/cube</t>
+          <t>RayFernando1337/MLX-Auto-Subtitled-Video-Generator</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/Roblox/cube</t>
+          <t>https://github.com/RayFernando1337/MLX-Auto-Subtitled-Video-Generator</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2025-03-11T22:09:47Z</t>
+          <t>2024-07-30T08:44:41Z</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-01-24T17:32:07Z</t>
+          <t>2026-02-27T07:44:24Z</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Ultimate-TTS-Studio</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>🟢 NVIDIA ONLY – All-in-One TTS App with Kokoro, KittenTTS, Higgs audio, Chatterbox, Fish-Speech, F5 &amp; index-tts &amp; indextts2, Supports Conversation Mode &amp; eBook-to-Audiobook. All features work across all engines in a unified interface except vibe voice which is it's own app panel.</t>
-        </is>
-      </c>
+          <t>cube</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/Ultimate-TTS-Studio</t>
+          <t>https://github.com/pinokiofactory/cube</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025-11-25T20:10:36Z</t>
+          <t>2025-03-20T21:16:36Z</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-02-23T15:45:46Z</t>
+          <t>2026-01-24T17:31:53Z</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-02-18T00:45:10Z</t>
+          <t>2025-12-02T21:01:20Z</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -2926,165 +2908,169 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>SUP3RMASS1VE/Ultimate-TTS-Studio-SUP3R-Edition</t>
+          <t>Roblox/cube</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/SUP3RMASS1VE/Ultimate-TTS-Studio-SUP3R-Edition</t>
+          <t>https://github.com/Roblox/cube</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2025-06-06T14:54:06Z</t>
+          <t>2025-03-11T22:09:47Z</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-02-28T14:20:01Z</t>
+          <t>2026-03-14T09:19:42Z</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>hertz</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr"/>
+          <t>Ultimate-TTS-Studio</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>🟢 NVIDIA ONLY – All-in-One TTS App with Kokoro, KittenTTS, Higgs audio, Chatterbox, Fish-Speech, F5 &amp; index-tts &amp; indextts2, Supports Conversation Mode &amp; eBook-to-Audiobook. All features work across all engines in a unified interface except vibe voice which is it's own app panel.</t>
+        </is>
+      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/hertz</t>
+          <t>https://github.com/pinokiofactory/Ultimate-TTS-Studio</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2024-11-04T01:04:51Z</t>
+          <t>2025-11-25T20:10:36Z</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2024-11-05T08:54:25Z</t>
+          <t>2026-03-12T03:14:42Z</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2024-11-05T08:54:21Z</t>
+          <t>2026-02-18T00:45:10Z</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Standard-Intelligence/hertz-dev</t>
+          <t>SUP3RMASS1VE/Ultimate-TTS-Studio-SUP3R-Edition</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/Standard-Intelligence/hertz-dev</t>
+          <t>https://github.com/SUP3RMASS1VE/Ultimate-TTS-Studio-SUP3R-Edition</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2024-11-03T14:41:39Z</t>
+          <t>2025-06-06T14:54:06Z</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2025-11-14T16:05:18Z</t>
+          <t>2026-03-14T08:32:05Z</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Hunyuan3D-2</t>
+          <t>hertz</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/Hunyuan3D-2</t>
+          <t>https://github.com/pinokiofactory/hertz</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025-01-25T04:41:01Z</t>
+          <t>2024-11-04T01:04:51Z</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2025-11-09T20:06:13Z</t>
+          <t>2024-11-05T08:54:25Z</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2025-11-09T20:06:10Z</t>
+          <t>2024-11-05T08:54:21Z</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Tencent-Hunyuan/Hunyuan3D-2</t>
+          <t>Standard-Intelligence/hertz-dev</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/Tencent-Hunyuan/Hunyuan3D-2</t>
+          <t>https://github.com/Standard-Intelligence/hertz-dev</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2025-01-21T05:21:35Z</t>
+          <t>2024-11-03T14:41:39Z</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2025-11-16T06:33:02Z</t>
+          <t>2026-03-13T21:16:02Z</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>219</v>
+        <v>16</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Hunyuan3D-2-mini</t>
+          <t>Hunyuan3D-2</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/Hunyuan3D-2-mini</t>
+          <t>https://github.com/pinokiofactory/Hunyuan3D-2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025-01-23T21:29:42Z</t>
+          <t>2025-01-25T04:41:01Z</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2025-01-25T03:18:46Z</t>
+          <t>2025-11-09T20:06:13Z</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2025-01-25T03:50:23Z</t>
+          <t>2025-11-09T20:06:10Z</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -3103,42 +3089,38 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2025-11-16T06:33:02Z</t>
+          <t>2026-03-15T05:38:56Z</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>219</v>
+        <v>231</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AudioX</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>AudioX: Diffusion Transformer for Anything-to-Audio Generation</t>
-        </is>
-      </c>
+          <t>Hunyuan3D-2-mini</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/AudioX</t>
+          <t>https://github.com/pinokiofactory/Hunyuan3D-2-mini</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025-04-23T00:08:00Z</t>
+          <t>2025-01-23T21:29:42Z</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2025-07-12T12:25:25Z</t>
+          <t>2025-01-25T03:18:46Z</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2025-07-12T12:25:21Z</t>
+          <t>2025-01-25T03:50:23Z</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -3146,771 +3128,775 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>ZeyueT/AudioX</t>
+          <t>Tencent-Hunyuan/Hunyuan3D-2</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/ZeyueT/AudioX</t>
+          <t>https://github.com/Tencent-Hunyuan/Hunyuan3D-2</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2025-03-13T10:18:21Z</t>
+          <t>2025-01-21T05:21:35Z</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2025-11-14T16:45:52Z</t>
+          <t>2026-03-15T05:38:56Z</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>52</v>
+        <v>231</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>RMBG-2-Studio</t>
+          <t>AudioX</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Enhanced background remove and replace app built around BRIA-RMBG-2.0.  Low VRAM/RAM | 6GB Install</t>
+          <t>AudioX: Diffusion Transformer for Anything-to-Audio Generation</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/RMBG-2-Studio</t>
+          <t>https://github.com/pinokiofactory/AudioX</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2024-11-15T07:13:23Z</t>
+          <t>2025-04-23T00:08:00Z</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-03-07T21:28:47Z</t>
+          <t>2025-07-12T12:25:25Z</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2025-12-02T22:50:55Z</t>
+          <t>2025-07-12T12:25:21Z</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>ZhengPeng7/BiRefNet</t>
+          <t>ZeyueT/AudioX</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/ZhengPeng7/BiRefNet</t>
+          <t>https://github.com/ZeyueT/AudioX</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2022-08-17T09:13:39Z</t>
+          <t>2025-03-13T10:18:21Z</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-03-07T14:17:38Z</t>
+          <t>2026-03-15T07:09:43Z</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>24</v>
+        <v>54</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>zonos</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr"/>
+          <t>RMBG-2-Studio</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Enhanced background remove and replace app built around BRIA-RMBG-2.0.  Low VRAM/RAM | 6GB Install</t>
+        </is>
+      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/zonos</t>
+          <t>https://github.com/pinokiofactory/RMBG-2-Studio</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025-02-11T09:00:12Z</t>
+          <t>2024-11-15T07:13:23Z</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2025-12-06T22:44:56Z</t>
+          <t>2026-03-13T08:49:46Z</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2025-12-06T22:44:52Z</t>
+          <t>2025-12-02T22:50:55Z</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Zyphra/Zonos</t>
+          <t>ZhengPeng7/BiRefNet</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/Zyphra/Zonos</t>
+          <t>https://github.com/ZhengPeng7/BiRefNet</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2025-02-07T00:32:44Z</t>
+          <t>2022-08-17T09:13:39Z</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2025-12-06T07:10:48Z</t>
+          <t>2026-03-13T17:21:13Z</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>167</v>
+        <v>27</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ACE-Step</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>A Step Towards Music Generation Foundation Model</t>
-        </is>
-      </c>
+          <t>zonos</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/ACE-Step</t>
+          <t>https://github.com/pinokiofactory/zonos</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025-05-07T11:25:33Z</t>
+          <t>2025-02-11T09:00:12Z</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2025-12-06T11:35:01Z</t>
+          <t>2026-03-13T16:05:10Z</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2025-12-06T11:34:57Z</t>
+          <t>2025-12-06T22:44:52Z</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>ace-step/ACE-Step</t>
+          <t>Zyphra/Zonos</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/ace-step/ACE-Step</t>
+          <t>https://github.com/Zyphra/Zonos</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2025-04-28T07:03:09Z</t>
+          <t>2025-02-07T00:32:44Z</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2025-12-07T04:48:04Z</t>
+          <t>2026-03-15T06:38:12Z</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>118</v>
+        <v>168</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>MagicQuill</t>
+          <t>ACE-Step</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>An intelligent, interactive Image Editing System. Easily erase and add objects on a user-friendly interface.</t>
+          <t>A Step Towards Music Generation Foundation Model</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/MagicQuill</t>
+          <t>https://github.com/pinokiofactory/ACE-Step</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025-02-19T03:58:52Z</t>
+          <t>2025-05-07T11:25:33Z</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-01-11T20:08:02Z</t>
+          <t>2025-12-06T11:35:01Z</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-01-11T20:07:58Z</t>
+          <t>2025-12-06T11:34:57Z</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>ant-research/MagicQuill</t>
+          <t>ace-step/ACE-Step</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/ant-research/MagicQuill</t>
+          <t>https://github.com/ace-step/ACE-Step</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2024-11-12T12:52:36Z</t>
+          <t>2025-04-28T07:03:09Z</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-01-13T22:00:43Z</t>
+          <t>2026-03-15T06:42:41Z</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>46</v>
+        <v>143</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>echomimic2</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr"/>
+          <t>MagicQuill</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>An intelligent, interactive Image Editing System. Easily erase and add objects on a user-friendly interface.</t>
+        </is>
+      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/echomimic2</t>
+          <t>https://github.com/pinokiofactory/MagicQuill</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2024-11-24T07:52:04Z</t>
+          <t>2025-02-19T03:58:52Z</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2025-12-06T05:47:59Z</t>
+          <t>2026-03-10T07:03:48Z</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2025-12-06T05:47:56Z</t>
+          <t>2026-01-11T20:07:58Z</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>antgroup/echomimic_v2</t>
+          <t>ant-research/MagicQuill</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antgroup/echomimic_v2</t>
+          <t>https://github.com/ant-research/MagicQuill</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2024-11-20T08:35:35Z</t>
+          <t>2024-11-12T12:52:36Z</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2025-12-06T17:52:50Z</t>
+          <t>2026-03-12T09:12:26Z</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>79</v>
+        <v>46</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>macOS-use</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>We Make Mac apps accessible for AI agents</t>
-        </is>
-      </c>
+          <t>echomimic2</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/macOS-use</t>
+          <t>https://github.com/pinokiofactory/echomimic2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025-02-18T16:54:37Z</t>
+          <t>2024-11-24T07:52:04Z</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2025-11-04T13:06:11Z</t>
+          <t>2025-12-06T05:47:59Z</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2025-04-01T04:14:59Z</t>
+          <t>2025-12-06T05:47:56Z</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>browser-use/macOS-use</t>
+          <t>antgroup/echomimic_v2</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/browser-use/macOS-use</t>
+          <t>https://github.com/antgroup/echomimic_v2</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2025-01-23T00:35:15Z</t>
+          <t>2024-11-20T08:35:35Z</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2025-11-14T12:34:29Z</t>
+          <t>2026-03-14T04:25:07Z</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>16</v>
+        <v>78</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>browser-use</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr"/>
+          <t>macOS-use</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>We Make Mac apps accessible for AI agents</t>
+        </is>
+      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/browser-use</t>
+          <t>https://github.com/pinokiofactory/macOS-use</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025-01-19T21:55:50Z</t>
+          <t>2025-02-18T16:54:37Z</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-01-27T14:53:11Z</t>
+          <t>2025-11-04T13:06:11Z</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2025-04-01T04:25:12Z</t>
+          <t>2025-04-01T04:14:59Z</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>browser-use/web-ui</t>
+          <t>browser-use/macOS-use</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/browser-use/web-ui</t>
+          <t>https://github.com/browser-use/macOS-use</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2025-01-02T01:29:44Z</t>
+          <t>2025-01-23T00:35:15Z</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-02-01T03:05:32Z</t>
+          <t>2026-03-13T23:25:03Z</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>309</v>
+        <v>17</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>uno</t>
+          <t>browser-use</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/uno</t>
+          <t>https://github.com/pinokiofactory/browser-use</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025-04-10T18:31:57Z</t>
+          <t>2025-01-19T21:55:50Z</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2025-12-02T20:55:29Z</t>
+          <t>2026-01-27T14:53:11Z</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2025-12-02T20:55:25Z</t>
+          <t>2025-04-01T04:25:12Z</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>bytedance/UNO</t>
+          <t>browser-use/web-ui</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/bytedance/UNO</t>
+          <t>https://github.com/browser-use/web-ui</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2025-04-01T13:25:11Z</t>
+          <t>2025-01-02T01:29:44Z</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2025-12-04T05:12:09Z</t>
+          <t>2026-03-14T20:08:39Z</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>28</v>
+        <v>315</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Hunyuan3d-2-lowvram</t>
+          <t>uno</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/Hunyuan3d-2-lowvram</t>
+          <t>https://github.com/pinokiofactory/uno</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025-01-25T04:44:25Z</t>
+          <t>2025-04-10T18:31:57Z</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-03-04T05:39:26Z</t>
+          <t>2025-12-02T20:55:29Z</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2025-12-27T20:44:51Z</t>
+          <t>2025-12-02T20:55:25Z</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>deepbeepmeep/Hunyuan3D-2GP</t>
+          <t>bytedance/UNO</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/deepbeepmeep/Hunyuan3D-2GP</t>
+          <t>https://github.com/bytedance/UNO</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2025-01-22T01:50:03Z</t>
+          <t>2025-04-01T13:25:11Z</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-03-04T19:04:33Z</t>
+          <t>2026-03-12T21:01:22Z</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>hunyuanvideo</t>
+          <t>Hunyuan3d-2-lowvram</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/hunyuanvideo</t>
+          <t>https://github.com/pinokiofactory/Hunyuan3d-2-lowvram</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2024-12-11T01:55:53Z</t>
+          <t>2025-01-25T04:44:25Z</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-01-19T16:49:14Z</t>
+          <t>2026-03-04T05:39:26Z</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2025-12-02T20:58:56Z</t>
+          <t>2025-12-27T20:44:51Z</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>deepbeepmeep/HunyuanVideoGP</t>
+          <t>deepbeepmeep/Hunyuan3D-2GP</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/deepbeepmeep/HunyuanVideoGP</t>
+          <t>https://github.com/deepbeepmeep/Hunyuan3D-2GP</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2024-12-10T18:34:42Z</t>
+          <t>2025-01-22T01:50:03Z</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-01-21T10:14:46Z</t>
+          <t>2026-03-13T18:55:15Z</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>wan</t>
+          <t>hunyuanvideo</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/wan</t>
+          <t>https://github.com/pinokiofactory/hunyuanvideo</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025-03-03T17:32:45Z</t>
+          <t>2024-12-11T01:55:53Z</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-03-07T20:45:48Z</t>
+          <t>2026-01-19T16:49:14Z</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-02-20T18:00:24Z</t>
+          <t>2025-12-02T20:58:56Z</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>deepbeepmeep/Wan2GP</t>
+          <t>deepbeepmeep/HunyuanVideoGP</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/deepbeepmeep/Wan2GP</t>
+          <t>https://github.com/deepbeepmeep/HunyuanVideoGP</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2025-02-27T23:52:36Z</t>
+          <t>2024-12-10T18:34:42Z</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-03-08T03:57:04Z</t>
+          <t>2026-03-12T03:18:44Z</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>686</v>
+        <v>13</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>yue</t>
+          <t>wan</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/yue</t>
+          <t>https://github.com/pinokiofactory/wan</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025-01-29T11:22:39Z</t>
+          <t>2025-03-03T17:32:45Z</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-02-11T18:06:59Z</t>
+          <t>2026-03-07T20:45:48Z</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2025-12-02T21:56:04Z</t>
+          <t>2026-02-20T18:00:24Z</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>deepbeepmeep/YuEGP</t>
+          <t>deepbeepmeep/Wan2GP</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/deepbeepmeep/YuEGP</t>
+          <t>https://github.com/deepbeepmeep/Wan2GP</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2025-01-28T07:23:51Z</t>
+          <t>2025-02-27T23:52:36Z</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-02-07T07:04:54Z</t>
+          <t>2026-03-15T04:06:48Z</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>21</v>
+        <v>701</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>janus</t>
+          <t>yue</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/janus</t>
+          <t>https://github.com/pinokiofactory/yue</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025-01-27T18:23:47Z</t>
+          <t>2025-01-29T11:22:39Z</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2025-01-28T02:37:49Z</t>
+          <t>2026-02-11T18:06:59Z</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2025-01-28T02:37:46Z</t>
+          <t>2025-12-02T21:56:04Z</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>deepseek-ai/Janus</t>
+          <t>deepbeepmeep/YuEGP</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/deepseek-ai/Janus</t>
+          <t>https://github.com/deepbeepmeep/YuEGP</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2024-10-18T03:48:16Z</t>
+          <t>2025-01-28T07:23:51Z</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2025-11-15T15:45:09Z</t>
+          <t>2026-03-05T16:08:21Z</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>177</v>
+        <v>21</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>diamond</t>
+          <t>janus</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/diamond</t>
+          <t>https://github.com/pinokiofactory/janus</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2024-10-12T15:37:19Z</t>
+          <t>2025-01-27T18:23:47Z</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-01-24T06:17:09Z</t>
+          <t>2025-01-28T02:37:49Z</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2025-12-02T23:46:49Z</t>
+          <t>2025-01-28T02:37:46Z</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -3918,833 +3904,829 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>eloialonso/diamond</t>
+          <t>deepseek-ai/Janus</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/eloialonso/diamond</t>
+          <t>https://github.com/deepseek-ai/Janus</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2024-05-19T22:31:40Z</t>
+          <t>2024-10-18T03:48:16Z</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-01-23T09:30:32Z</t>
+          <t>2026-03-15T05:10:23Z</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>6</v>
+        <v>184</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>AllTalk-TTS</t>
+          <t>diamond</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/AllTalk-TTS</t>
+          <t>https://github.com/pinokiofactory/diamond</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025-02-05T16:24:30Z</t>
+          <t>2024-10-12T15:37:19Z</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2025-04-05T16:19:34Z</t>
+          <t>2026-01-24T06:17:09Z</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2025-03-29T16:44:51Z</t>
+          <t>2025-12-02T23:46:49Z</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>erew123/alltalk_tts</t>
+          <t>eloialonso/diamond</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/erew123/alltalk_tts</t>
+          <t>https://github.com/eloialonso/diamond</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2023-12-08T09:35:19Z</t>
+          <t>2024-05-19T22:31:40Z</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2025-11-15T23:50:46Z</t>
+          <t>2026-03-14T17:04:12Z</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>71</v>
+        <v>6</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>oasis</t>
+          <t>AllTalk-TTS</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/oasis</t>
+          <t>https://github.com/pinokiofactory/AllTalk-TTS</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2024-10-31T23:24:32Z</t>
+          <t>2025-02-05T16:24:30Z</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2024-10-31T23:47:38Z</t>
+          <t>2025-04-05T16:19:34Z</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2024-10-31T23:47:35Z</t>
+          <t>2025-03-29T16:44:51Z</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>etched-ai/open-oasis</t>
+          <t>erew123/alltalk_tts</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/etched-ai/open-oasis</t>
+          <t>https://github.com/erew123/alltalk_tts</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2024-10-31T09:10:45Z</t>
+          <t>2023-12-08T09:35:19Z</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2025-11-14T05:41:47Z</t>
+          <t>2026-03-15T01:51:06Z</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>30</v>
+        <v>85</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>openaudio</t>
+          <t>oasis</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/openaudio</t>
+          <t>https://github.com/pinokiofactory/oasis</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2024-11-02T08:47:31Z</t>
+          <t>2024-10-31T23:24:32Z</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-01-30T21:11:00Z</t>
+          <t>2024-10-31T23:47:38Z</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-01-30T21:10:56Z</t>
+          <t>2024-10-31T23:47:35Z</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>fishaudio/fish-speech</t>
+          <t>etched-ai/open-oasis</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/fishaudio/fish-speech</t>
+          <t>https://github.com/etched-ai/open-oasis</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2023-10-10T03:16:51Z</t>
+          <t>2024-10-31T09:10:45Z</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-02-01T01:25:30Z</t>
+          <t>2026-03-10T03:23:19Z</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>mochi</t>
+          <t>openaudio</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/mochi</t>
+          <t>https://github.com/pinokiofactory/openaudio</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2024-10-23T18:51:07Z</t>
+          <t>2024-11-02T08:47:31Z</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2024-10-29T03:03:08Z</t>
+          <t>2026-01-30T21:11:00Z</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2024-10-29T03:03:04Z</t>
+          <t>2026-01-30T21:10:56Z</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>genmoai/mochi</t>
+          <t>fishaudio/fish-speech</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/genmoai/mochi</t>
+          <t>https://github.com/fishaudio/fish-speech</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2024-09-11T02:55:33Z</t>
+          <t>2023-10-10T03:16:51Z</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2025-11-15T23:14:45Z</t>
+          <t>2026-03-15T07:04:55Z</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>58</v>
+        <v>33</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>instantir</t>
+          <t>mochi</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/instantir</t>
+          <t>https://github.com/pinokiofactory/mochi</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2024-11-08T08:05:55Z</t>
+          <t>2024-10-23T18:51:07Z</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2025-12-02T22:52:18Z</t>
+          <t>2024-10-29T03:03:08Z</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2025-12-02T22:52:15Z</t>
+          <t>2024-10-29T03:03:04Z</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>instantX-research/InstantIR</t>
+          <t>genmoai/mochi</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/instantX-research/InstantIR</t>
+          <t>https://github.com/genmoai/mochi</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>2024-10-20T03:17:01Z</t>
+          <t>2024-09-11T02:55:33Z</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2025-11-26T08:31:35Z</t>
+          <t>2026-03-13T07:05:57Z</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>8</v>
+        <v>59</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>whisper-webui</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Pinokio Installer for Whisper-Webui</t>
-        </is>
-      </c>
+          <t>instantir</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/whisper-webui</t>
+          <t>https://github.com/pinokiofactory/instantir</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2024-09-21T20:42:20Z</t>
+          <t>2024-11-08T08:05:55Z</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-01-20T23:36:49Z</t>
+          <t>2025-12-02T22:52:18Z</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-01-09T00:52:01Z</t>
+          <t>2025-12-02T22:52:15Z</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>jhj0517/Whisper-WebUI</t>
+          <t>instantX-research/InstantIR</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/jhj0517/Whisper-WebUI</t>
+          <t>https://github.com/instantX-research/InstantIR</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>2023-03-02T13:42:01Z</t>
+          <t>2024-10-20T03:17:01Z</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-01-24T00:59:46Z</t>
+          <t>2026-03-14T16:00:20Z</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>136</v>
+        <v>8</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>pyramidflow</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr"/>
+          <t>whisper-webui</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Pinokio Installer for Whisper-Webui</t>
+        </is>
+      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/pyramidflow</t>
+          <t>https://github.com/pinokiofactory/whisper-webui</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2024-11-16T08:35:22Z</t>
+          <t>2024-09-21T20:42:20Z</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2025-12-04T18:28:05Z</t>
+          <t>2026-01-20T23:36:49Z</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2025-12-04T18:28:01Z</t>
+          <t>2026-01-09T00:52:01Z</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>jy0205/Pyramid-Flow</t>
+          <t>jhj0517/Whisper-WebUI</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/jy0205/Pyramid-Flow</t>
+          <t>https://github.com/jhj0517/Whisper-WebUI</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>2024-10-06T13:06:31Z</t>
+          <t>2023-03-02T13:42:01Z</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2025-12-06T20:01:25Z</t>
+          <t>2026-03-13T00:03:55Z</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>71</v>
+        <v>146</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Frame-Pack</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>(NVIDIA) FramePack is a next-frame (next-frame-section) prediction neural network structure that generates videos progressively.</t>
-        </is>
-      </c>
+          <t>pyramidflow</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr"/>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/Frame-Pack</t>
+          <t>https://github.com/pinokiofactory/pyramidflow</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025-04-17T11:43:03Z</t>
+          <t>2024-11-16T08:35:22Z</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-02-12T07:58:31Z</t>
+          <t>2025-12-04T18:28:05Z</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2025-12-18T10:04:19Z</t>
+          <t>2025-12-04T18:28:01Z</t>
         </is>
       </c>
       <c r="G88" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>lllyasviel/FramePack</t>
+          <t>jy0205/Pyramid-Flow</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/lllyasviel/FramePack</t>
+          <t>https://github.com/jy0205/Pyramid-Flow</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>2025-04-12T14:45:22Z</t>
+          <t>2024-10-06T13:06:31Z</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-02-15T02:39:47Z</t>
+          <t>2026-03-14T00:14:25Z</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>474</v>
+        <v>71</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>stable-diffusion-webui-forge</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr"/>
+          <t>Frame-Pack</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>(NVIDIA) FramePack is a next-frame (next-frame-section) prediction neural network structure that generates videos progressively.</t>
+        </is>
+      </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/stable-diffusion-webui-forge</t>
+          <t>https://github.com/pinokiofactory/Frame-Pack</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2024-08-12T12:38:49Z</t>
+          <t>2025-04-17T11:43:03Z</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-02-20T18:30:12Z</t>
+          <t>2026-03-09T14:29:40Z</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-02-10T03:05:55Z</t>
+          <t>2025-12-18T10:04:19Z</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>lllyasviel/stable-diffusion-webui-forge</t>
+          <t>lllyasviel/FramePack</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/lllyasviel/stable-diffusion-webui-forge</t>
+          <t>https://github.com/lllyasviel/FramePack</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>2024-01-14T11:39:30Z</t>
+          <t>2025-04-12T14:45:22Z</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-02-22T02:25:46Z</t>
+          <t>2026-03-15T03:25:29Z</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1128</v>
+        <v>475</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>omniparser</t>
+          <t>stable-diffusion-webui-forge</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/omniparser</t>
+          <t>https://github.com/pinokiofactory/stable-diffusion-webui-forge</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2024-10-26T06:04:17Z</t>
+          <t>2024-08-12T12:38:49Z</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2024-10-28T04:49:07Z</t>
+          <t>2026-02-20T18:30:12Z</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2024-10-26T08:03:10Z</t>
+          <t>2026-02-10T03:05:55Z</t>
         </is>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>microsoft/OmniParser</t>
+          <t>lllyasviel/stable-diffusion-webui-forge</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/microsoft/OmniParser</t>
+          <t>https://github.com/lllyasviel/stable-diffusion-webui-forge</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>2024-09-20T05:18:18Z</t>
+          <t>2024-01-14T11:39:30Z</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2025-11-16T06:25:49Z</t>
+          <t>2026-03-15T03:03:47Z</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>225</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>vibevoice-realtime</t>
+          <t>omniparser</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/vibevoice-realtime</t>
+          <t>https://github.com/pinokiofactory/omniparser</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025-12-04T21:57:09Z</t>
+          <t>2024-10-26T06:04:17Z</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-02-01T06:38:32Z</t>
+          <t>2024-10-28T04:49:07Z</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2025-12-22T22:00:09Z</t>
+          <t>2024-10-26T08:03:10Z</t>
         </is>
       </c>
       <c r="G91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>microsoft/VibeVoice</t>
+          <t>microsoft/OmniParser</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/microsoft/VibeVoice</t>
+          <t>https://github.com/microsoft/OmniParser</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>2025-08-25T13:24:01Z</t>
+          <t>2024-09-20T05:18:18Z</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-02-01T06:53:32Z</t>
+          <t>2026-03-14T15:37:21Z</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>87</v>
+        <v>231</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>dia</t>
+          <t>vibevoice-realtime</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/dia</t>
+          <t>https://github.com/pinokiofactory/vibevoice-realtime</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025-04-22T14:57:53Z</t>
+          <t>2025-12-04T21:57:09Z</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2025-12-07T19:55:02Z</t>
+          <t>2026-02-01T06:38:32Z</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2025-12-07T19:54:59Z</t>
+          <t>2025-12-22T22:00:09Z</t>
         </is>
       </c>
       <c r="G92" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>nari-labs/dia</t>
+          <t>microsoft/VibeVoice</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/nari-labs/dia</t>
+          <t>https://github.com/microsoft/VibeVoice</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>2025-04-19T07:15:57Z</t>
+          <t>2025-08-25T13:24:01Z</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2025-12-14T04:00:35Z</t>
+          <t>2026-03-15T05:24:59Z</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>87</v>
+        <v>104</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>clarity-refiners-ui</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Creative Image Enhancer/Upscaler. Powered By Refiners.  8GB VRAM | 10GB Install</t>
-        </is>
-      </c>
+          <t>dia</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr"/>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/clarity-refiners-ui</t>
+          <t>https://github.com/pinokiofactory/dia</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2024-11-12T07:03:48Z</t>
+          <t>2025-04-22T14:57:53Z</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-01-02T20:07:27Z</t>
+          <t>2025-12-07T19:55:02Z</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2025-12-02T22:18:28Z</t>
+          <t>2025-12-07T19:54:59Z</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>philz1337x/clarity-upscaler</t>
+          <t>nari-labs/dia</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/philz1337x/clarity-upscaler</t>
+          <t>https://github.com/nari-labs/dia</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>2024-03-15T15:21:40Z</t>
+          <t>2025-04-19T07:15:57Z</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2026-01-03T09:04:39Z</t>
+          <t>2026-03-15T00:24:03Z</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>18</v>
+        <v>90</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Allegro-txt2vid</t>
+          <t>clarity-refiners-ui</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Allegro is a powerful text-to-video model that generates high-quality videos up to 6 seconds at 15 FPS and 720p resolution from simple text input.</t>
+          <t>Creative Image Enhancer/Upscaler. Powered By Refiners.  8GB VRAM | 10GB Install</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/Allegro-txt2vid</t>
+          <t>https://github.com/pinokiofactory/clarity-refiners-ui</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2024-10-25T06:33:03Z</t>
+          <t>2024-11-12T07:03:48Z</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2024-11-05T23:56:50Z</t>
+          <t>2026-01-02T20:07:27Z</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2024-11-05T23:56:47Z</t>
+          <t>2025-12-02T22:18:28Z</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>rhymes-ai/Allegro</t>
+          <t>philz1337x/clarity-upscaler</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/rhymes-ai/Allegro</t>
+          <t>https://github.com/philz1337x/clarity-upscaler</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>2024-10-16T04:04:15Z</t>
+          <t>2024-03-15T15:21:40Z</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2025-11-07T08:32:13Z</t>
+          <t>2026-03-15T03:05:10Z</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Allegro-txt2vid-install</t>
+          <t>Allegro-txt2vid</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Allegro-txt2vid. WARNING: takes a long time to generate a result, 1hr on a 3090. 12GB+ VRAM | 32GB+ RAM | 30GB Download. Check the README for details</t>
+          <t>Allegro is a powerful text-to-video model that generates high-quality videos up to 6 seconds at 15 FPS and 720p resolution from simple text input.</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/Allegro-txt2vid-install</t>
+          <t>https://github.com/pinokiofactory/Allegro-txt2vid</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2024-10-27T14:58:05Z</t>
+          <t>2024-10-25T06:33:03Z</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2025-12-04T05:36:24Z</t>
+          <t>2024-11-05T23:56:50Z</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2025-12-04T05:36:20Z</t>
+          <t>2024-11-05T23:56:47Z</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -4763,7 +4745,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>2025-12-06T00:53:45Z</t>
+          <t>2026-03-04T19:39:48Z</t>
         </is>
       </c>
       <c r="L95" t="n">
@@ -4773,32 +4755,32 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>RuinedFooocus</t>
+          <t>Allegro-txt2vid-install</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t xml:space="preserve">(NVIDIA ONLY) Forget everything you thought you knew about AI art generation - RuinedFooocus is here to completely reinvent the game! This groundbreaking image creator combines the best aspects of Stable Diffusion and Midjourney into one seamless, cutting-edge experience. </t>
+          <t>Allegro-txt2vid. WARNING: takes a long time to generate a result, 1hr on a 3090. 12GB+ VRAM | 32GB+ RAM | 30GB Download. Check the README for details</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/RuinedFooocus</t>
+          <t>https://github.com/pinokiofactory/Allegro-txt2vid-install</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025-04-22T14:09:26Z</t>
+          <t>2024-10-27T14:58:05Z</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2025-10-30T19:53:32Z</t>
+          <t>2025-12-04T05:36:24Z</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2025-10-30T19:53:29Z</t>
+          <t>2025-12-04T05:36:20Z</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -4806,242 +4788,300 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>runew0lf/RuinedFooocus</t>
+          <t>rhymes-ai/Allegro</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/runew0lf/RuinedFooocus</t>
+          <t>https://github.com/rhymes-ai/Allegro</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>2023-08-16T09:20:46Z</t>
+          <t>2024-10-16T04:04:15Z</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2025-11-15T08:55:10Z</t>
+          <t>2026-03-04T19:39:48Z</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>bolt</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr"/>
+          <t>RuinedFooocus</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(NVIDIA ONLY) Forget everything you thought you knew about AI art generation - RuinedFooocus is here to completely reinvent the game! This groundbreaking image creator combines the best aspects of Stable Diffusion and Midjourney into one seamless, cutting-edge experience. </t>
+        </is>
+      </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/bolt</t>
+          <t>https://github.com/pinokiofactory/RuinedFooocus</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2024-10-30T04:46:10Z</t>
+          <t>2025-04-22T14:09:26Z</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-03-06T16:37:35Z</t>
+          <t>2025-10-30T19:53:32Z</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2025-12-06T21:59:33Z</t>
+          <t>2025-10-30T19:53:29Z</t>
         </is>
       </c>
       <c r="G97" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>stackblitz-labs/bolt.diy</t>
+          <t>runew0lf/RuinedFooocus</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/stackblitz-labs/bolt.diy</t>
+          <t>https://github.com/runew0lf/RuinedFooocus</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>2024-10-13T18:40:54Z</t>
+          <t>2023-08-16T09:20:46Z</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2026-03-08T05:14:22Z</t>
+          <t>2026-03-09T18:48:58Z</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>92</v>
+        <v>32</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ditto</t>
+          <t>bolt</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/ditto</t>
+          <t>https://github.com/pinokiofactory/bolt</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2024-10-15T21:29:32Z</t>
+          <t>2024-10-30T04:46:10Z</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2025-11-06T00:05:04Z</t>
+          <t>2026-03-08T17:52:56Z</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2024-10-15T22:47:07Z</t>
+          <t>2025-12-06T21:59:33Z</t>
         </is>
       </c>
       <c r="G98" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>yoheinakajima/ditto</t>
+          <t>stackblitz-labs/bolt.diy</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/yoheinakajima/ditto</t>
+          <t>https://github.com/stackblitz-labs/bolt.diy</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>2024-10-15T19:45:13Z</t>
+          <t>2024-10-13T18:40:54Z</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2025-11-11T07:07:11Z</t>
+          <t>2026-03-15T06:39:41Z</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>8</v>
+        <v>94</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>cogstudio</t>
+          <t>ditto</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/cogstudio</t>
+          <t>https://github.com/pinokiofactory/ditto</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2024-09-20T10:46:17Z</t>
+          <t>2024-10-15T21:29:32Z</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-03-01T16:13:28Z</t>
+          <t>2025-11-06T00:05:04Z</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-01-04T00:47:22Z</t>
+          <t>2024-10-15T22:47:07Z</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>zai-org/CogVideo</t>
+          <t>yoheinakajima/ditto</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/zai-org/CogVideo</t>
+          <t>https://github.com/yoheinakajima/ditto</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>2022-05-29T06:46:18Z</t>
+          <t>2024-10-15T19:45:13Z</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2026-03-08T06:29:40Z</t>
+          <t>2026-03-13T14:44:32Z</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>112</v>
+        <v>8</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>cogvideo</t>
+          <t>cogstudio</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" s="2" t="inlineStr">
         <is>
+          <t>https://github.com/pinokiofactory/cogstudio</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2024-09-20T10:46:17Z</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>2026-03-08T10:01:10Z</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-01-04T00:47:22Z</t>
+        </is>
+      </c>
+      <c r="G100" t="n">
+        <v>37</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>zai-org/CogVideo</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/zai-org/CogVideo</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>2022-05-29T06:46:18Z</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>2026-03-14T21:04:17Z</t>
+        </is>
+      </c>
+      <c r="L100" t="n">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>cogvideo</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
           <t>https://github.com/pinokiofactory/cogvideo</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
+      <c r="D101" t="inlineStr">
         <is>
           <t>2024-08-30T10:13:02Z</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
+      <c r="E101" t="inlineStr">
         <is>
           <t>2026-01-04T01:51:05Z</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
+      <c r="F101" t="inlineStr">
         <is>
           <t>2026-01-04T01:51:01Z</t>
         </is>
       </c>
-      <c r="G100" t="n">
+      <c r="G101" t="n">
         <v>1</v>
       </c>
-      <c r="H100" t="inlineStr">
+      <c r="H101" t="inlineStr">
         <is>
           <t>zai-org/CogVideo</t>
         </is>
       </c>
-      <c r="I100" s="2" t="inlineStr">
+      <c r="I101" s="2" t="inlineStr">
         <is>
           <t>https://github.com/zai-org/CogVideo</t>
         </is>
       </c>
-      <c r="J100" t="inlineStr">
+      <c r="J101" t="inlineStr">
         <is>
           <t>2022-05-29T06:46:18Z</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>2026-01-04T04:24:11Z</t>
-        </is>
-      </c>
-      <c r="L100" t="n">
-        <v>105</v>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>2026-03-14T21:04:17Z</t>
+        </is>
+      </c>
+      <c r="L101" t="n">
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -5097,103 +5137,104 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C52" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C53" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C54" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C56" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C58" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C59" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C60" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C61" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C62" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C63" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C64" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C65" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C66" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C67" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C68" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C69" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C70" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C71" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C72" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C73" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C74" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C75" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C76" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C77" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C78" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C79" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C80" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I80" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C81" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C82" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C83" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I83" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C84" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C85" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C86" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I86" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C87" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I87" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C88" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C89" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I89" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C90" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I90" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C91" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C92" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I92" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C93" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I93" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C94" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I94" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C95" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I95" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C96" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I96" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C97" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I97" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C98" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I98" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C99" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I99" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C100" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I100" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C54" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C56" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C58" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C59" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C60" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C61" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C62" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C63" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C64" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C65" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C66" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C67" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C68" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C69" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C70" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C71" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C72" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C73" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C74" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C75" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C76" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C77" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C78" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C79" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C80" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I80" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C81" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C82" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C83" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I83" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C84" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C85" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C86" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I86" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C87" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I87" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C88" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C89" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I89" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C90" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I90" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C91" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C92" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I92" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C93" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I93" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C94" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I94" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C95" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I95" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C96" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I96" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C97" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I97" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C98" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I98" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C99" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I99" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C100" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I100" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C101" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I101" r:id="rId149"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pinokio_repos.xlsx
+++ b/pinokio_repos.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2025-12-02T21:43:31Z</t>
+          <t>2026-03-21T14:32:12Z</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-02-28T17:33:00Z</t>
+          <t>2026-03-21T02:47:23Z</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-01-24T02:56:20Z</t>
+          <t>2026-03-20T07:27:12Z</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-03-10T07:05:42Z</t>
+          <t>2026-03-18T22:04:05Z</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2025-03-17T00:35:50Z</t>
+          <t>2026-03-18T22:03:59Z</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-02-14T00:58:46Z</t>
+          <t>2026-03-16T07:24:28Z</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-01-29T13:21:03Z</t>
+          <t>2026-03-19T19:59:22Z</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2025-12-19T04:34:32Z</t>
+          <t>2026-03-19T19:59:18Z</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -2707,7 +2707,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-03-14T21:25:05Z</t>
+          <t>2026-03-21T21:55:03Z</t>
         </is>
       </c>
       <c r="L58" t="n">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-03-04T05:39:26Z</t>
+          <t>2026-03-21T22:58:22Z</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2025-12-27T20:44:51Z</t>
+          <t>2026-03-16T18:10:31Z</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-03-13T18:55:15Z</t>
+          <t>2026-03-21T02:42:47Z</t>
         </is>
       </c>
       <c r="L76" t="n">
@@ -4107,12 +4107,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-01-30T21:11:00Z</t>
+          <t>2026-03-22T05:41:30Z</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-01-30T21:10:56Z</t>
+          <t>2026-03-22T05:41:26Z</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -4135,11 +4135,11 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-03-15T07:04:55Z</t>
+          <t>2026-03-22T06:33:42Z</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="85">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-03-09T14:29:40Z</t>
+          <t>2026-03-17T06:54:05Z</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -4413,11 +4413,11 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-03-15T03:25:29Z</t>
+          <t>2026-03-22T05:58:46Z</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="90">
@@ -4659,7 +4659,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-01-02T20:07:27Z</t>
+          <t>2026-03-20T14:31:18Z</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2026-03-15T03:05:10Z</t>
+          <t>2026-03-22T00:00:00Z</t>
         </is>
       </c>
       <c r="L94" t="n">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-03-08T10:01:10Z</t>
+          <t>2026-03-18T06:01:33Z</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>2026-03-14T21:04:17Z</t>
+          <t>2026-03-21T16:53:18Z</t>
         </is>
       </c>
       <c r="L100" t="n">

--- a/pinokio_repos.xlsx
+++ b/pinokio_repos.xlsx
@@ -1137,7 +1137,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-03-10T07:04:46Z</t>
+          <t>2026-03-23T07:33:59Z</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2025-03-16T23:50:32Z</t>
+          <t>2026-03-23T07:24:44Z</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-03-08T17:52:21Z</t>
+          <t>2026-03-28T22:29:22Z</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2025-11-03T21:06:34Z</t>
+          <t>2026-03-26T11:46:55Z</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2025-03-17T00:05:11Z</t>
+          <t>2026-03-23T23:00:40Z</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-03-06T10:06:31Z</t>
+          <t>2026-03-22T21:39:50Z</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-02-20T19:45:32Z</t>
+          <t>2026-03-22T21:39:25Z</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -2595,11 +2595,11 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-03-15T07:05:58Z</t>
+          <t>2026-03-29T07:01:32Z</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>3823</v>
+        <v>3910</v>
       </c>
     </row>
     <row r="57">
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-03-19T19:59:22Z</t>
+          <t>2026-03-22T10:54:11Z</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-19T19:59:18Z</t>
+          <t>2026-03-22T10:54:07Z</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -2707,7 +2707,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-03-21T21:55:03Z</t>
+          <t>2026-03-28T18:00:13Z</t>
         </is>
       </c>
       <c r="L58" t="n">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-03-12T03:14:42Z</t>
+          <t>2026-03-27T19:04:04Z</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2962,7 +2962,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-03-14T08:32:05Z</t>
+          <t>2026-03-28T23:26:32Z</t>
         </is>
       </c>
       <c r="L63" t="n">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-03-13T08:49:46Z</t>
+          <t>2026-03-26T06:25:21Z</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3259,11 +3259,11 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-03-13T17:21:13Z</t>
+          <t>2026-03-29T04:22:54Z</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="69">
@@ -3783,12 +3783,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-03-07T20:45:48Z</t>
+          <t>2026-03-27T19:03:49Z</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-02-20T18:00:24Z</t>
+          <t>2026-03-25T15:50:03Z</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -3811,11 +3811,11 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-03-15T04:06:48Z</t>
+          <t>2026-03-29T06:01:38Z</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>701</v>
+        <v>736</v>
       </c>
     </row>
     <row r="79">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-02-20T18:30:12Z</t>
+          <t>2026-03-25T00:20:15Z</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4467,11 +4467,11 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-03-15T03:03:47Z</t>
+          <t>2026-03-29T05:46:34Z</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>1131</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="91">

--- a/pinokio_repos.xlsx
+++ b/pinokio_repos.xlsx
@@ -569,7 +569,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-12T03:17:46Z</t>
+          <t>2026-03-30T18:41:46Z</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-03-12T02:15:07Z</t>
+          <t>2026-03-30T18:38:50Z</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2025-12-02T22:00:13Z</t>
+          <t>2026-03-30T18:36:45Z</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-03-21T14:32:12Z</t>
+          <t>2026-03-30T18:42:28Z</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2025-10-06T09:31:47Z</t>
+          <t>2026-03-30T18:36:08Z</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-01-13T16:59:17Z</t>
+          <t>2026-03-30T18:20:53Z</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-03-20T07:27:12Z</t>
+          <t>2026-04-01T17:20:27Z</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-03-12T03:43:34Z</t>
+          <t>2026-03-30T19:12:21Z</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2429,7 +2429,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-03-06T09:24:54Z</t>
+          <t>2026-03-15T20:38:15Z</t>
         </is>
       </c>
       <c r="L53" t="n">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-03-13T01:11:18Z</t>
+          <t>2026-04-02T16:49:42Z</t>
         </is>
       </c>
       <c r="L54" t="n">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-03-22T21:39:50Z</t>
+          <t>2026-04-04T01:59:20Z</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-22T21:39:25Z</t>
+          <t>2026-04-04T01:59:16Z</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -2595,11 +2595,11 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-03-29T07:01:32Z</t>
+          <t>2026-04-05T06:09:23Z</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>3910</v>
+        <v>3925</v>
       </c>
     </row>
     <row r="57">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-03-13T14:44:27Z</t>
+          <t>2026-03-20T03:53:47Z</t>
         </is>
       </c>
       <c r="L57" t="n">
@@ -2707,7 +2707,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-03-28T18:00:13Z</t>
+          <t>2026-04-05T06:13:14Z</t>
         </is>
       </c>
       <c r="L58" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-03-15T05:19:39Z</t>
+          <t>2026-04-05T04:54:53Z</t>
         </is>
       </c>
       <c r="L59" t="n">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-03-12T03:33:51Z</t>
+          <t>2026-03-30T18:42:32Z</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2815,11 +2815,11 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-03-10T16:47:25Z</t>
+          <t>2026-04-03T14:53:08Z</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="61">
@@ -2869,11 +2869,11 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-02-27T07:44:24Z</t>
+          <t>2026-04-01T13:38:39Z</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-03-14T09:19:42Z</t>
+          <t>2026-04-04T23:10:33Z</t>
         </is>
       </c>
       <c r="L62" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-03-28T23:26:32Z</t>
+          <t>2026-04-03T20:13:20Z</t>
         </is>
       </c>
       <c r="L63" t="n">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-03-13T21:16:02Z</t>
+          <t>2026-04-04T09:25:07Z</t>
         </is>
       </c>
       <c r="L64" t="n">
@@ -3089,11 +3089,11 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-03-15T05:38:56Z</t>
+          <t>2026-04-05T00:56:12Z</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="66">
@@ -3143,11 +3143,11 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-03-15T05:38:56Z</t>
+          <t>2026-04-05T00:56:12Z</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="67">
@@ -3201,11 +3201,11 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-03-15T07:09:43Z</t>
+          <t>2026-04-04T18:24:09Z</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="68">
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-03-26T06:25:21Z</t>
+          <t>2026-04-04T15:45:31Z</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2025-12-02T22:50:55Z</t>
+          <t>2026-03-30T01:12:28Z</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -3259,11 +3259,11 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-03-29T04:22:54Z</t>
+          <t>2026-04-04T04:21:46Z</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="69">
@@ -3313,11 +3313,11 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-03-15T06:38:12Z</t>
+          <t>2026-04-03T10:17:39Z</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="70">
@@ -3371,11 +3371,11 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-03-15T06:42:41Z</t>
+          <t>2026-04-05T06:23:17Z</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="71">
@@ -3429,7 +3429,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-03-12T09:12:26Z</t>
+          <t>2026-04-02T07:07:06Z</t>
         </is>
       </c>
       <c r="L71" t="n">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-03-14T04:25:07Z</t>
+          <t>2026-04-05T02:16:15Z</t>
         </is>
       </c>
       <c r="L72" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-03-13T23:25:03Z</t>
+          <t>2026-04-02T01:52:24Z</t>
         </is>
       </c>
       <c r="L73" t="n">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-03-14T20:08:39Z</t>
+          <t>2026-04-05T06:14:30Z</t>
         </is>
       </c>
       <c r="L74" t="n">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-03-12T21:01:22Z</t>
+          <t>2026-04-04T18:24:09Z</t>
         </is>
       </c>
       <c r="L75" t="n">
@@ -3684,7 +3684,7 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-03-21T02:42:47Z</t>
+          <t>2026-03-29T22:04:48Z</t>
         </is>
       </c>
       <c r="L76" t="n">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-03-12T03:18:44Z</t>
+          <t>2026-04-01T13:23:40Z</t>
         </is>
       </c>
       <c r="L77" t="n">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-03-27T19:03:49Z</t>
+          <t>2026-04-04T09:37:27Z</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3811,11 +3811,11 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-03-29T06:01:38Z</t>
+          <t>2026-04-05T05:12:41Z</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>736</v>
+        <v>756</v>
       </c>
     </row>
     <row r="79">
@@ -3865,7 +3865,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-03-05T16:08:21Z</t>
+          <t>2026-03-29T22:06:06Z</t>
         </is>
       </c>
       <c r="L79" t="n">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-03-15T05:10:23Z</t>
+          <t>2026-04-05T03:37:26Z</t>
         </is>
       </c>
       <c r="L80" t="n">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-03-14T17:04:12Z</t>
+          <t>2026-04-05T02:15:12Z</t>
         </is>
       </c>
       <c r="L81" t="n">
@@ -4027,11 +4027,11 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-03-15T01:51:06Z</t>
+          <t>2026-04-04T10:00:59Z</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="83">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-03-10T03:23:19Z</t>
+          <t>2026-04-03T19:55:37Z</t>
         </is>
       </c>
       <c r="L83" t="n">
@@ -4135,11 +4135,11 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-03-22T06:33:42Z</t>
+          <t>2026-04-05T07:13:05Z</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>49</v>
+        <v>24</v>
       </c>
     </row>
     <row r="85">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-03-13T07:05:57Z</t>
+          <t>2026-04-03T16:42:42Z</t>
         </is>
       </c>
       <c r="L85" t="n">
@@ -4243,7 +4243,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-03-14T16:00:20Z</t>
+          <t>2026-03-23T21:32:41Z</t>
         </is>
       </c>
       <c r="L86" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-03-13T00:03:55Z</t>
+          <t>2026-04-04T23:33:57Z</t>
         </is>
       </c>
       <c r="L87" t="n">
@@ -4355,7 +4355,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-03-14T00:14:25Z</t>
+          <t>2026-03-31T10:39:36Z</t>
         </is>
       </c>
       <c r="L88" t="n">
@@ -4413,11 +4413,11 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-03-22T05:58:46Z</t>
+          <t>2026-04-05T02:49:42Z</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="90">
@@ -4467,11 +4467,11 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-03-29T05:46:34Z</t>
+          <t>2026-04-05T03:48:07Z</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>1133</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="91">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-03-14T15:37:21Z</t>
+          <t>2026-04-05T05:58:32Z</t>
         </is>
       </c>
       <c r="L91" t="n">
@@ -4575,11 +4575,11 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-03-15T05:24:59Z</t>
+          <t>2026-04-05T07:18:00Z</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>104</v>
+        <v>131</v>
       </c>
     </row>
     <row r="93">
@@ -4629,11 +4629,11 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2026-03-15T00:24:03Z</t>
+          <t>2026-04-05T04:32:54Z</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="94">
@@ -4659,7 +4659,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-03-20T14:31:18Z</t>
+          <t>2026-03-30T18:29:46Z</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2026-03-22T00:00:00Z</t>
+          <t>2026-04-04T09:53:01Z</t>
         </is>
       </c>
       <c r="L94" t="n">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>2026-03-04T19:39:48Z</t>
+          <t>2026-03-31T09:05:56Z</t>
         </is>
       </c>
       <c r="L95" t="n">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2026-03-04T19:39:48Z</t>
+          <t>2026-03-31T09:05:56Z</t>
         </is>
       </c>
       <c r="L96" t="n">
@@ -4861,11 +4861,11 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2026-03-09T18:48:58Z</t>
+          <t>2026-04-04T11:45:51Z</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="98">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-03-08T17:52:56Z</t>
+          <t>2026-04-03T20:26:13Z</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -4915,11 +4915,11 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2026-03-15T06:39:41Z</t>
+          <t>2026-04-05T03:54:21Z</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="99">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2026-03-13T14:44:32Z</t>
+          <t>2026-04-04T07:38:16Z</t>
         </is>
       </c>
       <c r="L99" t="n">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-03-18T06:01:33Z</t>
+          <t>2026-04-01T01:57:33Z</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>2026-03-21T16:53:18Z</t>
+          <t>2026-04-05T07:03:49Z</t>
         </is>
       </c>
       <c r="L100" t="n">
@@ -5077,7 +5077,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>2026-03-14T21:04:17Z</t>
+          <t>2026-04-05T07:03:49Z</t>
         </is>
       </c>
       <c r="L101" t="n">

--- a/pinokio_repos.xlsx
+++ b/pinokio_repos.xlsx
@@ -1969,7 +1969,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-03-28T22:29:22Z</t>
+          <t>2026-04-07T13:14:13Z</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2365,12 +2365,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2025-12-01T19:45:36Z</t>
+          <t>2026-04-06T00:01:08Z</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2025-12-01T15:28:52Z</t>
+          <t>2026-04-06T00:01:05Z</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -2429,7 +2429,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-03-15T20:38:15Z</t>
+          <t>2026-04-10T04:06:55Z</t>
         </is>
       </c>
       <c r="L53" t="n">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-04-02T16:49:42Z</t>
+          <t>2026-04-06T21:09:10Z</t>
         </is>
       </c>
       <c r="L54" t="n">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-04-04T01:59:20Z</t>
+          <t>2026-04-08T02:42:37Z</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2595,11 +2595,11 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-04-05T06:09:23Z</t>
+          <t>2026-04-12T07:21:17Z</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>3925</v>
+        <v>3961</v>
       </c>
     </row>
     <row r="57">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-03-20T03:53:47Z</t>
+          <t>2026-04-10T19:29:17Z</t>
         </is>
       </c>
       <c r="L57" t="n">
@@ -2707,7 +2707,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-04-05T06:13:14Z</t>
+          <t>2026-04-12T01:42:24Z</t>
         </is>
       </c>
       <c r="L58" t="n">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-01-25T06:00:38Z</t>
+          <t>2026-04-07T06:02:19Z</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2761,11 +2761,11 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-04-05T04:54:53Z</t>
+          <t>2026-04-11T22:32:13Z</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="60">
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-04-03T14:53:08Z</t>
+          <t>2026-04-11T03:02:07Z</t>
         </is>
       </c>
       <c r="L60" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-03-12T03:41:40Z</t>
+          <t>2026-04-08T13:24:01Z</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-04-01T13:38:39Z</t>
+          <t>2026-04-08T13:24:08Z</t>
         </is>
       </c>
       <c r="L61" t="n">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-04-04T23:10:33Z</t>
+          <t>2026-04-07T02:55:15Z</t>
         </is>
       </c>
       <c r="L62" t="n">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-03-27T19:04:04Z</t>
+          <t>2026-04-09T06:32:07Z</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-04-03T20:13:20Z</t>
+          <t>2026-04-09T06:30:56Z</t>
         </is>
       </c>
       <c r="L63" t="n">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-04-04T09:25:07Z</t>
+          <t>2026-04-09T10:37:23Z</t>
         </is>
       </c>
       <c r="L64" t="n">
@@ -3089,11 +3089,11 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-04-05T00:56:12Z</t>
+          <t>2026-04-12T07:09:21Z</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="66">
@@ -3143,11 +3143,11 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-04-05T00:56:12Z</t>
+          <t>2026-04-12T07:09:21Z</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="67">
@@ -3201,11 +3201,11 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-04-04T18:24:09Z</t>
+          <t>2026-04-11T04:18:12Z</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="68">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-04-04T15:45:31Z</t>
+          <t>2026-04-11T13:57:08Z</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-04-04T04:21:46Z</t>
+          <t>2026-04-12T02:53:11Z</t>
         </is>
       </c>
       <c r="L68" t="n">
@@ -3313,11 +3313,11 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-04-03T10:17:39Z</t>
+          <t>2026-04-12T05:07:54Z</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="70">
@@ -3371,11 +3371,11 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-04-05T06:23:17Z</t>
+          <t>2026-04-12T04:50:10Z</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="71">
@@ -3429,7 +3429,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-04-02T07:07:06Z</t>
+          <t>2026-04-10T11:43:43Z</t>
         </is>
       </c>
       <c r="L71" t="n">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-04-05T02:16:15Z</t>
+          <t>2026-04-11T11:44:06Z</t>
         </is>
       </c>
       <c r="L72" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-04-02T01:52:24Z</t>
+          <t>2026-04-11T15:51:19Z</t>
         </is>
       </c>
       <c r="L73" t="n">
@@ -3595,11 +3595,11 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-04-05T06:14:30Z</t>
+          <t>2026-04-12T05:57:24Z</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="75">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-04-04T18:24:09Z</t>
+          <t>2026-04-09T18:05:21Z</t>
         </is>
       </c>
       <c r="L75" t="n">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-03-29T22:04:48Z</t>
+          <t>2026-04-09T17:14:53Z</t>
         </is>
       </c>
       <c r="L76" t="n">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-04-04T09:37:27Z</t>
+          <t>2026-04-08T12:51:50Z</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3792,7 +3792,7 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -3811,11 +3811,11 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-04-05T05:12:41Z</t>
+          <t>2026-04-12T07:05:44Z</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>756</v>
+        <v>773</v>
       </c>
     </row>
     <row r="79">
@@ -3865,7 +3865,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-03-29T22:06:06Z</t>
+          <t>2026-04-12T06:24:35Z</t>
         </is>
       </c>
       <c r="L79" t="n">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-04-05T03:37:26Z</t>
+          <t>2026-04-11T20:00:17Z</t>
         </is>
       </c>
       <c r="L80" t="n">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-04-05T02:15:12Z</t>
+          <t>2026-04-11T18:29:47Z</t>
         </is>
       </c>
       <c r="L81" t="n">
@@ -4027,11 +4027,11 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-04-04T10:00:59Z</t>
+          <t>2026-04-11T22:30:31Z</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="83">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-04-03T19:55:37Z</t>
+          <t>2026-04-11T12:47:50Z</t>
         </is>
       </c>
       <c r="L83" t="n">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-04-05T07:13:05Z</t>
+          <t>2026-04-12T07:17:31Z</t>
         </is>
       </c>
       <c r="L84" t="n">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-04-03T16:42:42Z</t>
+          <t>2026-04-12T05:56:50Z</t>
         </is>
       </c>
       <c r="L85" t="n">
@@ -4243,7 +4243,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-03-23T21:32:41Z</t>
+          <t>2026-04-12T05:01:21Z</t>
         </is>
       </c>
       <c r="L86" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-04-04T23:33:57Z</t>
+          <t>2026-04-10T15:09:10Z</t>
         </is>
       </c>
       <c r="L87" t="n">
@@ -4355,7 +4355,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-03-31T10:39:36Z</t>
+          <t>2026-04-10T20:03:26Z</t>
         </is>
       </c>
       <c r="L88" t="n">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-04-05T02:49:42Z</t>
+          <t>2026-04-12T03:17:10Z</t>
         </is>
       </c>
       <c r="L89" t="n">
@@ -4467,11 +4467,11 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-04-05T03:48:07Z</t>
+          <t>2026-04-12T04:31:09Z</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>1135</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="91">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-04-05T05:58:32Z</t>
+          <t>2026-04-12T05:07:52Z</t>
         </is>
       </c>
       <c r="L91" t="n">
@@ -4575,11 +4575,11 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-04-05T07:18:00Z</t>
+          <t>2026-04-12T07:22:05Z</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>131</v>
+        <v>123</v>
       </c>
     </row>
     <row r="93">
@@ -4629,11 +4629,11 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2026-04-05T04:32:54Z</t>
+          <t>2026-04-11T20:52:18Z</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="94">
@@ -4659,7 +4659,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-03-30T18:29:46Z</t>
+          <t>2026-04-06T19:35:04Z</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2026-04-04T09:53:01Z</t>
+          <t>2026-04-12T01:47:37Z</t>
         </is>
       </c>
       <c r="L94" t="n">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>2026-03-31T09:05:56Z</t>
+          <t>2026-04-10T09:19:08Z</t>
         </is>
       </c>
       <c r="L95" t="n">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2026-03-31T09:05:56Z</t>
+          <t>2026-04-10T09:19:08Z</t>
         </is>
       </c>
       <c r="L96" t="n">
@@ -4861,11 +4861,11 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2026-04-04T11:45:51Z</t>
+          <t>2026-04-11T20:43:27Z</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="98">
@@ -4915,11 +4915,11 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2026-04-05T03:54:21Z</t>
+          <t>2026-04-12T05:07:52Z</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="99">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2026-04-04T07:38:16Z</t>
+          <t>2026-04-09T07:54:05Z</t>
         </is>
       </c>
       <c r="L99" t="n">
@@ -5023,11 +5023,11 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>2026-04-05T07:03:49Z</t>
+          <t>2026-04-12T06:39:56Z</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="101">
@@ -5077,11 +5077,11 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>2026-04-05T07:03:49Z</t>
+          <t>2026-04-12T06:39:56Z</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/pinokio_repos.xlsx
+++ b/pinokio_repos.xlsx
@@ -569,7 +569,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-30T18:41:46Z</t>
+          <t>2026-04-17T16:00:19Z</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-01-18T13:15:57Z</t>
+          <t>2026-04-12T17:44:47Z</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-02-26T20:36:40Z</t>
+          <t>2026-04-13T20:17:06Z</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-04-09T06:32:07Z</t>
+          <t>2026-04-17T10:54:40Z</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-04-09T06:30:56Z</t>
+          <t>2026-04-17T21:56:19Z</t>
         </is>
       </c>
       <c r="L63" t="n">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-04-11T13:57:08Z</t>
+          <t>2026-04-18T13:02:19Z</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3259,11 +3259,11 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-04-12T02:53:11Z</t>
+          <t>2026-04-19T04:02:51Z</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="69">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-01-19T16:49:14Z</t>
+          <t>2026-04-17T16:26:23Z</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-04-01T13:23:40Z</t>
+          <t>2026-04-16T10:48:20Z</t>
         </is>
       </c>
       <c r="L77" t="n">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-03-22T05:41:30Z</t>
+          <t>2026-04-14T16:10:59Z</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -4116,7 +4116,7 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -4135,11 +4135,11 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-04-12T07:17:31Z</t>
+          <t>2026-04-19T06:23:05Z</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="85">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-04-03T20:26:13Z</t>
+          <t>2026-04-12T19:37:55Z</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -4896,7 +4896,7 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -4915,11 +4915,11 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2026-04-12T05:07:52Z</t>
+          <t>2026-04-19T04:45:36Z</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>96</v>
+        <v>102</v>
       </c>
     </row>
     <row r="99">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-04-01T01:57:33Z</t>
+          <t>2026-04-17T17:31:36Z</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>2026-04-12T06:39:56Z</t>
+          <t>2026-04-19T06:35:54Z</t>
         </is>
       </c>
       <c r="L100" t="n">

--- a/pinokio_repos.xlsx
+++ b/pinokio_repos.xlsx
@@ -1713,12 +1713,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-03-18T22:04:05Z</t>
+          <t>2026-04-24T20:51:19Z</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-18T22:03:59Z</t>
+          <t>2026-04-24T20:51:14Z</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-01-10T21:15:09Z</t>
+          <t>2026-04-23T19:53:52Z</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-01-10T21:15:05Z</t>
+          <t>2026-04-23T19:53:48Z</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-03-26T11:46:55Z</t>
+          <t>2026-04-25T02:38:23Z</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-23T23:00:40Z</t>
+          <t>2026-04-25T02:38:19Z</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -2429,7 +2429,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-04-10T04:06:55Z</t>
+          <t>2026-04-25T18:06:06Z</t>
         </is>
       </c>
       <c r="L53" t="n">
@@ -2595,11 +2595,11 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-04-12T07:21:17Z</t>
+          <t>2026-04-26T07:39:56Z</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>3961</v>
+        <v>3985</v>
       </c>
     </row>
     <row r="57">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-04-10T19:29:17Z</t>
+          <t>2026-04-17T03:43:29Z</t>
         </is>
       </c>
       <c r="L57" t="n">
@@ -2688,7 +2688,7 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-04-12T01:42:24Z</t>
+          <t>2026-04-26T07:23:29Z</t>
         </is>
       </c>
       <c r="L58" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-04-11T22:32:13Z</t>
+          <t>2026-04-26T06:42:42Z</t>
         </is>
       </c>
       <c r="L59" t="n">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-03-30T18:42:32Z</t>
+          <t>2026-04-25T11:27:59Z</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2815,11 +2815,11 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-04-11T03:02:07Z</t>
+          <t>2026-04-23T16:25:32Z</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="61">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-04-08T13:24:08Z</t>
+          <t>2026-04-22T16:07:49Z</t>
         </is>
       </c>
       <c r="L61" t="n">
@@ -2923,11 +2923,11 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-04-07T02:55:15Z</t>
+          <t>2026-04-25T22:20:25Z</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="63">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-04-17T10:54:40Z</t>
+          <t>2026-04-26T01:29:04Z</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-04-17T21:56:19Z</t>
+          <t>2026-04-26T06:49:38Z</t>
         </is>
       </c>
       <c r="L63" t="n">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-04-09T10:37:23Z</t>
+          <t>2026-04-14T19:52:07Z</t>
         </is>
       </c>
       <c r="L64" t="n">
@@ -3089,7 +3089,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-04-12T07:09:21Z</t>
+          <t>2026-04-26T07:06:46Z</t>
         </is>
       </c>
       <c r="L65" t="n">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-04-12T07:09:21Z</t>
+          <t>2026-04-26T07:06:46Z</t>
         </is>
       </c>
       <c r="L66" t="n">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-04-11T04:18:12Z</t>
+          <t>2026-04-25T14:07:08Z</t>
         </is>
       </c>
       <c r="L67" t="n">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-04-18T13:02:19Z</t>
+          <t>2026-04-26T04:35:19Z</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3259,11 +3259,11 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-04-19T04:02:51Z</t>
+          <t>2026-04-26T05:47:12Z</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="69">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-04-12T05:07:54Z</t>
+          <t>2026-04-24T09:39:36Z</t>
         </is>
       </c>
       <c r="L69" t="n">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-04-12T04:50:10Z</t>
+          <t>2026-04-25T20:32:05Z</t>
         </is>
       </c>
       <c r="L70" t="n">
@@ -3429,7 +3429,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-04-10T11:43:43Z</t>
+          <t>2026-04-25T14:10:32Z</t>
         </is>
       </c>
       <c r="L71" t="n">
@@ -3455,12 +3455,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2025-12-06T05:47:59Z</t>
+          <t>2026-04-24T00:59:26Z</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2025-12-06T05:47:56Z</t>
+          <t>2026-04-24T00:59:21Z</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-04-11T11:44:06Z</t>
+          <t>2026-04-26T04:25:29Z</t>
         </is>
       </c>
       <c r="L72" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-04-11T15:51:19Z</t>
+          <t>2026-04-25T06:14:28Z</t>
         </is>
       </c>
       <c r="L73" t="n">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-04-12T05:57:24Z</t>
+          <t>2026-04-26T07:13:58Z</t>
         </is>
       </c>
       <c r="L74" t="n">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-04-09T18:05:21Z</t>
+          <t>2026-04-22T06:48:20Z</t>
         </is>
       </c>
       <c r="L75" t="n">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-03-21T22:58:22Z</t>
+          <t>2026-04-23T19:59:25Z</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-16T18:10:31Z</t>
+          <t>2026-04-23T19:59:21Z</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-04-09T17:14:53Z</t>
+          <t>2026-04-26T03:45:59Z</t>
         </is>
       </c>
       <c r="L76" t="n">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-04-16T10:48:20Z</t>
+          <t>2026-04-24T20:06:05Z</t>
         </is>
       </c>
       <c r="L77" t="n">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-04-08T12:51:50Z</t>
+          <t>2026-04-20T03:31:12Z</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3792,7 +3792,7 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -3811,11 +3811,11 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-04-12T07:05:44Z</t>
+          <t>2026-04-26T07:33:25Z</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>773</v>
+        <v>802</v>
       </c>
     </row>
     <row r="79">
@@ -3865,7 +3865,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-04-12T06:24:35Z</t>
+          <t>2026-04-24T20:06:37Z</t>
         </is>
       </c>
       <c r="L79" t="n">
@@ -3919,11 +3919,11 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-04-11T20:00:17Z</t>
+          <t>2026-04-26T04:30:59Z</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="81">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-04-11T18:29:47Z</t>
+          <t>2026-04-24T20:30:12Z</t>
         </is>
       </c>
       <c r="L81" t="n">
@@ -4027,11 +4027,11 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-04-11T22:30:31Z</t>
+          <t>2026-04-26T02:25:38Z</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="83">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-04-11T12:47:50Z</t>
+          <t>2026-04-23T11:49:32Z</t>
         </is>
       </c>
       <c r="L83" t="n">
@@ -4107,12 +4107,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-04-14T16:10:59Z</t>
+          <t>2026-04-25T02:45:18Z</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-03-22T05:41:26Z</t>
+          <t>2026-04-25T02:45:14Z</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -4135,11 +4135,11 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-04-19T06:23:05Z</t>
+          <t>2026-04-26T07:28:47Z</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="85">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-04-12T05:56:50Z</t>
+          <t>2026-04-23T13:16:22Z</t>
         </is>
       </c>
       <c r="L85" t="n">
@@ -4282,7 +4282,7 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-04-10T15:09:10Z</t>
+          <t>2026-04-26T04:00:36Z</t>
         </is>
       </c>
       <c r="L87" t="n">
@@ -4355,7 +4355,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-04-10T20:03:26Z</t>
+          <t>2026-04-24T05:51:43Z</t>
         </is>
       </c>
       <c r="L88" t="n">
@@ -4413,11 +4413,11 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-04-12T03:17:10Z</t>
+          <t>2026-04-26T05:49:01Z</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="90">
@@ -4467,11 +4467,11 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-04-12T04:31:09Z</t>
+          <t>2026-04-26T06:15:19Z</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>1137</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="91">
@@ -4521,11 +4521,11 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-04-12T05:07:52Z</t>
+          <t>2026-04-25T23:50:40Z</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="92">
@@ -4575,11 +4575,11 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-04-12T07:22:05Z</t>
+          <t>2026-04-26T07:48:32Z</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>123</v>
+        <v>133</v>
       </c>
     </row>
     <row r="93">
@@ -4629,11 +4629,11 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2026-04-11T20:52:18Z</t>
+          <t>2026-04-26T05:05:38Z</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="94">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2026-04-12T01:47:37Z</t>
+          <t>2026-04-26T07:38:08Z</t>
         </is>
       </c>
       <c r="L94" t="n">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>2026-04-10T09:19:08Z</t>
+          <t>2026-04-22T07:48:52Z</t>
         </is>
       </c>
       <c r="L95" t="n">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2026-04-10T09:19:08Z</t>
+          <t>2026-04-22T07:48:52Z</t>
         </is>
       </c>
       <c r="L96" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2026-04-11T20:43:27Z</t>
+          <t>2026-04-26T04:46:38Z</t>
         </is>
       </c>
       <c r="L97" t="n">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-04-12T19:37:55Z</t>
+          <t>2026-04-25T15:48:50Z</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -4915,11 +4915,11 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2026-04-19T04:45:36Z</t>
+          <t>2026-04-26T06:10:49Z</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="99">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2026-04-09T07:54:05Z</t>
+          <t>2026-04-18T18:02:01Z</t>
         </is>
       </c>
       <c r="L99" t="n">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>2026-04-19T06:35:54Z</t>
+          <t>2026-04-25T21:40:40Z</t>
         </is>
       </c>
       <c r="L100" t="n">
@@ -5077,7 +5077,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>2026-04-12T06:39:56Z</t>
+          <t>2026-04-25T21:40:40Z</t>
         </is>
       </c>
       <c r="L101" t="n">

--- a/pinokio_repos.xlsx
+++ b/pinokio_repos.xlsx
@@ -609,7 +609,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-03-30T18:38:50Z</t>
+          <t>2026-04-29T14:14:09Z</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-01-04T05:07:11Z</t>
+          <t>2026-04-30T01:01:36Z</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1101,12 +1101,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-03-30T18:20:53Z</t>
+          <t>2026-04-30T23:13:48Z</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-01-13T16:59:11Z</t>
+          <t>2026-04-30T23:13:43Z</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -1569,12 +1569,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-04-01T17:20:27Z</t>
+          <t>2026-05-01T00:58:59Z</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-01-06T14:59:02Z</t>
+          <t>2026-05-01T00:58:55Z</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-04-13T20:17:06Z</t>
+          <t>2026-04-28T21:38:17Z</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-02-26T20:36:35Z</t>
+          <t>2026-04-28T21:38:12Z</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-04-08T02:42:37Z</t>
+          <t>2026-04-27T03:11:23Z</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-04T01:59:16Z</t>
+          <t>2026-04-27T03:11:19Z</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -2595,11 +2595,11 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-04-26T07:39:56Z</t>
+          <t>2026-05-03T08:09:04Z</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>3985</v>
+        <v>4016</v>
       </c>
     </row>
     <row r="57">
@@ -2621,12 +2621,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2025-03-17T00:02:40Z</t>
+          <t>2026-04-30T23:53:07Z</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2025-03-17T00:02:36Z</t>
+          <t>2026-04-30T23:53:01Z</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -2707,7 +2707,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-04-26T07:23:29Z</t>
+          <t>2026-05-02T21:06:48Z</t>
         </is>
       </c>
       <c r="L58" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-04-07T06:02:19Z</t>
+          <t>2026-04-28T23:37:23Z</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-01-25T06:00:34Z</t>
+          <t>2026-04-28T23:37:19Z</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-04-26T06:42:42Z</t>
+          <t>2026-05-03T07:12:35Z</t>
         </is>
       </c>
       <c r="L59" t="n">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-04-23T16:25:32Z</t>
+          <t>2026-04-26T17:53:52Z</t>
         </is>
       </c>
       <c r="L60" t="n">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-04-22T16:07:49Z</t>
+          <t>2026-05-03T06:49:04Z</t>
         </is>
       </c>
       <c r="L61" t="n">
@@ -2923,11 +2923,11 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-04-25T22:20:25Z</t>
+          <t>2026-05-03T04:35:06Z</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="63">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-04-26T01:29:04Z</t>
+          <t>2026-05-01T08:20:29Z</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-04-26T06:49:38Z</t>
+          <t>2026-05-01T21:04:20Z</t>
         </is>
       </c>
       <c r="L63" t="n">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-04-14T19:52:07Z</t>
+          <t>2026-05-02T00:10:01Z</t>
         </is>
       </c>
       <c r="L64" t="n">
@@ -3089,7 +3089,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-04-26T07:06:46Z</t>
+          <t>2026-05-03T06:13:38Z</t>
         </is>
       </c>
       <c r="L65" t="n">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-04-26T07:06:46Z</t>
+          <t>2026-05-03T06:13:38Z</t>
         </is>
       </c>
       <c r="L66" t="n">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-04-25T14:07:08Z</t>
+          <t>2026-04-30T02:46:00Z</t>
         </is>
       </c>
       <c r="L67" t="n">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-04-26T04:35:19Z</t>
+          <t>2026-04-27T09:23:24Z</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3240,7 +3240,7 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-04-26T05:47:12Z</t>
+          <t>2026-05-02T19:34:26Z</t>
         </is>
       </c>
       <c r="L68" t="n">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-04-24T09:39:36Z</t>
+          <t>2026-05-01T15:05:33Z</t>
         </is>
       </c>
       <c r="L69" t="n">
@@ -3371,11 +3371,11 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-04-25T20:32:05Z</t>
+          <t>2026-05-03T05:20:18Z</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="71">
@@ -3429,7 +3429,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-04-25T14:10:32Z</t>
+          <t>2026-05-03T05:48:59Z</t>
         </is>
       </c>
       <c r="L71" t="n">
@@ -3455,12 +3455,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-04-24T00:59:26Z</t>
+          <t>2026-04-28T23:29:48Z</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-24T00:59:21Z</t>
+          <t>2026-04-28T23:29:43Z</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-04-26T04:25:29Z</t>
+          <t>2026-05-02T20:48:54Z</t>
         </is>
       </c>
       <c r="L72" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-04-25T06:14:28Z</t>
+          <t>2026-05-03T00:00:27Z</t>
         </is>
       </c>
       <c r="L73" t="n">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-04-26T07:13:58Z</t>
+          <t>2026-05-02T23:23:36Z</t>
         </is>
       </c>
       <c r="L74" t="n">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-04-22T06:48:20Z</t>
+          <t>2026-05-02T09:43:14Z</t>
         </is>
       </c>
       <c r="L75" t="n">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-04-26T03:45:59Z</t>
+          <t>2026-04-29T11:55:54Z</t>
         </is>
       </c>
       <c r="L76" t="n">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-04-24T20:06:05Z</t>
+          <t>2026-05-02T15:39:29Z</t>
         </is>
       </c>
       <c r="L77" t="n">
@@ -3783,12 +3783,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-04-20T03:31:12Z</t>
+          <t>2026-04-29T04:48:58Z</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-25T15:50:03Z</t>
+          <t>2026-04-29T04:48:55Z</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -3811,11 +3811,11 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-04-26T07:33:25Z</t>
+          <t>2026-05-03T04:44:44Z</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>802</v>
+        <v>810</v>
       </c>
     </row>
     <row r="79">
@@ -3865,7 +3865,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-04-24T20:06:37Z</t>
+          <t>2026-05-02T15:38:09Z</t>
         </is>
       </c>
       <c r="L79" t="n">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-04-26T04:30:59Z</t>
+          <t>2026-05-03T05:56:07Z</t>
         </is>
       </c>
       <c r="L80" t="n">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-04-24T20:30:12Z</t>
+          <t>2026-05-03T04:51:58Z</t>
         </is>
       </c>
       <c r="L81" t="n">
@@ -4027,11 +4027,11 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-04-26T02:25:38Z</t>
+          <t>2026-05-02T12:49:34Z</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="83">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-04-23T11:49:32Z</t>
+          <t>2026-05-01T18:11:07Z</t>
         </is>
       </c>
       <c r="L83" t="n">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-04-25T02:45:18Z</t>
+          <t>2026-04-28T21:58:57Z</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -4135,11 +4135,11 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-04-26T07:28:47Z</t>
+          <t>2026-05-03T07:35:54Z</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="85">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-04-23T13:16:22Z</t>
+          <t>2026-05-01T11:29:35Z</t>
         </is>
       </c>
       <c r="L85" t="n">
@@ -4243,7 +4243,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-04-12T05:01:21Z</t>
+          <t>2026-04-26T09:51:50Z</t>
         </is>
       </c>
       <c r="L86" t="n">
@@ -4301,11 +4301,11 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-04-26T04:00:36Z</t>
+          <t>2026-05-03T05:24:08Z</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="88">
@@ -4355,7 +4355,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-04-24T05:51:43Z</t>
+          <t>2026-05-01T13:37:09Z</t>
         </is>
       </c>
       <c r="L88" t="n">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-04-26T05:49:01Z</t>
+          <t>2026-05-03T06:43:09Z</t>
         </is>
       </c>
       <c r="L89" t="n">
@@ -4439,12 +4439,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-03-25T00:20:15Z</t>
+          <t>2026-04-28T22:51:49Z</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-02-10T03:05:55Z</t>
+          <t>2026-04-28T22:51:44Z</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -4467,11 +4467,11 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-04-26T06:15:19Z</t>
+          <t>2026-05-03T06:42:54Z</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>1138</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="91">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-04-25T23:50:40Z</t>
+          <t>2026-05-03T07:54:03Z</t>
         </is>
       </c>
       <c r="L91" t="n">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-02-01T06:38:32Z</t>
+          <t>2026-04-30T14:45:13Z</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4575,11 +4575,11 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-04-26T07:48:32Z</t>
+          <t>2026-05-03T07:41:17Z</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>133</v>
+        <v>150</v>
       </c>
     </row>
     <row r="93">
@@ -4629,7 +4629,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2026-04-26T05:05:38Z</t>
+          <t>2026-05-02T23:57:41Z</t>
         </is>
       </c>
       <c r="L93" t="n">
@@ -4659,7 +4659,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-04-06T19:35:04Z</t>
+          <t>2026-04-26T09:52:27Z</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2026-04-26T07:38:08Z</t>
+          <t>2026-04-29T14:21:51Z</t>
         </is>
       </c>
       <c r="L94" t="n">
@@ -4861,11 +4861,11 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2026-04-26T04:46:38Z</t>
+          <t>2026-05-02T17:57:29Z</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="98">
@@ -4915,11 +4915,11 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2026-04-26T06:10:49Z</t>
+          <t>2026-05-02T20:32:27Z</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="99">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2026-04-18T18:02:01Z</t>
+          <t>2026-05-01T19:29:34Z</t>
         </is>
       </c>
       <c r="L99" t="n">
@@ -4995,12 +4995,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-04-17T17:31:36Z</t>
+          <t>2026-05-01T02:35:28Z</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-01-04T00:47:22Z</t>
+          <t>2026-05-01T02:35:24Z</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>2026-04-25T21:40:40Z</t>
+          <t>2026-05-02T21:59:21Z</t>
         </is>
       </c>
       <c r="L100" t="n">
@@ -5049,12 +5049,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-01-04T01:51:05Z</t>
+          <t>2026-05-01T02:00:24Z</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-01-04T01:51:01Z</t>
+          <t>2026-05-01T02:00:20Z</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -5077,7 +5077,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>2026-04-25T21:40:40Z</t>
+          <t>2026-05-02T21:59:21Z</t>
         </is>
       </c>
       <c r="L101" t="n">

--- a/pinokio_repos.xlsx
+++ b/pinokio_repos.xlsx
@@ -845,7 +845,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-04-30T01:01:36Z</t>
+          <t>2026-05-09T10:15:00Z</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-03-22T10:54:11Z</t>
+          <t>2026-05-08T22:45:10Z</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-22T10:54:07Z</t>
+          <t>2026-05-08T22:45:06Z</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -2707,7 +2707,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-05-02T21:06:48Z</t>
+          <t>2026-05-10T00:11:59Z</t>
         </is>
       </c>
       <c r="L58" t="n">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-05-01T08:20:29Z</t>
+          <t>2026-05-07T07:27:56Z</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-05-01T21:04:20Z</t>
+          <t>2026-05-08T23:22:12Z</t>
         </is>
       </c>
       <c r="L63" t="n">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-04-27T09:23:24Z</t>
+          <t>2026-05-09T03:23:48Z</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3259,11 +3259,11 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-05-02T19:34:26Z</t>
+          <t>2026-05-10T03:39:06Z</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="69">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-03-10T07:03:48Z</t>
+          <t>2026-05-05T13:33:04Z</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3429,7 +3429,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-05-03T05:48:59Z</t>
+          <t>2026-05-07T13:30:37Z</t>
         </is>
       </c>
       <c r="L71" t="n">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-01-20T23:36:49Z</t>
+          <t>2026-05-10T01:53:27Z</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -4301,11 +4301,11 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-05-03T05:24:08Z</t>
+          <t>2026-05-09T14:14:42Z</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="88">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-05-01T02:35:28Z</t>
+          <t>2026-05-04T21:34:13Z</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>2026-05-02T21:59:21Z</t>
+          <t>2026-05-10T07:34:24Z</t>
         </is>
       </c>
       <c r="L100" t="n">

--- a/pinokio_repos.xlsx
+++ b/pinokio_repos.xlsx
@@ -957,7 +957,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-01-09T05:42:47Z</t>
+          <t>2026-05-16T10:54:13Z</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-05-01T00:58:59Z</t>
+          <t>2026-05-15T21:22:01Z</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-04-27T03:11:23Z</t>
+          <t>2026-05-14T12:58:11Z</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2595,11 +2595,11 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-05-03T08:09:04Z</t>
+          <t>2026-05-17T08:19:27Z</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>4016</v>
+        <v>4011</v>
       </c>
     </row>
     <row r="57">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-05-07T07:27:56Z</t>
+          <t>2026-05-12T18:31:44Z</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-05-08T23:22:12Z</t>
+          <t>2026-05-16T09:37:12Z</t>
         </is>
       </c>
       <c r="L63" t="n">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-05-09T03:23:48Z</t>
+          <t>2026-05-16T05:08:58Z</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3259,11 +3259,11 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-05-10T03:39:06Z</t>
+          <t>2026-05-17T07:52:51Z</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="69">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-04-28T22:51:49Z</t>
+          <t>2026-05-15T18:54:36Z</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4467,11 +4467,11 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-05-03T06:42:54Z</t>
+          <t>2026-05-17T07:49:42Z</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>1140</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="91">

--- a/pinokio_repos.xlsx
+++ b/pinokio_repos.xlsx
@@ -1317,12 +1317,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-03-21T02:47:23Z</t>
+          <t>2026-05-23T20:26:54Z</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2025-12-20T20:47:38Z</t>
+          <t>2026-05-23T20:26:50Z</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-05-08T22:45:10Z</t>
+          <t>2026-05-23T20:30:07Z</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-05-08T22:45:06Z</t>
+          <t>2026-05-23T20:30:03Z</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -2707,11 +2707,11 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-05-10T00:11:59Z</t>
+          <t>2026-05-24T08:27:37Z</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="59">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-05-12T18:31:44Z</t>
+          <t>2026-05-18T11:10:13Z</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-05-16T09:37:12Z</t>
+          <t>2026-05-22T07:49:36Z</t>
         </is>
       </c>
       <c r="L63" t="n">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-05-16T05:08:58Z</t>
+          <t>2026-05-23T14:30:03Z</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-05-17T07:52:51Z</t>
+          <t>2026-05-24T03:34:45Z</t>
         </is>
       </c>
       <c r="L68" t="n">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-04-29T04:48:58Z</t>
+          <t>2026-05-20T05:52:58Z</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3811,11 +3811,11 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-05-03T04:44:44Z</t>
+          <t>2026-05-24T08:34:56Z</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>810</v>
+        <v>852</v>
       </c>
     </row>
     <row r="79">
@@ -4273,16 +4273,16 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-05-10T01:53:27Z</t>
+          <t>2026-05-23T20:32:52Z</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-01-09T00:52:01Z</t>
+          <t>2026-05-23T20:32:48Z</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -4301,11 +4301,11 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-05-09T14:14:42Z</t>
+          <t>2026-05-23T20:36:11Z</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="88">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2025-12-04T18:28:05Z</t>
+          <t>2026-05-18T00:26:24Z</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -4355,7 +4355,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-05-01T13:37:09Z</t>
+          <t>2026-05-23T13:24:48Z</t>
         </is>
       </c>
       <c r="L88" t="n">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-03-17T06:54:05Z</t>
+          <t>2026-05-24T02:17:34Z</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2025-12-18T10:04:19Z</t>
+          <t>2026-05-24T02:17:30Z</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -4413,11 +4413,11 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-05-03T06:43:09Z</t>
+          <t>2026-05-23T23:50:10Z</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>481</v>
+        <v>485</v>
       </c>
     </row>
     <row r="90">

--- a/pinokio_repos.xlsx
+++ b/pinokio_repos.xlsx
@@ -1245,12 +1245,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-03-01T17:52:15Z</t>
+          <t>2026-05-25T01:57:13Z</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2025-04-15T20:43:01Z</t>
+          <t>2026-05-25T01:57:08Z</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -1389,12 +1389,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2025-12-04T03:24:42Z</t>
+          <t>2026-05-26T19:29:06Z</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2025-12-04T03:24:37Z</t>
+          <t>2026-05-26T19:29:02Z</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-02-06T04:29:23Z</t>
+          <t>2026-05-26T15:38:52Z</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-01-12T03:44:31Z</t>
+          <t>2026-05-27T01:42:51Z</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2025-12-04T05:43:02Z</t>
+          <t>2026-05-27T01:42:47Z</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-03-07T20:08:42Z</t>
+          <t>2026-05-26T19:49:18Z</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2025-12-02T23:04:48Z</t>
+          <t>2026-05-26T19:49:13Z</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-04-25T11:27:59Z</t>
+          <t>2026-05-28T20:33:04Z</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-04-26T17:53:52Z</t>
+          <t>2026-05-29T22:40:51Z</t>
         </is>
       </c>
       <c r="L60" t="n">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-05-18T11:10:13Z</t>
+          <t>2026-05-26T19:25:32Z</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-05-22T07:49:36Z</t>
+          <t>2026-05-29T14:08:04Z</t>
         </is>
       </c>
       <c r="L63" t="n">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-05-23T14:30:03Z</t>
+          <t>2026-05-30T06:50:16Z</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3259,11 +3259,11 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-05-24T03:34:45Z</t>
+          <t>2026-05-31T04:32:08Z</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="69">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-03-13T16:05:10Z</t>
+          <t>2026-05-25T01:01:31Z</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2025-12-06T22:44:52Z</t>
+          <t>2026-05-25T01:01:26Z</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-05-01T15:05:33Z</t>
+          <t>2026-05-30T10:02:43Z</t>
         </is>
       </c>
       <c r="L69" t="n">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2025-12-02T22:52:18Z</t>
+          <t>2026-05-28T03:05:24Z</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2025-12-02T22:52:15Z</t>
+          <t>2026-05-28T03:05:19Z</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -4243,7 +4243,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-04-26T09:51:50Z</t>
+          <t>2026-05-31T04:54:18Z</t>
         </is>
       </c>
       <c r="L86" t="n">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-05-18T00:26:24Z</t>
+          <t>2026-05-25T01:05:38Z</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2025-12-04T18:28:01Z</t>
+          <t>2026-05-25T01:05:35Z</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -4355,7 +4355,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-05-23T13:24:48Z</t>
+          <t>2026-05-30T01:54:22Z</t>
         </is>
       </c>
       <c r="L88" t="n">
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2025-12-07T19:55:02Z</t>
+          <t>2026-05-25T00:57:28Z</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2025-12-07T19:54:59Z</t>
+          <t>2026-05-25T00:57:23Z</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -4629,11 +4629,11 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2026-05-02T23:57:41Z</t>
+          <t>2026-05-31T03:36:41Z</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="94">
@@ -4659,16 +4659,16 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-04-26T09:52:27Z</t>
+          <t>2026-05-28T08:16:37Z</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2025-12-02T22:18:28Z</t>
+          <t>2026-05-28T08:16:33Z</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2026-04-29T14:21:51Z</t>
+          <t>2026-05-30T10:02:36Z</t>
         </is>
       </c>
       <c r="L94" t="n">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2025-12-04T05:36:24Z</t>
+          <t>2026-05-26T19:25:15Z</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2025-12-04T05:36:20Z</t>
+          <t>2026-05-26T19:25:11Z</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2026-04-22T07:48:52Z</t>
+          <t>2026-05-19T12:52:07Z</t>
         </is>
       </c>
       <c r="L96" t="n">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-05-04T21:34:13Z</t>
+          <t>2026-05-31T00:51:08Z</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -5004,7 +5004,7 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>2026-05-10T07:34:24Z</t>
+          <t>2026-05-31T06:59:53Z</t>
         </is>
       </c>
       <c r="L100" t="n">

--- a/pinokio_repos.xlsx
+++ b/pinokio_repos.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L101"/>
+  <dimension ref="A1:L102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -609,7 +609,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-04-29T14:14:09Z</t>
+          <t>2026-06-05T20:00:37Z</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -941,32 +941,36 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ai-video-composer</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
+          <t>ai-toolkit</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>A Pinokio installer for Ostris' ai-toolkit, The ultimate training toolkit for finetuning diffusion models. Main branch is [NVIDIA ONLY]</t>
+        </is>
+      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/ai-video-composer</t>
+          <t>https://github.com/pinokiofactory/ai-toolkit</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2024-11-26T00:57:07Z</t>
+          <t>2025-07-26T13:41:13Z</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-05-16T10:54:13Z</t>
+          <t>2026-06-07T02:25:57Z</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2025-12-02T22:14:35Z</t>
+          <t>2026-06-07T03:19:39Z</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
@@ -977,32 +981,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>applio-old</t>
+          <t>ai-video-composer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/applio-old</t>
+          <t>https://github.com/pinokiofactory/ai-video-composer</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2024-06-17T22:35:00Z</t>
+          <t>2024-11-26T00:57:07Z</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024-09-12T13:25:42Z</t>
+          <t>2026-05-16T10:54:13Z</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2024-06-24T21:39:45Z</t>
+          <t>2025-12-02T22:14:35Z</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
@@ -1013,32 +1017,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>artist</t>
+          <t>applio-old</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/artist</t>
+          <t>https://github.com/pinokiofactory/applio-old</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2024-07-30T14:02:34Z</t>
+          <t>2024-06-17T22:35:00Z</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2025-04-23T21:33:35Z</t>
+          <t>2024-09-12T13:25:42Z</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2025-04-23T21:33:31Z</t>
+          <t>2024-06-24T21:39:45Z</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
@@ -1049,28 +1053,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>augmentoolkit</t>
+          <t>artist</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/augmentoolkit</t>
+          <t>https://github.com/pinokiofactory/artist</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2024-05-16T12:39:35Z</t>
+          <t>2024-07-30T14:02:34Z</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024-10-19T17:14:02Z</t>
+          <t>2025-04-23T21:33:35Z</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2024-08-15T01:13:13Z</t>
+          <t>2025-04-23T21:33:31Z</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -1085,28 +1089,28 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>aura-sr-upscaler</t>
+          <t>augmentoolkit</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/aura-sr-upscaler</t>
+          <t>https://github.com/pinokiofactory/augmentoolkit</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2024-07-31T12:18:57Z</t>
+          <t>2024-05-16T12:39:35Z</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-04-30T23:13:48Z</t>
+          <t>2024-10-19T17:14:02Z</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-30T23:13:43Z</t>
+          <t>2024-08-15T01:13:13Z</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -1121,32 +1125,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>autogpt</t>
+          <t>aura-sr-upscaler</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/autogpt</t>
+          <t>https://github.com/pinokiofactory/aura-sr-upscaler</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2024-07-19T14:00:12Z</t>
+          <t>2024-07-31T12:18:57Z</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-03-23T07:33:59Z</t>
+          <t>2026-04-30T23:13:48Z</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2024-09-11T05:57:21Z</t>
+          <t>2026-04-30T23:13:43Z</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
@@ -1157,32 +1161,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>controlyourself</t>
+          <t>autogpt</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/controlyourself</t>
+          <t>https://github.com/pinokiofactory/autogpt</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2024-11-26T09:11:44Z</t>
+          <t>2024-07-19T14:00:12Z</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024-11-26T11:00:33Z</t>
+          <t>2026-03-23T07:33:59Z</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2024-11-26T11:00:30Z</t>
+          <t>2024-09-11T05:57:21Z</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
@@ -1193,32 +1197,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>diffrhythm</t>
+          <t>controlyourself</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/diffrhythm</t>
+          <t>https://github.com/pinokiofactory/controlyourself</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-03-04T22:13:30Z</t>
+          <t>2024-11-26T09:11:44Z</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-01-15T18:34:00Z</t>
+          <t>2024-11-26T11:00:33Z</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2025-12-05T01:50:29Z</t>
+          <t>2024-11-26T11:00:30Z</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
@@ -1229,32 +1233,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>diffusers-image-fill</t>
+          <t>diffrhythm</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/diffusers-image-fill</t>
+          <t>https://github.com/pinokiofactory/diffrhythm</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2024-09-27T17:14:28Z</t>
+          <t>2025-03-04T22:13:30Z</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-05-25T01:57:13Z</t>
+          <t>2026-01-15T18:34:00Z</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-25T01:57:08Z</t>
+          <t>2025-12-05T01:50:29Z</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
@@ -1265,32 +1269,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>dough</t>
+          <t>diffusers-image-fill</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/dough</t>
+          <t>https://github.com/pinokiofactory/diffusers-image-fill</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2024-07-18T11:39:16Z</t>
+          <t>2024-09-27T17:14:28Z</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024-07-19T12:30:00Z</t>
+          <t>2026-05-25T01:57:13Z</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2024-08-14T20:21:12Z</t>
+          <t>2026-05-25T01:57:08Z</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
@@ -1301,32 +1305,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>e2-f5-tts</t>
+          <t>dough</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/e2-f5-tts</t>
+          <t>https://github.com/pinokiofactory/dough</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2024-10-13T17:23:57Z</t>
+          <t>2024-07-18T11:39:16Z</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-05-23T20:26:54Z</t>
+          <t>2024-07-19T12:30:00Z</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-23T20:26:50Z</t>
+          <t>2024-08-14T20:21:12Z</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
@@ -1337,32 +1341,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>errortest</t>
+          <t>e2-f5-tts</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/errortest</t>
+          <t>https://github.com/pinokiofactory/e2-f5-tts</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2024-11-12T02:01:21Z</t>
+          <t>2024-10-13T17:23:57Z</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024-11-16T03:20:20Z</t>
+          <t>2026-05-23T20:26:54Z</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2024-11-16T03:20:16Z</t>
+          <t>2026-05-23T20:26:50Z</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
@@ -1373,32 +1377,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>facepoke</t>
+          <t>errortest</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/facepoke</t>
+          <t>https://github.com/pinokiofactory/errortest</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2024-10-07T13:28:53Z</t>
+          <t>2024-11-12T02:01:21Z</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-05-26T19:29:06Z</t>
+          <t>2024-11-16T03:20:20Z</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-26T19:29:02Z</t>
+          <t>2024-11-16T03:20:16Z</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
@@ -1409,32 +1413,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>factory</t>
+          <t>facepoke</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/factory</t>
+          <t>https://github.com/pinokiofactory/facepoke</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2024-08-27T21:49:02Z</t>
+          <t>2024-10-07T13:28:53Z</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024-08-27T21:49:02Z</t>
+          <t>2026-05-26T19:29:06Z</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2024-08-27T21:49:02Z</t>
+          <t>2026-05-26T19:29:02Z</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -1445,32 +1449,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>flashdiffusion</t>
+          <t>factory</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/flashdiffusion</t>
+          <t>https://github.com/pinokiofactory/factory</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2024-06-07T19:33:04Z</t>
+          <t>2024-08-27T21:49:02Z</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-03-10T07:04:34Z</t>
+          <t>2024-08-27T21:49:02Z</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2025-03-17T00:27:32Z</t>
+          <t>2024-08-27T21:49:02Z</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
@@ -1481,28 +1485,28 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>florence-sam</t>
+          <t>flashdiffusion</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/florence-sam</t>
+          <t>https://github.com/pinokiofactory/flashdiffusion</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2024-08-01T14:15:49Z</t>
+          <t>2024-06-07T19:33:04Z</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024-08-01T18:30:44Z</t>
+          <t>2026-03-10T07:04:34Z</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2024-08-01T18:30:41Z</t>
+          <t>2025-03-17T00:27:32Z</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -1517,28 +1521,28 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>florence2</t>
+          <t>florence-sam</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/florence2</t>
+          <t>https://github.com/pinokiofactory/florence-sam</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2024-06-20T21:16:01Z</t>
+          <t>2024-08-01T14:15:49Z</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2025-11-06T04:53:27Z</t>
+          <t>2024-08-01T18:30:44Z</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2025-11-06T04:53:23Z</t>
+          <t>2024-08-01T18:30:41Z</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -1553,32 +1557,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>flux-webui</t>
+          <t>florence2</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/flux-webui</t>
+          <t>https://github.com/pinokiofactory/florence2</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2024-08-07T15:22:56Z</t>
+          <t>2024-06-20T21:16:01Z</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-05-15T21:22:01Z</t>
+          <t>2025-11-06T04:53:27Z</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-01T00:58:55Z</t>
+          <t>2025-11-06T04:53:23Z</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
@@ -1589,32 +1593,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>forge</t>
+          <t>flux-webui</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/forge</t>
+          <t>https://github.com/pinokiofactory/flux-webui</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2024-05-11T09:24:03Z</t>
+          <t>2024-08-07T15:22:56Z</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024-08-16T22:18:57Z</t>
+          <t>2026-06-05T17:24:14Z</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2024-08-16T22:18:54Z</t>
+          <t>2026-05-01T00:58:55Z</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
@@ -1625,32 +1629,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>hallo</t>
+          <t>forge</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/hallo</t>
+          <t>https://github.com/pinokiofactory/forge</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2024-06-15T21:19:25Z</t>
+          <t>2024-05-11T09:24:03Z</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-05-26T15:38:52Z</t>
+          <t>2024-08-16T22:18:57Z</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2025-11-27T21:34:29Z</t>
+          <t>2024-08-16T22:18:54Z</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
@@ -1661,32 +1665,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>invoke</t>
+          <t>hallo</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/invoke</t>
+          <t>https://github.com/pinokiofactory/hallo</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2024-05-10T07:32:14Z</t>
+          <t>2024-06-15T21:19:25Z</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-05-27T01:42:51Z</t>
+          <t>2026-05-26T15:38:52Z</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-27T01:42:47Z</t>
+          <t>2025-11-27T21:34:29Z</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
@@ -1697,32 +1701,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>llamafactory</t>
+          <t>invoke</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/llamafactory</t>
+          <t>https://github.com/pinokiofactory/invoke</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2024-05-09T06:38:54Z</t>
+          <t>2024-05-10T07:32:14Z</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-04-24T20:51:19Z</t>
+          <t>2026-05-27T01:42:51Z</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-24T20:51:14Z</t>
+          <t>2026-05-27T01:42:47Z</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
@@ -1733,32 +1737,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>mcp</t>
+          <t>llamafactory</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/mcp</t>
+          <t>https://github.com/pinokiofactory/llamafactory</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2024-12-21T14:25:08Z</t>
+          <t>2024-05-09T06:38:54Z</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2025-04-28T07:12:22Z</t>
+          <t>2026-04-24T20:51:19Z</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2025-01-03T15:23:57Z</t>
+          <t>2026-04-24T20:51:14Z</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
@@ -1769,32 +1773,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>mlx</t>
+          <t>mcp</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/mlx</t>
+          <t>https://github.com/pinokiofactory/mcp</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2024-06-11T18:20:24Z</t>
+          <t>2024-12-21T14:25:08Z</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2025-11-04T13:12:35Z</t>
+          <t>2025-04-28T07:12:22Z</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2024-11-20T20:34:34Z</t>
+          <t>2025-01-03T15:23:57Z</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
@@ -1805,36 +1809,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>mlx-video-ui</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Pinokio launcher scripts for MLX Video UI</t>
-        </is>
-      </c>
+          <t>mlx</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/mlx-video-ui</t>
+          <t>https://github.com/pinokiofactory/mlx</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-02-07T12:57:17Z</t>
+          <t>2024-06-11T18:20:24Z</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-03-16T07:24:28Z</t>
+          <t>2025-11-04T13:12:35Z</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-02-14T00:58:43Z</t>
+          <t>2024-11-20T20:34:34Z</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
@@ -1845,28 +1845,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>moshi</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
+          <t>mlx-video-ui</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Pinokio launcher scripts for MLX Video UI</t>
+        </is>
+      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/moshi</t>
+          <t>https://github.com/pinokiofactory/mlx-video-ui</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2024-09-18T19:39:38Z</t>
+          <t>2026-02-07T12:57:17Z</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-03-23T07:24:44Z</t>
+          <t>2026-03-16T07:24:28Z</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2025-03-16T23:50:29Z</t>
+          <t>2026-02-14T00:58:43Z</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -1881,28 +1885,28 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ominicontrol</t>
+          <t>moshi</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/ominicontrol</t>
+          <t>https://github.com/pinokiofactory/moshi</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2024-11-25T21:32:15Z</t>
+          <t>2024-09-18T19:39:38Z</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024-11-27T09:17:35Z</t>
+          <t>2026-03-23T07:24:44Z</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2024-11-27T09:17:32Z</t>
+          <t>2025-03-16T23:50:29Z</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -1917,32 +1921,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>omnigen</t>
+          <t>ominicontrol</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/omnigen</t>
+          <t>https://github.com/pinokiofactory/ominicontrol</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2024-10-23T18:24:35Z</t>
+          <t>2024-11-25T21:32:15Z</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-05-26T19:49:18Z</t>
+          <t>2024-11-27T09:17:35Z</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-05-26T19:49:13Z</t>
+          <t>2024-11-27T09:17:32Z</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
@@ -1953,32 +1957,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>open-webui</t>
+          <t>omnigen</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/open-webui</t>
+          <t>https://github.com/pinokiofactory/omnigen</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2024-07-23T16:53:00Z</t>
+          <t>2024-10-23T18:24:35Z</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-04-07T13:14:13Z</t>
+          <t>2026-06-05T17:24:01Z</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2025-11-25T11:47:58Z</t>
+          <t>2026-05-26T19:49:13Z</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
@@ -1989,32 +1993,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>openui</t>
+          <t>open-webui</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/openui</t>
+          <t>https://github.com/pinokiofactory/open-webui</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2024-05-08T08:33:21Z</t>
+          <t>2024-07-23T16:53:00Z</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2025-11-04T12:30:09Z</t>
+          <t>2026-04-07T13:14:13Z</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2024-11-28T23:09:18Z</t>
+          <t>2025-11-25T11:47:58Z</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
@@ -2025,32 +2029,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>pcm</t>
+          <t>openui</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/pcm</t>
+          <t>https://github.com/pinokiofactory/openui</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2024-06-05T15:35:00Z</t>
+          <t>2024-05-08T08:33:21Z</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-03-10T07:04:59Z</t>
+          <t>2025-11-04T12:30:09Z</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2025-03-20T03:06:07Z</t>
+          <t>2024-11-28T23:09:18Z</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
@@ -2061,32 +2065,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>photomaker2</t>
+          <t>pcm</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/photomaker2</t>
+          <t>https://github.com/pinokiofactory/pcm</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2024-07-22T16:01:32Z</t>
+          <t>2024-06-05T15:35:00Z</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-04-23T19:53:52Z</t>
+          <t>2026-03-10T07:04:59Z</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-23T19:53:48Z</t>
+          <t>2025-03-20T03:06:07Z</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
@@ -2097,32 +2101,32 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>rc-stableaudio</t>
+          <t>photomaker2</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/rc-stableaudio</t>
+          <t>https://github.com/pinokiofactory/photomaker2</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2024-07-29T14:44:01Z</t>
+          <t>2024-07-22T16:01:32Z</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-04-25T02:38:23Z</t>
+          <t>2026-06-05T17:25:06Z</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-25T02:38:19Z</t>
+          <t>2026-04-23T19:53:48Z</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
@@ -2133,28 +2137,28 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>sd35</t>
+          <t>rc-stableaudio</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/sd35</t>
+          <t>https://github.com/pinokiofactory/rc-stableaudio</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2024-10-22T19:23:06Z</t>
+          <t>2024-07-29T14:44:01Z</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2024-10-22T19:50:14Z</t>
+          <t>2026-04-25T02:38:23Z</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2024-10-22T19:50:11Z</t>
+          <t>2026-04-25T02:38:19Z</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -2169,32 +2173,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>sillytavern</t>
+          <t>sd35</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/sillytavern</t>
+          <t>https://github.com/pinokiofactory/sd35</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2024-05-21T11:58:31Z</t>
+          <t>2024-10-22T19:23:06Z</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-03-14T07:34:23Z</t>
+          <t>2024-10-22T19:50:14Z</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2025-11-26T23:36:47Z</t>
+          <t>2024-10-22T19:50:11Z</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
@@ -2205,32 +2209,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>stable-fast-3d</t>
+          <t>sillytavern</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/stable-fast-3d</t>
+          <t>https://github.com/pinokiofactory/sillytavern</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2024-08-01T18:33:57Z</t>
+          <t>2024-05-21T11:58:31Z</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2024-08-07T20:21:37Z</t>
+          <t>2026-03-14T07:34:23Z</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2024-08-01T18:34:06Z</t>
+          <t>2025-11-26T23:36:47Z</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
@@ -2241,28 +2245,28 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>stableaudio</t>
+          <t>stable-fast-3d</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/stableaudio</t>
+          <t>https://github.com/pinokiofactory/stable-fast-3d</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2024-06-05T20:15:59Z</t>
+          <t>2024-08-01T18:33:57Z</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-04-28T21:38:17Z</t>
+          <t>2024-08-07T20:21:37Z</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-28T21:38:12Z</t>
+          <t>2024-08-01T18:34:06Z</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -2277,28 +2281,28 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>video-background-removal</t>
+          <t>stableaudio</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/video-background-removal</t>
+          <t>https://github.com/pinokiofactory/stableaudio</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2024-10-11T16:00:13Z</t>
+          <t>2024-06-05T20:15:59Z</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-03-30T19:12:21Z</t>
+          <t>2026-04-28T21:38:17Z</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2024-10-11T17:35:54Z</t>
+          <t>2026-04-28T21:38:12Z</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -2313,32 +2317,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>video-background-removal</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/y</t>
+          <t>https://github.com/pinokiofactory/video-background-removal</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2024-05-20T15:06:00Z</t>
+          <t>2024-10-11T16:00:13Z</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2024-05-20T15:06:01Z</t>
+          <t>2026-03-30T19:12:21Z</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2024-05-20T15:06:01Z</t>
+          <t>2024-10-11T17:35:54Z</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
@@ -2349,32 +2353,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>z-image-turbo</t>
+          <t>y</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/z-image-turbo</t>
+          <t>https://github.com/pinokiofactory/y</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025-12-01T15:28:39Z</t>
+          <t>2024-05-20T15:06:00Z</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-04-06T00:01:08Z</t>
+          <t>2024-05-20T15:06:01Z</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-06T00:01:05Z</t>
+          <t>2024-05-20T15:06:01Z</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
@@ -2385,82 +2389,64 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ovis</t>
+          <t>z-image-turbo</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/ovis</t>
+          <t>https://github.com/pinokiofactory/z-image-turbo</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025-12-01T17:31:10Z</t>
+          <t>2025-12-01T15:28:39Z</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2025-12-01T19:45:35Z</t>
+          <t>2026-04-06T00:01:08Z</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2025-12-01T17:31:27Z</t>
+          <t>2026-04-06T00:01:05Z</t>
         </is>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>AIDC-AI/Ovis-Image</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/AIDC-AI/Ovis-Image</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>2025-11-18T03:46:26Z</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>2026-04-25T18:06:06Z</t>
-        </is>
-      </c>
-      <c r="L53" t="n">
-        <v>4</v>
-      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>text2midi</t>
+          <t>ovis</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/text2midi</t>
+          <t>https://github.com/pinokiofactory/ovis</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2024-12-27T18:31:20Z</t>
+          <t>2025-12-01T17:31:10Z</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2024-12-27T19:21:42Z</t>
+          <t>2025-12-01T19:45:35Z</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2024-12-27T19:21:39Z</t>
+          <t>2025-12-01T17:31:27Z</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -2468,57 +2454,53 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>AMAAI-Lab/Text2midi</t>
+          <t>AIDC-AI/Ovis-Image</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/AMAAI-Lab/Text2midi</t>
+          <t>https://github.com/AIDC-AI/Ovis-Image</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2024-12-19T07:51:33Z</t>
+          <t>2025-11-18T03:46:26Z</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-04-06T21:09:10Z</t>
+          <t>2026-04-25T18:06:06Z</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SongGeneration-Studio-MLX</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Tencent SongGeneration Studio MLX</t>
-        </is>
-      </c>
+          <t>text2midi</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/SongGeneration-Studio-MLX</t>
+          <t>https://github.com/pinokiofactory/text2midi</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-01-17T09:12:39Z</t>
+          <t>2024-12-27T18:31:20Z</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-03-12T03:44:58Z</t>
+          <t>2024-12-27T19:21:42Z</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-01-31T15:36:45Z</t>
+          <t>2024-12-27T19:21:39Z</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -2526,273 +2508,277 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>CharafChnioune/SongGeneration-Studio-MLX</t>
+          <t>AMAAI-Lab/Text2midi</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/CharafChnioune/SongGeneration-Studio-MLX</t>
+          <t>https://github.com/AMAAI-Lab/Text2midi</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-01-16T21:45:05Z</t>
+          <t>2024-12-19T07:51:33Z</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-02-10T22:42:47Z</t>
+          <t>2026-04-06T21:09:10Z</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>comfy</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr"/>
+          <t>SongGeneration-Studio-MLX</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Tencent SongGeneration Studio MLX</t>
+        </is>
+      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/comfy</t>
+          <t>https://github.com/pinokiofactory/SongGeneration-Studio-MLX</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2024-08-13T19:47:18Z</t>
+          <t>2026-01-17T09:12:39Z</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-05-14T12:58:11Z</t>
+          <t>2026-03-12T03:44:58Z</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-27T03:11:19Z</t>
+          <t>2026-01-31T15:36:45Z</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Comfy-Org/ComfyUI</t>
+          <t>CharafChnioune/SongGeneration-Studio-MLX</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/Comfy-Org/ComfyUI</t>
+          <t>https://github.com/CharafChnioune/SongGeneration-Studio-MLX</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2023-01-17T03:15:56Z</t>
+          <t>2026-01-16T21:45:05Z</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-05-17T08:19:27Z</t>
+          <t>2026-02-10T22:42:47Z</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>4011</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>audiocraft_plus</t>
+          <t>comfy</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/audiocraft_plus</t>
+          <t>https://github.com/pinokiofactory/comfy</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2024-07-30T17:39:46Z</t>
+          <t>2024-08-13T19:47:18Z</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-04-30T23:53:07Z</t>
+          <t>2026-05-14T12:58:11Z</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-30T23:53:01Z</t>
+          <t>2026-04-27T03:11:19Z</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>GrandaddyShmax/audiocraft_plus</t>
+          <t>Comfy-Org/ComfyUI</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/GrandaddyShmax/audiocraft_plus</t>
+          <t>https://github.com/Comfy-Org/ComfyUI</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2023-06-13T14:44:53Z</t>
+          <t>2023-01-17T03:15:56Z</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-04-17T03:43:29Z</t>
+          <t>2026-05-17T08:19:27Z</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>39</v>
+        <v>4011</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>applio</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Pinokio Installer for Applio</t>
-        </is>
-      </c>
+          <t>audiocraft_plus</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/applio</t>
+          <t>https://github.com/pinokiofactory/audiocraft_plus</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2024-09-13T18:29:14Z</t>
+          <t>2024-07-30T17:39:46Z</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-05-23T20:30:07Z</t>
+          <t>2026-04-30T23:53:07Z</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-05-23T20:30:03Z</t>
+          <t>2026-04-30T23:53:01Z</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>IAHispano/Applio</t>
+          <t>GrandaddyShmax/audiocraft_plus</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/IAHispano/Applio</t>
+          <t>https://github.com/GrandaddyShmax/audiocraft_plus</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2023-08-07T22:42:16Z</t>
+          <t>2023-06-13T14:44:53Z</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-05-24T08:27:37Z</t>
+          <t>2026-04-17T03:43:29Z</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>liveportrait</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr"/>
+          <t>applio</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Pinokio Installer for Applio</t>
+        </is>
+      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/liveportrait</t>
+          <t>https://github.com/pinokiofactory/applio</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2024-07-22T12:47:06Z</t>
+          <t>2024-09-13T18:29:14Z</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-04-28T23:37:23Z</t>
+          <t>2026-05-23T20:30:07Z</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-28T23:37:19Z</t>
+          <t>2026-05-23T20:30:03Z</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>KlingAIResearch/LivePortrait</t>
+          <t>IAHispano/Applio</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/KlingAIResearch/LivePortrait</t>
+          <t>https://github.com/IAHispano/Applio</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2024-07-03T16:15:03Z</t>
+          <t>2023-08-07T22:42:16Z</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-05-03T07:12:35Z</t>
+          <t>2026-05-24T08:27:37Z</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>286</v>
+        <v>28</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Orpheus-TTS-FastAPI</t>
+          <t>liveportrait</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/Orpheus-TTS-FastAPI</t>
+          <t>https://github.com/pinokiofactory/liveportrait</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025-03-23T05:39:00Z</t>
+          <t>2024-07-22T12:47:06Z</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-05-28T20:33:04Z</t>
+          <t>2026-04-28T23:37:23Z</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2025-12-02T20:56:20Z</t>
+          <t>2026-04-28T23:37:19Z</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -2800,331 +2786,331 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Lex-au/Orpheus-FastAPI</t>
+          <t>KlingAIResearch/LivePortrait</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/Lex-au/Orpheus-FastAPI</t>
+          <t>https://github.com/KlingAIResearch/LivePortrait</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2025-03-21T15:24:16Z</t>
+          <t>2024-07-03T16:15:03Z</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-05-29T22:40:51Z</t>
+          <t>2026-05-03T07:12:35Z</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>15</v>
+        <v>286</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>mlx-video-transcription</t>
+          <t>Orpheus-TTS-FastAPI</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/mlx-video-transcription</t>
+          <t>https://github.com/pinokiofactory/Orpheus-TTS-FastAPI</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2024-08-19T17:41:12Z</t>
+          <t>2025-03-23T05:39:00Z</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-04-08T13:24:01Z</t>
+          <t>2026-05-28T20:33:04Z</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2024-10-03T19:11:23Z</t>
+          <t>2025-12-02T20:56:20Z</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>RayFernando1337/MLX-Auto-Subtitled-Video-Generator</t>
+          <t>Lex-au/Orpheus-FastAPI</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/RayFernando1337/MLX-Auto-Subtitled-Video-Generator</t>
+          <t>https://github.com/Lex-au/Orpheus-FastAPI</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2024-07-30T08:44:41Z</t>
+          <t>2025-03-21T15:24:16Z</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-05-03T06:49:04Z</t>
+          <t>2026-05-29T22:40:51Z</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>cube</t>
+          <t>mlx-video-transcription</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/cube</t>
+          <t>https://github.com/pinokiofactory/mlx-video-transcription</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025-03-20T21:16:36Z</t>
+          <t>2024-08-19T17:41:12Z</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-01-24T17:31:53Z</t>
+          <t>2026-04-08T13:24:01Z</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2025-12-02T21:01:20Z</t>
+          <t>2024-10-03T19:11:23Z</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Roblox/cube</t>
+          <t>RayFernando1337/MLX-Auto-Subtitled-Video-Generator</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/Roblox/cube</t>
+          <t>https://github.com/RayFernando1337/MLX-Auto-Subtitled-Video-Generator</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2025-03-11T22:09:47Z</t>
+          <t>2024-07-30T08:44:41Z</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-05-03T04:35:06Z</t>
+          <t>2026-05-03T06:49:04Z</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Ultimate-TTS-Studio</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>🟢 NVIDIA ONLY – All-in-One TTS App with Kokoro, KittenTTS, Higgs audio, Chatterbox, Fish-Speech, F5 &amp; index-tts &amp; indextts2, Supports Conversation Mode &amp; eBook-to-Audiobook. All features work across all engines in a unified interface except vibe voice which is it's own app panel.</t>
-        </is>
-      </c>
+          <t>cube</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/Ultimate-TTS-Studio</t>
+          <t>https://github.com/pinokiofactory/cube</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025-11-25T20:10:36Z</t>
+          <t>2025-03-20T21:16:36Z</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-05-26T19:25:32Z</t>
+          <t>2026-01-24T17:31:53Z</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-02-18T00:45:10Z</t>
+          <t>2025-12-02T21:01:20Z</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>SUP3RMASS1VE/Ultimate-TTS-Studio-SUP3R-Edition</t>
+          <t>Roblox/cube</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/SUP3RMASS1VE/Ultimate-TTS-Studio-SUP3R-Edition</t>
+          <t>https://github.com/Roblox/cube</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2025-06-06T14:54:06Z</t>
+          <t>2025-03-11T22:09:47Z</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-05-29T14:08:04Z</t>
+          <t>2026-05-03T04:35:06Z</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>hertz</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr"/>
+          <t>Ultimate-TTS-Studio</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>🟢 NVIDIA ONLY – All-in-One TTS App with Kokoro, KittenTTS, Higgs audio, Chatterbox, Fish-Speech, F5 &amp; index-tts &amp; indextts2, Supports Conversation Mode &amp; eBook-to-Audiobook. All features work across all engines in a unified interface except vibe voice which is it's own app panel.</t>
+        </is>
+      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/hertz</t>
+          <t>https://github.com/pinokiofactory/Ultimate-TTS-Studio</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2024-11-04T01:04:51Z</t>
+          <t>2025-11-25T20:10:36Z</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2024-11-05T08:54:25Z</t>
+          <t>2026-05-26T19:25:32Z</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2024-11-05T08:54:21Z</t>
+          <t>2026-02-18T00:45:10Z</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Standard-Intelligence/hertz-dev</t>
+          <t>SUP3RMASS1VE/Ultimate-TTS-Studio-SUP3R-Edition</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/Standard-Intelligence/hertz-dev</t>
+          <t>https://github.com/SUP3RMASS1VE/Ultimate-TTS-Studio-SUP3R-Edition</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2024-11-03T14:41:39Z</t>
+          <t>2025-06-06T14:54:06Z</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-05-02T00:10:01Z</t>
+          <t>2026-05-29T14:08:04Z</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Hunyuan3D-2</t>
+          <t>hertz</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/Hunyuan3D-2</t>
+          <t>https://github.com/pinokiofactory/hertz</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025-01-25T04:41:01Z</t>
+          <t>2024-11-04T01:04:51Z</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2025-11-09T20:06:13Z</t>
+          <t>2024-11-05T08:54:25Z</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2025-11-09T20:06:10Z</t>
+          <t>2024-11-05T08:54:21Z</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Tencent-Hunyuan/Hunyuan3D-2</t>
+          <t>Standard-Intelligence/hertz-dev</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/Tencent-Hunyuan/Hunyuan3D-2</t>
+          <t>https://github.com/Standard-Intelligence/hertz-dev</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2025-01-21T05:21:35Z</t>
+          <t>2024-11-03T14:41:39Z</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-05-03T06:13:38Z</t>
+          <t>2026-05-02T00:10:01Z</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>231</v>
+        <v>16</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Hunyuan3D-2-mini</t>
+          <t>Hunyuan3D-2</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/Hunyuan3D-2-mini</t>
+          <t>https://github.com/pinokiofactory/Hunyuan3D-2</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025-01-23T21:29:42Z</t>
+          <t>2025-01-25T04:41:01Z</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2025-01-25T03:18:46Z</t>
+          <t>2025-11-09T20:06:13Z</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2025-01-25T03:50:23Z</t>
+          <t>2025-11-09T20:06:10Z</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -3153,32 +3139,28 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AudioX</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>AudioX: Diffusion Transformer for Anything-to-Audio Generation</t>
-        </is>
-      </c>
+          <t>Hunyuan3D-2-mini</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/AudioX</t>
+          <t>https://github.com/pinokiofactory/Hunyuan3D-2-mini</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025-04-23T00:08:00Z</t>
+          <t>2025-01-23T21:29:42Z</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2025-07-12T12:25:25Z</t>
+          <t>2025-01-25T03:18:46Z</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2025-07-12T12:25:21Z</t>
+          <t>2025-01-25T03:50:23Z</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -3186,771 +3168,775 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>ZeyueT/AudioX</t>
+          <t>Tencent-Hunyuan/Hunyuan3D-2</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/ZeyueT/AudioX</t>
+          <t>https://github.com/Tencent-Hunyuan/Hunyuan3D-2</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2025-03-13T10:18:21Z</t>
+          <t>2025-01-21T05:21:35Z</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-04-30T02:46:00Z</t>
+          <t>2026-05-03T06:13:38Z</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>57</v>
+        <v>231</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>RMBG-2-Studio</t>
+          <t>AudioX</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Enhanced background remove and replace app built around BRIA-RMBG-2.0.  Low VRAM/RAM | 6GB Install</t>
+          <t>AudioX: Diffusion Transformer for Anything-to-Audio Generation</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/RMBG-2-Studio</t>
+          <t>https://github.com/pinokiofactory/AudioX</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2024-11-15T07:13:23Z</t>
+          <t>2025-04-23T00:08:00Z</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-05-30T06:50:16Z</t>
+          <t>2025-07-12T12:25:25Z</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-30T01:12:28Z</t>
+          <t>2025-07-12T12:25:21Z</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>ZhengPeng7/BiRefNet</t>
+          <t>ZeyueT/AudioX</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/ZhengPeng7/BiRefNet</t>
+          <t>https://github.com/ZeyueT/AudioX</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2022-08-17T09:13:39Z</t>
+          <t>2025-03-13T10:18:21Z</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-05-31T04:32:08Z</t>
+          <t>2026-04-30T02:46:00Z</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>21</v>
+        <v>57</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>zonos</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr"/>
+          <t>RMBG-2-Studio</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Enhanced background remove and replace app built around BRIA-RMBG-2.0.  Low VRAM/RAM | 6GB Install</t>
+        </is>
+      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/zonos</t>
+          <t>https://github.com/pinokiofactory/RMBG-2-Studio</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025-02-11T09:00:12Z</t>
+          <t>2024-11-15T07:13:23Z</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-05-25T01:01:31Z</t>
+          <t>2026-06-07T04:31:49Z</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-05-25T01:01:26Z</t>
+          <t>2026-03-30T01:12:28Z</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Zyphra/Zonos</t>
+          <t>ZhengPeng7/BiRefNet</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/Zyphra/Zonos</t>
+          <t>https://github.com/ZhengPeng7/BiRefNet</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2025-02-07T00:32:44Z</t>
+          <t>2022-08-17T09:13:39Z</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-05-30T10:02:43Z</t>
+          <t>2026-06-07T08:29:52Z</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>168</v>
+        <v>21</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ACE-Step</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>A Step Towards Music Generation Foundation Model</t>
-        </is>
-      </c>
+          <t>zonos</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/ACE-Step</t>
+          <t>https://github.com/pinokiofactory/zonos</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025-05-07T11:25:33Z</t>
+          <t>2025-02-11T09:00:12Z</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2025-12-06T11:35:01Z</t>
+          <t>2026-05-25T01:01:31Z</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2025-12-06T11:34:57Z</t>
+          <t>2026-05-25T01:01:26Z</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>ace-step/ACE-Step</t>
+          <t>Zyphra/Zonos</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/ace-step/ACE-Step</t>
+          <t>https://github.com/Zyphra/Zonos</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2025-04-28T07:03:09Z</t>
+          <t>2025-02-07T00:32:44Z</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-05-03T05:20:18Z</t>
+          <t>2026-05-30T10:02:43Z</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>144</v>
+        <v>168</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>MagicQuill</t>
+          <t>ACE-Step</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>An intelligent, interactive Image Editing System. Easily erase and add objects on a user-friendly interface.</t>
+          <t>A Step Towards Music Generation Foundation Model</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/MagicQuill</t>
+          <t>https://github.com/pinokiofactory/ACE-Step</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025-02-19T03:58:52Z</t>
+          <t>2025-05-07T11:25:33Z</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-05-05T13:33:04Z</t>
+          <t>2025-12-06T11:35:01Z</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-01-11T20:07:58Z</t>
+          <t>2025-12-06T11:34:57Z</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>ant-research/MagicQuill</t>
+          <t>ace-step/ACE-Step</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/ant-research/MagicQuill</t>
+          <t>https://github.com/ace-step/ACE-Step</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2024-11-12T12:52:36Z</t>
+          <t>2025-04-28T07:03:09Z</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-05-07T13:30:37Z</t>
+          <t>2026-05-03T05:20:18Z</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>46</v>
+        <v>144</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>echomimic2</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr"/>
+          <t>MagicQuill</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>An intelligent, interactive Image Editing System. Easily erase and add objects on a user-friendly interface.</t>
+        </is>
+      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/echomimic2</t>
+          <t>https://github.com/pinokiofactory/MagicQuill</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2024-11-24T07:52:04Z</t>
+          <t>2025-02-19T03:58:52Z</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-04-28T23:29:48Z</t>
+          <t>2026-05-05T13:33:04Z</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-28T23:29:43Z</t>
+          <t>2026-01-11T20:07:58Z</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>antgroup/echomimic_v2</t>
+          <t>ant-research/MagicQuill</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antgroup/echomimic_v2</t>
+          <t>https://github.com/ant-research/MagicQuill</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2024-11-20T08:35:35Z</t>
+          <t>2024-11-12T12:52:36Z</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-05-02T20:48:54Z</t>
+          <t>2026-05-07T13:30:37Z</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>78</v>
+        <v>46</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>macOS-use</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>We Make Mac apps accessible for AI agents</t>
-        </is>
-      </c>
+          <t>echomimic2</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/macOS-use</t>
+          <t>https://github.com/pinokiofactory/echomimic2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025-02-18T16:54:37Z</t>
+          <t>2024-11-24T07:52:04Z</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2025-11-04T13:06:11Z</t>
+          <t>2026-04-28T23:29:48Z</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2025-04-01T04:14:59Z</t>
+          <t>2026-04-28T23:29:43Z</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>browser-use/macOS-use</t>
+          <t>antgroup/echomimic_v2</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/browser-use/macOS-use</t>
+          <t>https://github.com/antgroup/echomimic_v2</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2025-01-23T00:35:15Z</t>
+          <t>2024-11-20T08:35:35Z</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-05-03T00:00:27Z</t>
+          <t>2026-05-02T20:48:54Z</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>17</v>
+        <v>78</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>browser-use</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr"/>
+          <t>macOS-use</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>We Make Mac apps accessible for AI agents</t>
+        </is>
+      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/browser-use</t>
+          <t>https://github.com/pinokiofactory/macOS-use</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025-01-19T21:55:50Z</t>
+          <t>2025-02-18T16:54:37Z</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-01-27T14:53:11Z</t>
+          <t>2025-11-04T13:06:11Z</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2025-04-01T04:25:12Z</t>
+          <t>2025-04-01T04:14:59Z</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>browser-use/web-ui</t>
+          <t>browser-use/macOS-use</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/browser-use/web-ui</t>
+          <t>https://github.com/browser-use/macOS-use</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2025-01-02T01:29:44Z</t>
+          <t>2025-01-23T00:35:15Z</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-05-02T23:23:36Z</t>
+          <t>2026-05-03T00:00:27Z</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>316</v>
+        <v>17</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>uno</t>
+          <t>browser-use</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/uno</t>
+          <t>https://github.com/pinokiofactory/browser-use</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025-04-10T18:31:57Z</t>
+          <t>2025-01-19T21:55:50Z</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2025-12-02T20:55:29Z</t>
+          <t>2026-01-27T14:53:11Z</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2025-12-02T20:55:25Z</t>
+          <t>2025-04-01T04:25:12Z</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>bytedance/UNO</t>
+          <t>browser-use/web-ui</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/bytedance/UNO</t>
+          <t>https://github.com/browser-use/web-ui</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2025-04-01T13:25:11Z</t>
+          <t>2025-01-02T01:29:44Z</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-05-02T09:43:14Z</t>
+          <t>2026-05-02T23:23:36Z</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>30</v>
+        <v>316</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Hunyuan3d-2-lowvram</t>
+          <t>uno</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/Hunyuan3d-2-lowvram</t>
+          <t>https://github.com/pinokiofactory/uno</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025-01-25T04:44:25Z</t>
+          <t>2025-04-10T18:31:57Z</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-04-23T19:59:25Z</t>
+          <t>2025-12-02T20:55:29Z</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-23T19:59:21Z</t>
+          <t>2025-12-02T20:55:25Z</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>deepbeepmeep/Hunyuan3D-2GP</t>
+          <t>bytedance/UNO</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/deepbeepmeep/Hunyuan3D-2GP</t>
+          <t>https://github.com/bytedance/UNO</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2025-01-22T01:50:03Z</t>
+          <t>2025-04-01T13:25:11Z</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-04-29T11:55:54Z</t>
+          <t>2026-05-02T09:43:14Z</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>hunyuanvideo</t>
+          <t>Hunyuan3d-2-lowvram</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/hunyuanvideo</t>
+          <t>https://github.com/pinokiofactory/Hunyuan3d-2-lowvram</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2024-12-11T01:55:53Z</t>
+          <t>2025-01-25T04:44:25Z</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-04-17T16:26:23Z</t>
+          <t>2026-04-23T19:59:25Z</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2025-12-02T20:58:56Z</t>
+          <t>2026-04-23T19:59:21Z</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>deepbeepmeep/HunyuanVideoGP</t>
+          <t>deepbeepmeep/Hunyuan3D-2GP</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/deepbeepmeep/HunyuanVideoGP</t>
+          <t>https://github.com/deepbeepmeep/Hunyuan3D-2GP</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2024-12-10T18:34:42Z</t>
+          <t>2025-01-22T01:50:03Z</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-05-02T15:39:29Z</t>
+          <t>2026-04-29T11:55:54Z</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>wan</t>
+          <t>hunyuanvideo</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/wan</t>
+          <t>https://github.com/pinokiofactory/hunyuanvideo</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025-03-03T17:32:45Z</t>
+          <t>2024-12-11T01:55:53Z</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-05-20T05:52:58Z</t>
+          <t>2026-06-05T19:59:58Z</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-29T04:48:55Z</t>
+          <t>2025-12-02T20:58:56Z</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>deepbeepmeep/Wan2GP</t>
+          <t>deepbeepmeep/HunyuanVideoGP</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/deepbeepmeep/Wan2GP</t>
+          <t>https://github.com/deepbeepmeep/HunyuanVideoGP</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2025-02-27T23:52:36Z</t>
+          <t>2024-12-10T18:34:42Z</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-05-24T08:34:56Z</t>
+          <t>2026-06-04T12:36:42Z</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>852</v>
+        <v>13</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>yue</t>
+          <t>wan</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/yue</t>
+          <t>https://github.com/pinokiofactory/wan</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025-01-29T11:22:39Z</t>
+          <t>2025-03-03T17:32:45Z</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-02-11T18:06:59Z</t>
+          <t>2026-05-20T05:52:58Z</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2025-12-02T21:56:04Z</t>
+          <t>2026-04-29T04:48:55Z</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>deepbeepmeep/YuEGP</t>
+          <t>deepbeepmeep/Wan2GP</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/deepbeepmeep/YuEGP</t>
+          <t>https://github.com/deepbeepmeep/Wan2GP</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2025-01-28T07:23:51Z</t>
+          <t>2025-02-27T23:52:36Z</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-05-02T15:38:09Z</t>
+          <t>2026-05-24T08:34:56Z</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>21</v>
+        <v>852</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>janus</t>
+          <t>yue</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/janus</t>
+          <t>https://github.com/pinokiofactory/yue</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025-01-27T18:23:47Z</t>
+          <t>2025-01-29T11:22:39Z</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2025-01-28T02:37:49Z</t>
+          <t>2026-02-11T18:06:59Z</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2025-01-28T02:37:46Z</t>
+          <t>2025-12-02T21:56:04Z</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>deepseek-ai/Janus</t>
+          <t>deepbeepmeep/YuEGP</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/deepseek-ai/Janus</t>
+          <t>https://github.com/deepbeepmeep/YuEGP</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2024-10-18T03:48:16Z</t>
+          <t>2025-01-28T07:23:51Z</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-05-03T05:56:07Z</t>
+          <t>2026-05-02T15:38:09Z</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>185</v>
+        <v>21</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>diamond</t>
+          <t>janus</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/diamond</t>
+          <t>https://github.com/pinokiofactory/janus</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2024-10-12T15:37:19Z</t>
+          <t>2025-01-27T18:23:47Z</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-01-24T06:17:09Z</t>
+          <t>2025-01-28T02:37:49Z</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2025-12-02T23:46:49Z</t>
+          <t>2025-01-28T02:37:46Z</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -3958,601 +3944,601 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>eloialonso/diamond</t>
+          <t>deepseek-ai/Janus</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/eloialonso/diamond</t>
+          <t>https://github.com/deepseek-ai/Janus</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2024-05-19T22:31:40Z</t>
+          <t>2024-10-18T03:48:16Z</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-05-03T04:51:58Z</t>
+          <t>2026-05-03T05:56:07Z</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>6</v>
+        <v>185</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>AllTalk-TTS</t>
+          <t>diamond</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/AllTalk-TTS</t>
+          <t>https://github.com/pinokiofactory/diamond</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025-02-05T16:24:30Z</t>
+          <t>2024-10-12T15:37:19Z</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2025-04-05T16:19:34Z</t>
+          <t>2026-01-24T06:17:09Z</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2025-03-29T16:44:51Z</t>
+          <t>2025-12-02T23:46:49Z</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>erew123/alltalk_tts</t>
+          <t>eloialonso/diamond</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/erew123/alltalk_tts</t>
+          <t>https://github.com/eloialonso/diamond</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2023-12-08T09:35:19Z</t>
+          <t>2024-05-19T22:31:40Z</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-05-02T12:49:34Z</t>
+          <t>2026-05-03T04:51:58Z</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>85</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>oasis</t>
+          <t>AllTalk-TTS</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/oasis</t>
+          <t>https://github.com/pinokiofactory/AllTalk-TTS</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2024-10-31T23:24:32Z</t>
+          <t>2025-02-05T16:24:30Z</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2024-10-31T23:47:38Z</t>
+          <t>2025-04-05T16:19:34Z</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2024-10-31T23:47:35Z</t>
+          <t>2025-03-29T16:44:51Z</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>etched-ai/open-oasis</t>
+          <t>erew123/alltalk_tts</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/etched-ai/open-oasis</t>
+          <t>https://github.com/erew123/alltalk_tts</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2024-10-31T09:10:45Z</t>
+          <t>2023-12-08T09:35:19Z</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-05-01T18:11:07Z</t>
+          <t>2026-05-02T12:49:34Z</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>32</v>
+        <v>85</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>openaudio</t>
+          <t>oasis</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/openaudio</t>
+          <t>https://github.com/pinokiofactory/oasis</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2024-11-02T08:47:31Z</t>
+          <t>2024-10-31T23:24:32Z</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-04-28T21:58:57Z</t>
+          <t>2024-10-31T23:47:38Z</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-04-25T02:45:14Z</t>
+          <t>2024-10-31T23:47:35Z</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>fishaudio/fish-speech</t>
+          <t>etched-ai/open-oasis</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/fishaudio/fish-speech</t>
+          <t>https://github.com/etched-ai/open-oasis</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2023-10-10T03:16:51Z</t>
+          <t>2024-10-31T09:10:45Z</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-05-03T07:35:54Z</t>
+          <t>2026-05-01T18:11:07Z</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>mochi</t>
+          <t>openaudio</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/mochi</t>
+          <t>https://github.com/pinokiofactory/openaudio</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2024-10-23T18:51:07Z</t>
+          <t>2024-11-02T08:47:31Z</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2024-10-29T03:03:08Z</t>
+          <t>2026-04-28T21:58:57Z</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2024-10-29T03:03:04Z</t>
+          <t>2026-04-25T02:45:14Z</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>genmoai/mochi</t>
+          <t>fishaudio/fish-speech</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/genmoai/mochi</t>
+          <t>https://github.com/fishaudio/fish-speech</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>2024-09-11T02:55:33Z</t>
+          <t>2023-10-10T03:16:51Z</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-05-01T11:29:35Z</t>
+          <t>2026-05-03T07:35:54Z</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>59</v>
+        <v>30</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>instantir</t>
+          <t>mochi</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/instantir</t>
+          <t>https://github.com/pinokiofactory/mochi</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2024-11-08T08:05:55Z</t>
+          <t>2024-10-23T18:51:07Z</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-05-28T03:05:24Z</t>
+          <t>2024-10-29T03:03:08Z</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-05-28T03:05:19Z</t>
+          <t>2024-10-29T03:03:04Z</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>instantX-research/InstantIR</t>
+          <t>genmoai/mochi</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/instantX-research/InstantIR</t>
+          <t>https://github.com/genmoai/mochi</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>2024-10-20T03:17:01Z</t>
+          <t>2024-09-11T02:55:33Z</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-05-31T04:54:18Z</t>
+          <t>2026-05-01T11:29:35Z</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>8</v>
+        <v>59</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>whisper-webui</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Pinokio Installer for Whisper-Webui</t>
-        </is>
-      </c>
+          <t>instantir</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/whisper-webui</t>
+          <t>https://github.com/pinokiofactory/instantir</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2024-09-21T20:42:20Z</t>
+          <t>2024-11-08T08:05:55Z</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-05-23T20:32:52Z</t>
+          <t>2026-05-28T03:05:24Z</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-05-23T20:32:48Z</t>
+          <t>2026-05-28T03:05:19Z</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>jhj0517/Whisper-WebUI</t>
+          <t>instantX-research/InstantIR</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/jhj0517/Whisper-WebUI</t>
+          <t>https://github.com/instantX-research/InstantIR</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>2023-03-02T13:42:01Z</t>
+          <t>2024-10-20T03:17:01Z</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-05-23T20:36:11Z</t>
+          <t>2026-05-31T04:54:18Z</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>148</v>
+        <v>8</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>pyramidflow</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr"/>
+          <t>whisper-webui</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Pinokio Installer for Whisper-Webui</t>
+        </is>
+      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/pyramidflow</t>
+          <t>https://github.com/pinokiofactory/whisper-webui</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2024-11-16T08:35:22Z</t>
+          <t>2024-09-21T20:42:20Z</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-05-25T01:05:38Z</t>
+          <t>2026-05-23T20:32:52Z</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-05-25T01:05:35Z</t>
+          <t>2026-05-23T20:32:48Z</t>
         </is>
       </c>
       <c r="G88" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>jy0205/Pyramid-Flow</t>
+          <t>jhj0517/Whisper-WebUI</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/jy0205/Pyramid-Flow</t>
+          <t>https://github.com/jhj0517/Whisper-WebUI</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>2024-10-06T13:06:31Z</t>
+          <t>2023-03-02T13:42:01Z</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-05-30T01:54:22Z</t>
+          <t>2026-05-23T20:36:11Z</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>71</v>
+        <v>148</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Frame-Pack</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>(NVIDIA) FramePack is a next-frame (next-frame-section) prediction neural network structure that generates videos progressively.</t>
-        </is>
-      </c>
+          <t>pyramidflow</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr"/>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/Frame-Pack</t>
+          <t>https://github.com/pinokiofactory/pyramidflow</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025-04-17T11:43:03Z</t>
+          <t>2024-11-16T08:35:22Z</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-05-24T02:17:34Z</t>
+          <t>2026-05-25T01:05:38Z</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-05-24T02:17:30Z</t>
+          <t>2026-05-25T01:05:35Z</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>lllyasviel/FramePack</t>
+          <t>jy0205/Pyramid-Flow</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/lllyasviel/FramePack</t>
+          <t>https://github.com/jy0205/Pyramid-Flow</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>2025-04-12T14:45:22Z</t>
+          <t>2024-10-06T13:06:31Z</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-05-23T23:50:10Z</t>
+          <t>2026-05-30T01:54:22Z</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>485</v>
+        <v>71</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>stable-diffusion-webui-forge</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr"/>
+          <t>Frame-Pack</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>(NVIDIA) FramePack is a next-frame (next-frame-section) prediction neural network structure that generates videos progressively.</t>
+        </is>
+      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/stable-diffusion-webui-forge</t>
+          <t>https://github.com/pinokiofactory/Frame-Pack</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2024-08-12T12:38:49Z</t>
+          <t>2025-04-17T11:43:03Z</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-05-15T18:54:36Z</t>
+          <t>2026-06-05T19:56:54Z</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-04-28T22:51:44Z</t>
+          <t>2026-05-24T02:17:30Z</t>
         </is>
       </c>
       <c r="G90" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>lllyasviel/stable-diffusion-webui-forge</t>
+          <t>lllyasviel/FramePack</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/lllyasviel/stable-diffusion-webui-forge</t>
+          <t>https://github.com/lllyasviel/FramePack</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>2024-01-14T11:39:30Z</t>
+          <t>2025-04-12T14:45:22Z</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-05-17T07:49:42Z</t>
+          <t>2026-06-06T21:18:59Z</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>1144</v>
+        <v>484</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>omniparser</t>
+          <t>stable-diffusion-webui-forge</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/omniparser</t>
+          <t>https://github.com/pinokiofactory/stable-diffusion-webui-forge</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2024-10-26T06:04:17Z</t>
+          <t>2024-08-12T12:38:49Z</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2024-10-28T04:49:07Z</t>
+          <t>2026-05-15T18:54:36Z</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2024-10-26T08:03:10Z</t>
+          <t>2026-04-28T22:51:44Z</t>
         </is>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>microsoft/OmniParser</t>
+          <t>lllyasviel/stable-diffusion-webui-forge</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/microsoft/OmniParser</t>
+          <t>https://github.com/lllyasviel/stable-diffusion-webui-forge</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>2024-09-20T05:18:18Z</t>
+          <t>2024-01-14T11:39:30Z</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-05-03T07:54:03Z</t>
+          <t>2026-05-17T07:49:42Z</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>232</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>vibevoice-realtime</t>
+          <t>omniparser</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/vibevoice-realtime</t>
+          <t>https://github.com/pinokiofactory/omniparser</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025-12-04T21:57:09Z</t>
+          <t>2024-10-26T06:04:17Z</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-04-30T14:45:13Z</t>
+          <t>2024-10-28T04:49:07Z</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2025-12-22T22:00:09Z</t>
+          <t>2024-10-26T08:03:10Z</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -4560,231 +4546,227 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>microsoft/VibeVoice</t>
+          <t>microsoft/OmniParser</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/microsoft/VibeVoice</t>
+          <t>https://github.com/microsoft/OmniParser</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>2025-08-25T13:24:01Z</t>
+          <t>2024-09-20T05:18:18Z</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-05-03T07:41:17Z</t>
+          <t>2026-05-03T07:54:03Z</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>150</v>
+        <v>232</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>dia</t>
+          <t>vibevoice-realtime</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/dia</t>
+          <t>https://github.com/pinokiofactory/vibevoice-realtime</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025-04-22T14:57:53Z</t>
+          <t>2025-12-04T21:57:09Z</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-05-25T00:57:28Z</t>
+          <t>2026-04-30T14:45:13Z</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-05-25T00:57:23Z</t>
+          <t>2025-12-22T22:00:09Z</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>nari-labs/dia</t>
+          <t>microsoft/VibeVoice</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/nari-labs/dia</t>
+          <t>https://github.com/microsoft/VibeVoice</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>2025-04-19T07:15:57Z</t>
+          <t>2025-08-25T13:24:01Z</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2026-05-31T03:36:41Z</t>
+          <t>2026-05-03T07:41:17Z</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>92</v>
+        <v>150</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>clarity-refiners-ui</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Creative Image Enhancer/Upscaler. Powered By Refiners.  8GB VRAM | 10GB Install</t>
-        </is>
-      </c>
+          <t>dia</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr"/>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/clarity-refiners-ui</t>
+          <t>https://github.com/pinokiofactory/dia</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2024-11-12T07:03:48Z</t>
+          <t>2025-04-22T14:57:53Z</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-05-28T08:16:37Z</t>
+          <t>2026-05-25T00:57:28Z</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-05-28T08:16:33Z</t>
+          <t>2026-05-25T00:57:23Z</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>philz1337x/clarity-upscaler</t>
+          <t>nari-labs/dia</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/philz1337x/clarity-upscaler</t>
+          <t>https://github.com/nari-labs/dia</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>2024-03-15T15:21:40Z</t>
+          <t>2025-04-19T07:15:57Z</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2026-05-30T10:02:36Z</t>
+          <t>2026-05-31T03:36:41Z</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>18</v>
+        <v>92</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Allegro-txt2vid</t>
+          <t>clarity-refiners-ui</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Allegro is a powerful text-to-video model that generates high-quality videos up to 6 seconds at 15 FPS and 720p resolution from simple text input.</t>
+          <t>Creative Image Enhancer/Upscaler. Powered By Refiners.  8GB VRAM | 10GB Install</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/Allegro-txt2vid</t>
+          <t>https://github.com/pinokiofactory/clarity-refiners-ui</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2024-10-25T06:33:03Z</t>
+          <t>2024-11-12T07:03:48Z</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2024-11-05T23:56:50Z</t>
+          <t>2026-05-28T08:16:37Z</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2024-11-05T23:56:47Z</t>
+          <t>2026-05-28T08:16:33Z</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>rhymes-ai/Allegro</t>
+          <t>philz1337x/clarity-upscaler</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/rhymes-ai/Allegro</t>
+          <t>https://github.com/philz1337x/clarity-upscaler</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>2024-10-16T04:04:15Z</t>
+          <t>2024-03-15T15:21:40Z</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>2026-04-22T07:48:52Z</t>
+          <t>2026-05-30T10:02:36Z</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Allegro-txt2vid-install</t>
+          <t>Allegro-txt2vid</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Allegro-txt2vid. WARNING: takes a long time to generate a result, 1hr on a 3090. 12GB+ VRAM | 32GB+ RAM | 30GB Download. Check the README for details</t>
+          <t>Allegro is a powerful text-to-video model that generates high-quality videos up to 6 seconds at 15 FPS and 720p resolution from simple text input.</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/Allegro-txt2vid-install</t>
+          <t>https://github.com/pinokiofactory/Allegro-txt2vid</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2024-10-27T14:58:05Z</t>
+          <t>2024-10-25T06:33:03Z</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-05-26T19:25:15Z</t>
+          <t>2024-11-05T23:56:50Z</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-05-26T19:25:11Z</t>
+          <t>2024-11-05T23:56:47Z</t>
         </is>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -4803,7 +4785,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2026-05-19T12:52:07Z</t>
+          <t>2026-04-22T07:48:52Z</t>
         </is>
       </c>
       <c r="L96" t="n">
@@ -4813,32 +4795,32 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>RuinedFooocus</t>
+          <t>Allegro-txt2vid-install</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t xml:space="preserve">(NVIDIA ONLY) Forget everything you thought you knew about AI art generation - RuinedFooocus is here to completely reinvent the game! This groundbreaking image creator combines the best aspects of Stable Diffusion and Midjourney into one seamless, cutting-edge experience. </t>
+          <t>Allegro-txt2vid. WARNING: takes a long time to generate a result, 1hr on a 3090. 12GB+ VRAM | 32GB+ RAM | 30GB Download. Check the README for details</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/RuinedFooocus</t>
+          <t>https://github.com/pinokiofactory/Allegro-txt2vid-install</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025-04-22T14:09:26Z</t>
+          <t>2024-10-27T14:58:05Z</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2025-10-30T19:53:32Z</t>
+          <t>2026-05-26T19:25:15Z</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2025-10-30T19:53:29Z</t>
+          <t>2026-05-26T19:25:11Z</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -4846,241 +4828,299 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>runew0lf/RuinedFooocus</t>
+          <t>rhymes-ai/Allegro</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/runew0lf/RuinedFooocus</t>
+          <t>https://github.com/rhymes-ai/Allegro</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>2023-08-16T09:20:46Z</t>
+          <t>2024-10-16T04:04:15Z</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2026-05-02T17:57:29Z</t>
+          <t>2026-05-19T12:52:07Z</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>bolt</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr"/>
+          <t>RuinedFooocus</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(NVIDIA ONLY) Forget everything you thought you knew about AI art generation - RuinedFooocus is here to completely reinvent the game! This groundbreaking image creator combines the best aspects of Stable Diffusion and Midjourney into one seamless, cutting-edge experience. </t>
+        </is>
+      </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/bolt</t>
+          <t>https://github.com/pinokiofactory/RuinedFooocus</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2024-10-30T04:46:10Z</t>
+          <t>2025-04-22T14:09:26Z</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-04-25T15:48:50Z</t>
+          <t>2025-10-30T19:53:32Z</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2025-12-06T21:59:33Z</t>
+          <t>2025-10-30T19:53:29Z</t>
         </is>
       </c>
       <c r="G98" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>stackblitz-labs/bolt.diy</t>
+          <t>runew0lf/RuinedFooocus</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/stackblitz-labs/bolt.diy</t>
+          <t>https://github.com/runew0lf/RuinedFooocus</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>2024-10-13T18:40:54Z</t>
+          <t>2023-08-16T09:20:46Z</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2026-05-02T20:32:27Z</t>
+          <t>2026-05-02T17:57:29Z</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>108</v>
+        <v>30</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ditto</t>
+          <t>bolt</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/ditto</t>
+          <t>https://github.com/pinokiofactory/bolt</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2024-10-15T21:29:32Z</t>
+          <t>2024-10-30T04:46:10Z</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2025-11-06T00:05:04Z</t>
+          <t>2026-04-25T15:48:50Z</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2024-10-15T22:47:07Z</t>
+          <t>2025-12-06T21:59:33Z</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>yoheinakajima/ditto</t>
+          <t>stackblitz-labs/bolt.diy</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/yoheinakajima/ditto</t>
+          <t>https://github.com/stackblitz-labs/bolt.diy</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>2024-10-15T19:45:13Z</t>
+          <t>2024-10-13T18:40:54Z</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2026-05-01T19:29:34Z</t>
+          <t>2026-05-02T20:32:27Z</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>8</v>
+        <v>108</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>cogstudio</t>
+          <t>ditto</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/cogstudio</t>
+          <t>https://github.com/pinokiofactory/ditto</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2024-09-20T10:46:17Z</t>
+          <t>2024-10-15T21:29:32Z</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-05-31T00:51:08Z</t>
+          <t>2025-11-06T00:05:04Z</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-05-01T02:35:24Z</t>
+          <t>2024-10-15T22:47:07Z</t>
         </is>
       </c>
       <c r="G100" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>zai-org/CogVideo</t>
+          <t>yoheinakajima/ditto</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/zai-org/CogVideo</t>
+          <t>https://github.com/yoheinakajima/ditto</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>2022-05-29T06:46:18Z</t>
+          <t>2024-10-15T19:45:13Z</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>2026-05-31T06:59:53Z</t>
+          <t>2026-05-01T19:29:34Z</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>113</v>
+        <v>8</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>cogvideo</t>
+          <t>cogstudio</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" s="2" t="inlineStr">
         <is>
+          <t>https://github.com/pinokiofactory/cogstudio</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2024-09-20T10:46:17Z</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>2026-05-31T00:51:08Z</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-05-01T02:35:24Z</t>
+        </is>
+      </c>
+      <c r="G101" t="n">
+        <v>39</v>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>zai-org/CogVideo</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/zai-org/CogVideo</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>2022-05-29T06:46:18Z</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>2026-05-31T06:59:53Z</t>
+        </is>
+      </c>
+      <c r="L101" t="n">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>cogvideo</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr"/>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
           <t>https://github.com/pinokiofactory/cogvideo</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
+      <c r="D102" t="inlineStr">
         <is>
           <t>2024-08-30T10:13:02Z</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
+      <c r="E102" t="inlineStr">
         <is>
           <t>2026-05-01T02:00:24Z</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
+      <c r="F102" t="inlineStr">
         <is>
           <t>2026-05-01T02:00:20Z</t>
         </is>
       </c>
-      <c r="G101" t="n">
+      <c r="G102" t="n">
         <v>1</v>
       </c>
-      <c r="H101" t="inlineStr">
+      <c r="H102" t="inlineStr">
         <is>
           <t>zai-org/CogVideo</t>
         </is>
       </c>
-      <c r="I101" s="2" t="inlineStr">
+      <c r="I102" s="2" t="inlineStr">
         <is>
           <t>https://github.com/zai-org/CogVideo</t>
         </is>
       </c>
-      <c r="J101" t="inlineStr">
+      <c r="J102" t="inlineStr">
         <is>
           <t>2022-05-29T06:46:18Z</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr">
+      <c r="K102" t="inlineStr">
         <is>
           <t>2026-05-02T21:59:21Z</t>
         </is>
       </c>
-      <c r="L101" t="n">
+      <c r="L102" t="n">
         <v>113</v>
       </c>
     </row>
@@ -5138,103 +5178,104 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C52" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C53" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C54" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C56" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C58" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C59" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C60" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C61" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C62" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C63" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C64" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C65" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C66" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C67" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C68" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C69" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C70" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C71" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C72" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C73" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C74" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C75" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C76" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C77" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C78" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C79" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C80" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I80" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C81" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C82" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C83" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I83" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C84" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C85" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C86" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I86" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C87" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I87" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C88" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C89" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I89" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C90" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I90" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C91" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C92" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I92" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C93" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I93" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C94" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I94" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C95" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I95" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C96" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I96" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C97" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I97" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C98" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I98" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C99" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I99" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C100" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I100" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C101" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I101" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C56" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C58" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C59" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C60" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C61" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C62" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C63" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C64" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C65" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C66" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C67" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C68" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C69" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C70" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C71" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C72" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C73" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C74" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C75" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C76" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C77" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C78" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C79" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C80" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I80" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C81" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C82" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C83" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I83" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C84" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C85" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C86" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I86" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C87" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I87" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C88" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C89" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I89" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C90" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I90" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C91" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C92" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I92" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C93" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I93" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C94" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I94" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C95" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I95" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C96" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I96" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C97" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I97" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C98" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I98" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C99" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I99" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C100" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I100" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C101" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I101" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C102" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I102" r:id="rId150"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pinokio_repos.xlsx
+++ b/pinokio_repos.xlsx
@@ -961,12 +961,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-06-07T02:25:57Z</t>
+          <t>2026-06-08T19:47:01Z</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-07T03:19:39Z</t>
+          <t>2026-06-08T19:58:28Z</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-05-26T15:38:52Z</t>
+          <t>2026-06-10T21:45:09Z</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-05-14T12:58:11Z</t>
+          <t>2026-06-13T21:00:26Z</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2635,11 +2635,11 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-05-17T08:19:27Z</t>
+          <t>2026-06-14T09:44:36Z</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>4011</v>
+        <v>4123</v>
       </c>
     </row>
     <row r="58">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-05-26T19:25:32Z</t>
+          <t>2026-06-13T17:20:51Z</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3021,11 +3021,11 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-05-29T14:08:04Z</t>
+          <t>2026-06-13T17:20:45Z</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="65">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-06-07T04:31:49Z</t>
+          <t>2026-06-11T00:10:04Z</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-06-07T08:29:52Z</t>
+          <t>2026-06-14T03:52:13Z</t>
         </is>
       </c>
       <c r="L69" t="n">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-04-23T19:59:25Z</t>
+          <t>2026-06-08T23:08:38Z</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3724,7 +3724,7 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-04-29T11:55:54Z</t>
+          <t>2026-06-13T15:05:55Z</t>
         </is>
       </c>
       <c r="L77" t="n">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-05-20T05:52:58Z</t>
+          <t>2026-06-10T13:53:24Z</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3851,11 +3851,11 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-05-24T08:34:56Z</t>
+          <t>2026-06-14T08:38:31Z</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>852</v>
+        <v>901</v>
       </c>
     </row>
     <row r="80">

--- a/pinokio_repos.xlsx
+++ b/pinokio_repos.xlsx
@@ -1609,7 +1609,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-06-05T17:24:14Z</t>
+          <t>2026-06-17T13:04:27Z</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2045,7 +2045,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2025-11-04T12:30:09Z</t>
+          <t>2026-06-18T22:16:08Z</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-06-11T00:10:04Z</t>
+          <t>2026-06-17T02:05:44Z</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3299,11 +3299,11 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-06-14T03:52:13Z</t>
+          <t>2026-06-21T04:28:29Z</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="70">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-05-05T13:33:04Z</t>
+          <t>2026-06-15T00:32:37Z</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-05-07T13:30:37Z</t>
+          <t>2026-06-19T16:17:29Z</t>
         </is>
       </c>
       <c r="L72" t="n">
@@ -4313,7 +4313,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-05-23T20:32:52Z</t>
+          <t>2026-06-19T11:53:14Z</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -4322,7 +4322,7 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -4341,11 +4341,11 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-05-23T20:36:11Z</t>
+          <t>2026-06-17T11:39:32Z</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="89">
@@ -5035,7 +5035,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-05-31T00:51:08Z</t>
+          <t>2026-06-21T05:04:02Z</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -5063,11 +5063,11 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>2026-05-31T06:59:53Z</t>
+          <t>2026-06-21T09:45:00Z</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="102">

--- a/pinokio_repos.xlsx
+++ b/pinokio_repos.xlsx
@@ -2607,7 +2607,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-06-13T21:00:26Z</t>
+          <t>2026-06-26T13:30:41Z</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2616,7 +2616,7 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -2635,11 +2635,11 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-06-14T09:44:36Z</t>
+          <t>2026-06-28T09:20:01Z</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>4123</v>
+        <v>4167</v>
       </c>
     </row>
     <row r="58">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-05-28T20:33:04Z</t>
+          <t>2026-06-22T00:43:17Z</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2025-12-02T20:56:20Z</t>
+          <t>2026-06-22T00:43:13Z</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -2855,11 +2855,11 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-05-29T22:40:51Z</t>
+          <t>2026-06-27T21:00:17Z</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="62">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-06-17T02:05:44Z</t>
+          <t>2026-06-22T20:40:29Z</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3299,11 +3299,11 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-06-21T04:28:29Z</t>
+          <t>2026-06-28T08:03:45Z</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="70">
@@ -3553,7 +3553,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2025-11-04T13:06:11Z</t>
+          <t>2026-06-23T11:41:29Z</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3581,11 +3581,11 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-05-03T00:00:27Z</t>
+          <t>2026-06-27T11:48:22Z</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="75">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-06-10T13:53:24Z</t>
+          <t>2026-06-26T05:14:07Z</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3832,7 +3832,7 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -3851,11 +3851,11 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-06-14T08:38:31Z</t>
+          <t>2026-06-28T08:36:23Z</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>901</v>
+        <v>934</v>
       </c>
     </row>
     <row r="80">
@@ -4367,7 +4367,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-05-25T01:05:38Z</t>
+          <t>2026-06-23T16:22:14Z</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -4395,11 +4395,11 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-05-30T01:54:22Z</t>
+          <t>2026-06-25T09:16:47Z</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="90">
